--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA415"/>
+  <dimension ref="A1:AA431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -42336,6 +42336,1494 @@
         </is>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>Vk Suma Sro</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>Vk Suma Sro</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>53809</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>Veľký Krtíš</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>27 Osloboditeľov</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>990 01</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vksuma.sk</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr"/>
+      <c r="K416" s="2" t="inlineStr"/>
+      <c r="L416" s="2" t="inlineStr"/>
+      <c r="M416" s="2" t="inlineStr"/>
+      <c r="N416" s="2" t="inlineStr">
+        <is>
+          <t>karolszuma@gmail.com</t>
+        </is>
+      </c>
+      <c r="O416" s="2" t="inlineStr">
+        <is>
+          <t>+421 47 483 11 00</t>
+        </is>
+      </c>
+      <c r="P416" s="2" t="inlineStr"/>
+      <c r="Q416" s="2" t="inlineStr"/>
+      <c r="R416" s="2" t="inlineStr"/>
+      <c r="S416" s="2" t="inlineStr"/>
+      <c r="T416" s="2" t="inlineStr"/>
+      <c r="U416" s="2" t="inlineStr"/>
+      <c r="V416" s="2" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
+      <c r="X416" s="2" t="inlineStr"/>
+      <c r="Y416" s="2" t="inlineStr"/>
+      <c r="Z416" s="2" t="inlineStr"/>
+      <c r="AA416" s="2" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj IV</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>28a Jána Stanislava</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>841 05</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koft.sk</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr"/>
+      <c r="K417" s="2" t="inlineStr"/>
+      <c r="L417" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M417" s="2" t="inlineStr"/>
+      <c r="N417" s="2" t="inlineStr">
+        <is>
+          <t>infokoft@koft.sk</t>
+        </is>
+      </c>
+      <c r="O417" s="2" t="inlineStr">
+        <is>
+          <t>+421 2 502 052 00</t>
+        </is>
+      </c>
+      <c r="P417" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q417" s="2" t="inlineStr">
+        <is>
+          <t>17335248</t>
+        </is>
+      </c>
+      <c r="R417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/koft-s-r-o/</t>
+        </is>
+      </c>
+      <c r="S417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/otazkavoflasi</t>
+        </is>
+      </c>
+      <c r="T417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/koft.sk</t>
+        </is>
+      </c>
+      <c r="U417" s="2" t="inlineStr"/>
+      <c r="V417" s="2" t="inlineStr"/>
+      <c r="W417" s="2" t="inlineStr">
+        <is>
+          <t>Branislav Machovič</t>
+        </is>
+      </c>
+      <c r="X417" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y417" s="2" t="inlineStr"/>
+      <c r="Z417" s="2" t="inlineStr"/>
+      <c r="AA417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/branislav-machovič-53a57085</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj IV</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>28a Jána Stanislava</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>841 05</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koft.sk</t>
+        </is>
+      </c>
+      <c r="J418" s="2" t="inlineStr"/>
+      <c r="K418" s="2" t="inlineStr"/>
+      <c r="L418" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M418" s="2" t="inlineStr"/>
+      <c r="N418" s="2" t="inlineStr">
+        <is>
+          <t>infokoft@koft.sk</t>
+        </is>
+      </c>
+      <c r="O418" s="2" t="inlineStr">
+        <is>
+          <t>+421 2 502 052 00</t>
+        </is>
+      </c>
+      <c r="P418" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q418" s="2" t="inlineStr">
+        <is>
+          <t>17335248</t>
+        </is>
+      </c>
+      <c r="R418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/koft-s-r-o/</t>
+        </is>
+      </c>
+      <c r="S418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/otazkavoflasi</t>
+        </is>
+      </c>
+      <c r="T418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/koft.sk</t>
+        </is>
+      </c>
+      <c r="U418" s="2" t="inlineStr"/>
+      <c r="V418" s="2" t="inlineStr"/>
+      <c r="W418" s="2" t="inlineStr">
+        <is>
+          <t>Martin Lešo</t>
+        </is>
+      </c>
+      <c r="X418" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y418" s="2" t="inlineStr"/>
+      <c r="Z418" s="2" t="inlineStr"/>
+      <c r="AA418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martin-le%C5%A1o-8536aa34/?originalSubdomain=sk</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>Valsesia, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>Valsesia, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>11929</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>Budča</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj, Zvolen</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>10 Stromová</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>962 33</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vino-obchod.sk</t>
+        </is>
+      </c>
+      <c r="J419" s="2" t="inlineStr"/>
+      <c r="K419" s="2" t="inlineStr"/>
+      <c r="L419" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M419" s="2" t="inlineStr"/>
+      <c r="N419" s="2" t="inlineStr">
+        <is>
+          <t>info@vino-obchod.sk</t>
+        </is>
+      </c>
+      <c r="O419" s="2" t="inlineStr"/>
+      <c r="P419" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q419" s="2" t="inlineStr">
+        <is>
+          <t>36626031</t>
+        </is>
+      </c>
+      <c r="R419" s="2" t="inlineStr"/>
+      <c r="S419" s="2" t="inlineStr"/>
+      <c r="T419" s="2" t="inlineStr"/>
+      <c r="U419" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Valsesiasro</t>
+        </is>
+      </c>
+      <c r="V419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCAnww4K_EunrRxjdBi6EfvQ</t>
+        </is>
+      </c>
+      <c r="W419" s="2" t="inlineStr">
+        <is>
+          <t>Róbert Mráz</t>
+        </is>
+      </c>
+      <c r="X419" s="2" t="inlineStr">
+        <is>
+          <t>Executive Manager</t>
+        </is>
+      </c>
+      <c r="Y419" s="2" t="inlineStr"/>
+      <c r="Z419" s="2" t="inlineStr"/>
+      <c r="AA419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/r%C3%B3bert-mr%C3%A1z-718436153/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>Diskonto S.r.o.</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>Diskonto S.r.o.</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>54205</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>Spišská Nová Ves</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>17 Radlinského</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>052 01</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.diskonto.sk</t>
+        </is>
+      </c>
+      <c r="J420" s="2" t="inlineStr"/>
+      <c r="K420" s="2" t="inlineStr"/>
+      <c r="L420" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M420" s="2" t="inlineStr"/>
+      <c r="N420" s="2" t="inlineStr">
+        <is>
+          <t>diskonto@diskonto.sk</t>
+        </is>
+      </c>
+      <c r="O420" s="2" t="inlineStr"/>
+      <c r="P420" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q420" s="2" t="inlineStr">
+        <is>
+          <t>44541473</t>
+        </is>
+      </c>
+      <c r="R420" s="2" t="inlineStr"/>
+      <c r="S420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/diskontoSK/</t>
+        </is>
+      </c>
+      <c r="T420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diskonto_sk/</t>
+        </is>
+      </c>
+      <c r="U420" s="2" t="inlineStr"/>
+      <c r="V420" s="2" t="inlineStr"/>
+      <c r="W420" s="2" t="inlineStr"/>
+      <c r="X420" s="2" t="inlineStr"/>
+      <c r="Y420" s="2" t="inlineStr"/>
+      <c r="Z420" s="2" t="inlineStr"/>
+      <c r="AA420" s="2" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>Vino Sardo S. R. O.</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>Vino Sardo S. R. O.</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>20247</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>Myjava</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>524/19 Nám. M. R. Štefánika</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>907 01</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>https://vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="J421" s="2" t="inlineStr"/>
+      <c r="K421" s="2" t="inlineStr"/>
+      <c r="L421" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M421" s="2" t="inlineStr"/>
+      <c r="N421" s="2" t="inlineStr">
+        <is>
+          <t>info@vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="O421" s="2" t="inlineStr">
+        <is>
+          <t>+421 34/653 81 85</t>
+        </is>
+      </c>
+      <c r="P421" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q421" s="2" t="inlineStr">
+        <is>
+          <t>46833625</t>
+        </is>
+      </c>
+      <c r="R421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vino-sardo</t>
+        </is>
+      </c>
+      <c r="S421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="T421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinosardo</t>
+        </is>
+      </c>
+      <c r="U421" s="2" t="inlineStr"/>
+      <c r="V421" s="2" t="inlineStr"/>
+      <c r="W421" s="2" t="inlineStr">
+        <is>
+          <t>Veronika Lhotska</t>
+        </is>
+      </c>
+      <c r="X421" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y421" s="2" t="inlineStr"/>
+      <c r="Z421" s="2" t="inlineStr"/>
+      <c r="AA421" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/veronika-lhotska-00808511a</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>Fine Wines S.r.o.</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>Fine Wines S.r.o.</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>11880</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>Staré Grunty 7A</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>841 04</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.finewines.sk</t>
+        </is>
+      </c>
+      <c r="J422" s="2" t="inlineStr"/>
+      <c r="K422" s="2" t="inlineStr"/>
+      <c r="L422" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M422" s="2" t="inlineStr"/>
+      <c r="N422" s="2" t="inlineStr">
+        <is>
+          <t>office@finewines.sk</t>
+        </is>
+      </c>
+      <c r="O422" s="2" t="inlineStr"/>
+      <c r="P422" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q422" s="2" t="inlineStr">
+        <is>
+          <t>35752173</t>
+        </is>
+      </c>
+      <c r="R422" s="2" t="inlineStr"/>
+      <c r="S422" s="2" t="inlineStr"/>
+      <c r="T422" s="2" t="inlineStr"/>
+      <c r="U422" s="2" t="inlineStr"/>
+      <c r="V422" s="2" t="inlineStr"/>
+      <c r="W422" s="2" t="inlineStr"/>
+      <c r="X422" s="2" t="inlineStr"/>
+      <c r="Y422" s="2" t="inlineStr"/>
+      <c r="Z422" s="2" t="inlineStr"/>
+      <c r="AA422" s="2" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>Cromatop, S.r.o</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>Cromatop, S.r.o</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>54109</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>Hôrka nad Váhom</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj, Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>Hôrka Nad Váhom 1</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>916 32</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>https://croma.sk, https://www.flaskomat.sk</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr"/>
+      <c r="K423" s="2" t="inlineStr"/>
+      <c r="L423" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="inlineStr"/>
+      <c r="N423" s="2" t="inlineStr">
+        <is>
+          <t>croma@croma.sk</t>
+        </is>
+      </c>
+      <c r="O423" s="2" t="inlineStr"/>
+      <c r="P423" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q423" s="2" t="inlineStr">
+        <is>
+          <t>36338893</t>
+        </is>
+      </c>
+      <c r="R423" s="2" t="inlineStr"/>
+      <c r="S423" s="2" t="inlineStr"/>
+      <c r="T423" s="2" t="inlineStr"/>
+      <c r="U423" s="2" t="inlineStr"/>
+      <c r="V423" s="2" t="inlineStr"/>
+      <c r="W423" s="2" t="inlineStr">
+        <is>
+          <t>Miloslav Králik</t>
+        </is>
+      </c>
+      <c r="X423" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y423" s="2" t="inlineStr"/>
+      <c r="Z423" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA423" s="2" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>Gourmand Sk S. R. O.</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>Gourmand Sk S. R. O.</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>11918</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>12573, 50E Tomášikova</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>https://vinopolis.sk</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr"/>
+      <c r="K424" s="2" t="inlineStr"/>
+      <c r="L424" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="inlineStr"/>
+      <c r="N424" s="2" t="inlineStr">
+        <is>
+          <t>info@vinopolis.sk</t>
+        </is>
+      </c>
+      <c r="O424" s="2" t="inlineStr"/>
+      <c r="P424" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q424" s="2" t="inlineStr">
+        <is>
+          <t>46005188</t>
+        </is>
+      </c>
+      <c r="R424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinopolis-sk/</t>
+        </is>
+      </c>
+      <c r="S424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinopolis.sk/</t>
+        </is>
+      </c>
+      <c r="T424" s="2" t="inlineStr"/>
+      <c r="U424" s="2" t="inlineStr"/>
+      <c r="V424" s="2" t="inlineStr"/>
+      <c r="W424" s="2" t="inlineStr">
+        <is>
+          <t>Tibor Körmendi</t>
+        </is>
+      </c>
+      <c r="X424" s="2" t="inlineStr">
+        <is>
+          <t>Responsible</t>
+        </is>
+      </c>
+      <c r="Y424" s="2" t="inlineStr"/>
+      <c r="Z424" s="2" t="inlineStr"/>
+      <c r="AA424" s="2" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>Ll Wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>Ll Wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>42564</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj V</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>7 Bosákova</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>851 04</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.llwine.sk</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr"/>
+      <c r="K425" s="2" t="inlineStr"/>
+      <c r="L425" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="inlineStr"/>
+      <c r="N425" s="2" t="inlineStr">
+        <is>
+          <t>lipka@llwine.sk</t>
+        </is>
+      </c>
+      <c r="O425" s="2" t="inlineStr"/>
+      <c r="P425" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q425" s="2" t="inlineStr">
+        <is>
+          <t>45895813</t>
+        </is>
+      </c>
+      <c r="R425" s="2" t="inlineStr"/>
+      <c r="S425" s="2" t="inlineStr"/>
+      <c r="T425" s="2" t="inlineStr"/>
+      <c r="U425" s="2" t="inlineStr"/>
+      <c r="V425" s="2" t="inlineStr"/>
+      <c r="W425" s="2" t="inlineStr"/>
+      <c r="X425" s="2" t="inlineStr"/>
+      <c r="Y425" s="2" t="inlineStr"/>
+      <c r="Z425" s="2" t="inlineStr"/>
+      <c r="AA425" s="2" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>Barbara Mincíková - Vinopolitan</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Vinopolitan</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>32100</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj I</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>6 Námestie SNP</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>811 06</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinopolitan.sk</t>
+        </is>
+      </c>
+      <c r="J426" s="2" t="inlineStr"/>
+      <c r="K426" s="2" t="inlineStr"/>
+      <c r="L426" s="2" t="inlineStr"/>
+      <c r="M426" s="2" t="inlineStr"/>
+      <c r="N426" s="2" t="inlineStr">
+        <is>
+          <t>info@vinopolitan.sk</t>
+        </is>
+      </c>
+      <c r="O426" s="2" t="inlineStr"/>
+      <c r="P426" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q426" s="2" t="inlineStr">
+        <is>
+          <t>47657235</t>
+        </is>
+      </c>
+      <c r="R426" s="2" t="inlineStr"/>
+      <c r="S426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinopolitanbratislava/</t>
+        </is>
+      </c>
+      <c r="T426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinopolitan_wineshop/</t>
+        </is>
+      </c>
+      <c r="U426" s="2" t="inlineStr"/>
+      <c r="V426" s="2" t="inlineStr"/>
+      <c r="W426" s="2" t="inlineStr"/>
+      <c r="X426" s="2" t="inlineStr"/>
+      <c r="Y426" s="2" t="inlineStr"/>
+      <c r="Z426" s="2" t="inlineStr"/>
+      <c r="AA426" s="2" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr"/>
+      <c r="K427" s="2" t="inlineStr"/>
+      <c r="L427" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="inlineStr"/>
+      <c r="N427" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O427" s="2" t="inlineStr"/>
+      <c r="P427" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q427" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R427" s="2" t="inlineStr"/>
+      <c r="S427" s="2" t="inlineStr"/>
+      <c r="T427" s="2" t="inlineStr"/>
+      <c r="U427" s="2" t="inlineStr"/>
+      <c r="V427" s="2" t="inlineStr"/>
+      <c r="W427" s="2" t="inlineStr">
+        <is>
+          <t>Pavol Pavlus</t>
+        </is>
+      </c>
+      <c r="X427" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y427" s="2" t="inlineStr"/>
+      <c r="Z427" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA427" s="2" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J428" s="2" t="inlineStr"/>
+      <c r="K428" s="2" t="inlineStr"/>
+      <c r="L428" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M428" s="2" t="inlineStr"/>
+      <c r="N428" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O428" s="2" t="inlineStr"/>
+      <c r="P428" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q428" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R428" s="2" t="inlineStr"/>
+      <c r="S428" s="2" t="inlineStr"/>
+      <c r="T428" s="2" t="inlineStr"/>
+      <c r="U428" s="2" t="inlineStr"/>
+      <c r="V428" s="2" t="inlineStr"/>
+      <c r="W428" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Vrska</t>
+        </is>
+      </c>
+      <c r="X428" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y428" s="2" t="inlineStr"/>
+      <c r="Z428" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA428" s="2" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr"/>
+      <c r="K429" s="2" t="inlineStr"/>
+      <c r="L429" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M429" s="2" t="inlineStr"/>
+      <c r="N429" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O429" s="2" t="inlineStr"/>
+      <c r="P429" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q429" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R429" s="2" t="inlineStr"/>
+      <c r="S429" s="2" t="inlineStr"/>
+      <c r="T429" s="2" t="inlineStr"/>
+      <c r="U429" s="2" t="inlineStr"/>
+      <c r="V429" s="2" t="inlineStr"/>
+      <c r="W429" s="2" t="inlineStr">
+        <is>
+          <t>Štefan Ondrúš</t>
+        </is>
+      </c>
+      <c r="X429" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y429" s="2" t="inlineStr"/>
+      <c r="Z429" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA429" s="2" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J430" s="2" t="inlineStr"/>
+      <c r="K430" s="2" t="inlineStr"/>
+      <c r="L430" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M430" s="2" t="inlineStr"/>
+      <c r="N430" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O430" s="2" t="inlineStr"/>
+      <c r="P430" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q430" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R430" s="2" t="inlineStr"/>
+      <c r="S430" s="2" t="inlineStr"/>
+      <c r="T430" s="2" t="inlineStr"/>
+      <c r="U430" s="2" t="inlineStr"/>
+      <c r="V430" s="2" t="inlineStr"/>
+      <c r="W430" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Bošanský</t>
+        </is>
+      </c>
+      <c r="X430" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y430" s="2" t="inlineStr"/>
+      <c r="Z430" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA430" s="2" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J431" s="2" t="inlineStr"/>
+      <c r="K431" s="2" t="inlineStr"/>
+      <c r="L431" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M431" s="2" t="inlineStr"/>
+      <c r="N431" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O431" s="2" t="inlineStr"/>
+      <c r="P431" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q431" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R431" s="2" t="inlineStr"/>
+      <c r="S431" s="2" t="inlineStr"/>
+      <c r="T431" s="2" t="inlineStr"/>
+      <c r="U431" s="2" t="inlineStr"/>
+      <c r="V431" s="2" t="inlineStr"/>
+      <c r="W431" s="2" t="inlineStr">
+        <is>
+          <t>Martin Cehula</t>
+        </is>
+      </c>
+      <c r="X431" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y431" s="2" t="inlineStr"/>
+      <c r="Z431" s="2" t="inlineStr"/>
+      <c r="AA431" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA431"/>
+  <dimension ref="A1:AA484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -43824,6 +43824,4875 @@
       <c r="Z431" s="2" t="inlineStr"/>
       <c r="AA431" s="2" t="inlineStr"/>
     </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>Topwine.sk</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>Topwine.sk</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>11930</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>Budča</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj, Zvolen</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>463 Stromová</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>962 33</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.topwine.sk</t>
+        </is>
+      </c>
+      <c r="J432" s="2" t="inlineStr"/>
+      <c r="K432" s="2" t="inlineStr"/>
+      <c r="L432" s="2" t="inlineStr"/>
+      <c r="M432" s="2" t="inlineStr"/>
+      <c r="N432" s="2" t="inlineStr">
+        <is>
+          <t>info@topwine.sk</t>
+        </is>
+      </c>
+      <c r="O432" s="2" t="inlineStr"/>
+      <c r="P432" s="2" t="inlineStr"/>
+      <c r="Q432" s="2" t="inlineStr"/>
+      <c r="R432" s="2" t="inlineStr"/>
+      <c r="S432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Topwinesk-61550639900124/</t>
+        </is>
+      </c>
+      <c r="T432" s="2" t="inlineStr"/>
+      <c r="U432" s="2" t="inlineStr"/>
+      <c r="V432" s="2" t="inlineStr"/>
+      <c r="W432" s="2" t="inlineStr"/>
+      <c r="X432" s="2" t="inlineStr"/>
+      <c r="Y432" s="2" t="inlineStr"/>
+      <c r="Z432" s="2" t="inlineStr"/>
+      <c r="AA432" s="2" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>Shop4wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>Shop4wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>11926</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>Piešťany</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>2149 Hodžova</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>921 01</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>https://shop4wine.sk</t>
+        </is>
+      </c>
+      <c r="J433" s="2" t="inlineStr"/>
+      <c r="K433" s="2" t="inlineStr"/>
+      <c r="L433" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M433" s="2" t="inlineStr"/>
+      <c r="N433" s="2" t="inlineStr">
+        <is>
+          <t>info@shop4wine.sk</t>
+        </is>
+      </c>
+      <c r="O433" s="2" t="inlineStr"/>
+      <c r="P433" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q433" s="2" t="inlineStr">
+        <is>
+          <t>45909911</t>
+        </is>
+      </c>
+      <c r="R433" s="2" t="inlineStr"/>
+      <c r="S433" s="2" t="inlineStr"/>
+      <c r="T433" s="2" t="inlineStr"/>
+      <c r="U433" s="2" t="inlineStr"/>
+      <c r="V433" s="2" t="inlineStr"/>
+      <c r="W433" s="2" t="inlineStr"/>
+      <c r="X433" s="2" t="inlineStr"/>
+      <c r="Y433" s="2" t="inlineStr"/>
+      <c r="Z433" s="2" t="inlineStr"/>
+      <c r="AA433" s="2" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>Komfos Prešov, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>Komfos Prešov, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>103173</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>Ľubotice</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj, Prešov</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>2 Ľubochnianska</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>080 06</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>https://cbashop.sk, https://www.komfos.sk</t>
+        </is>
+      </c>
+      <c r="J434" s="2" t="inlineStr"/>
+      <c r="K434" s="2" t="inlineStr"/>
+      <c r="L434" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="M434" s="2" t="inlineStr"/>
+      <c r="N434" s="2" t="inlineStr">
+        <is>
+          <t>office@komfos.sk</t>
+        </is>
+      </c>
+      <c r="O434" s="2" t="inlineStr"/>
+      <c r="P434" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q434" s="2" t="inlineStr">
+        <is>
+          <t>36454184</t>
+        </is>
+      </c>
+      <c r="R434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cba-komfos/</t>
+        </is>
+      </c>
+      <c r="S434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CBAKomfos</t>
+        </is>
+      </c>
+      <c r="T434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cbakomfos/</t>
+        </is>
+      </c>
+      <c r="U434" s="2" t="inlineStr"/>
+      <c r="V434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@komfospresovs.r.o.-velkoob8582/</t>
+        </is>
+      </c>
+      <c r="W434" s="2" t="inlineStr">
+        <is>
+          <t>Slavko Koncar</t>
+        </is>
+      </c>
+      <c r="X434" s="2" t="inlineStr">
+        <is>
+          <t>Area Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y434" s="2" t="inlineStr"/>
+      <c r="Z434" s="2" t="inlineStr"/>
+      <c r="AA434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/slavko-koncar-2817a726/</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>Alko90</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>Alko90</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>29347</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>Most pri Bratislave</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Senec</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>775, Bratislavská</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>900 46</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alko90.sk</t>
+        </is>
+      </c>
+      <c r="J435" s="2" t="inlineStr"/>
+      <c r="K435" s="2" t="inlineStr"/>
+      <c r="L435" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M435" s="2" t="inlineStr"/>
+      <c r="N435" s="2" t="inlineStr">
+        <is>
+          <t>info@alko90.sk</t>
+        </is>
+      </c>
+      <c r="O435" s="2" t="inlineStr"/>
+      <c r="P435" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q435" s="2" t="inlineStr">
+        <is>
+          <t>50484800</t>
+        </is>
+      </c>
+      <c r="R435" s="2" t="inlineStr"/>
+      <c r="S435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/alko90sk/</t>
+        </is>
+      </c>
+      <c r="T435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alko90sk/</t>
+        </is>
+      </c>
+      <c r="U435" s="2" t="inlineStr"/>
+      <c r="V435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@alko90sk/</t>
+        </is>
+      </c>
+      <c r="W435" s="2" t="inlineStr">
+        <is>
+          <t>Andrej Slavik</t>
+        </is>
+      </c>
+      <c r="X435" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y435" s="2" t="inlineStr"/>
+      <c r="Z435" s="2" t="inlineStr"/>
+      <c r="AA435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrej-sl%C3%A1vik-91808758/</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>27285</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>18 Jakuba Hašku</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="J436" s="2" t="inlineStr"/>
+      <c r="K436" s="2" t="inlineStr"/>
+      <c r="L436" s="2" t="inlineStr"/>
+      <c r="M436" s="2" t="inlineStr"/>
+      <c r="N436" s="2" t="inlineStr">
+        <is>
+          <t>hornisova.maria@vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="O436" s="2" t="inlineStr"/>
+      <c r="P436" s="2" t="inlineStr"/>
+      <c r="Q436" s="2" t="inlineStr"/>
+      <c r="R436" s="2" t="inlineStr"/>
+      <c r="S436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekahornis/</t>
+        </is>
+      </c>
+      <c r="T436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_hornis/</t>
+        </is>
+      </c>
+      <c r="U436" s="2" t="inlineStr"/>
+      <c r="V436" s="2" t="inlineStr"/>
+      <c r="W436" s="2" t="inlineStr">
+        <is>
+          <t>Viliam Horniš</t>
+        </is>
+      </c>
+      <c r="X436" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y436" s="2" t="inlineStr"/>
+      <c r="Z436" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA436" s="2" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>27285</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>18 Jakuba Hašku</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="J437" s="2" t="inlineStr"/>
+      <c r="K437" s="2" t="inlineStr"/>
+      <c r="L437" s="2" t="inlineStr"/>
+      <c r="M437" s="2" t="inlineStr"/>
+      <c r="N437" s="2" t="inlineStr">
+        <is>
+          <t>hornisova.maria@vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="O437" s="2" t="inlineStr"/>
+      <c r="P437" s="2" t="inlineStr"/>
+      <c r="Q437" s="2" t="inlineStr"/>
+      <c r="R437" s="2" t="inlineStr"/>
+      <c r="S437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekahornis/</t>
+        </is>
+      </c>
+      <c r="T437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_hornis/</t>
+        </is>
+      </c>
+      <c r="U437" s="2" t="inlineStr"/>
+      <c r="V437" s="2" t="inlineStr"/>
+      <c r="W437" s="2" t="inlineStr">
+        <is>
+          <t>Mária Hornišová</t>
+        </is>
+      </c>
+      <c r="X437" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y437" s="2" t="inlineStr"/>
+      <c r="Z437" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA437" s="2" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>Radničná Vinotéka Pezinok</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>Radničná Vinotéka Pezinok</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>41106</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>Pezinok</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>1, 1 M. R. Štefánika</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>902 01</t>
+        </is>
+      </c>
+      <c r="I438" s="2" t="inlineStr">
+        <is>
+          <t>http://vinoradnica.sk, https://ratuzky.sk</t>
+        </is>
+      </c>
+      <c r="J438" s="2" t="inlineStr"/>
+      <c r="K438" s="2" t="inlineStr"/>
+      <c r="L438" s="2" t="inlineStr"/>
+      <c r="M438" s="2" t="inlineStr"/>
+      <c r="N438" s="2" t="inlineStr">
+        <is>
+          <t>info@vinoradnica.sk</t>
+        </is>
+      </c>
+      <c r="O438" s="2" t="inlineStr"/>
+      <c r="P438" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q438" s="2" t="inlineStr">
+        <is>
+          <t>34675493</t>
+        </is>
+      </c>
+      <c r="R438" s="2" t="inlineStr"/>
+      <c r="S438" s="2" t="inlineStr"/>
+      <c r="T438" s="2" t="inlineStr"/>
+      <c r="U438" s="2" t="inlineStr"/>
+      <c r="V438" s="2" t="inlineStr"/>
+      <c r="W438" s="2" t="inlineStr"/>
+      <c r="X438" s="2" t="inlineStr"/>
+      <c r="Y438" s="2" t="inlineStr"/>
+      <c r="Z438" s="2" t="inlineStr"/>
+      <c r="AA438" s="2" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka One More</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka One More</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>21140</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>10301, 108 Vajnorská</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>https://onemore.sk</t>
+        </is>
+      </c>
+      <c r="J439" s="2" t="inlineStr"/>
+      <c r="K439" s="2" t="inlineStr"/>
+      <c r="L439" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M439" s="2" t="inlineStr"/>
+      <c r="N439" s="2" t="inlineStr">
+        <is>
+          <t>info@onemore.sk</t>
+        </is>
+      </c>
+      <c r="O439" s="2" t="inlineStr"/>
+      <c r="P439" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q439" s="2" t="inlineStr">
+        <is>
+          <t>46896961</t>
+        </is>
+      </c>
+      <c r="R439" s="2" t="inlineStr"/>
+      <c r="S439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/onemore.wine/</t>
+        </is>
+      </c>
+      <c r="T439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onemore_wine/</t>
+        </is>
+      </c>
+      <c r="U439" s="2" t="inlineStr"/>
+      <c r="V439" s="2" t="inlineStr"/>
+      <c r="W439" s="2" t="inlineStr"/>
+      <c r="X439" s="2" t="inlineStr"/>
+      <c r="Y439" s="2" t="inlineStr"/>
+      <c r="Z439" s="2" t="inlineStr"/>
+      <c r="AA439" s="2" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>40555</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>Laurinská 210/8</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>811 05</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>https://bwd.sk</t>
+        </is>
+      </c>
+      <c r="J440" s="2" t="inlineStr"/>
+      <c r="K440" s="2" t="inlineStr"/>
+      <c r="L440" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M440" s="2" t="inlineStr"/>
+      <c r="N440" s="2" t="inlineStr">
+        <is>
+          <t>info@bwd.sk</t>
+        </is>
+      </c>
+      <c r="O440" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/207 824 67</t>
+        </is>
+      </c>
+      <c r="P440" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q440" s="2" t="inlineStr">
+        <is>
+          <t>50444271</t>
+        </is>
+      </c>
+      <c r="R440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/best-wines-distribution/</t>
+        </is>
+      </c>
+      <c r="S440" s="2" t="inlineStr"/>
+      <c r="T440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bwd.sk/</t>
+        </is>
+      </c>
+      <c r="U440" s="2" t="inlineStr"/>
+      <c r="V440" s="2" t="inlineStr"/>
+      <c r="W440" s="2" t="inlineStr">
+        <is>
+          <t>Marco Masutti</t>
+        </is>
+      </c>
+      <c r="X440" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y440" s="2" t="inlineStr"/>
+      <c r="Z440" s="2" t="inlineStr"/>
+      <c r="AA440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marco-masutti-056b12203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>40555</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>Laurinská 210/8</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>811 05</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>https://bwd.sk</t>
+        </is>
+      </c>
+      <c r="J441" s="2" t="inlineStr"/>
+      <c r="K441" s="2" t="inlineStr"/>
+      <c r="L441" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M441" s="2" t="inlineStr"/>
+      <c r="N441" s="2" t="inlineStr">
+        <is>
+          <t>info@bwd.sk</t>
+        </is>
+      </c>
+      <c r="O441" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/207 824 67</t>
+        </is>
+      </c>
+      <c r="P441" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q441" s="2" t="inlineStr">
+        <is>
+          <t>50444271</t>
+        </is>
+      </c>
+      <c r="R441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/best-wines-distribution/</t>
+        </is>
+      </c>
+      <c r="S441" s="2" t="inlineStr"/>
+      <c r="T441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bwd.sk/</t>
+        </is>
+      </c>
+      <c r="U441" s="2" t="inlineStr"/>
+      <c r="V441" s="2" t="inlineStr"/>
+      <c r="W441" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Kollar</t>
+        </is>
+      </c>
+      <c r="X441" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier/ Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y441" s="2" t="inlineStr"/>
+      <c r="Z441" s="2" t="inlineStr"/>
+      <c r="AA441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gabriel-kollar-5996183a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka André, Sro</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka André, Sro</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>41101</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>1 Obchodné centrum Turiec</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>036 01</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoteka-andre.sk</t>
+        </is>
+      </c>
+      <c r="J442" s="2" t="inlineStr"/>
+      <c r="K442" s="2" t="inlineStr"/>
+      <c r="L442" s="2" t="inlineStr"/>
+      <c r="M442" s="2" t="inlineStr"/>
+      <c r="N442" s="2" t="inlineStr">
+        <is>
+          <t>info@vinoteka-andre.sk</t>
+        </is>
+      </c>
+      <c r="O442" s="2" t="inlineStr"/>
+      <c r="P442" s="2" t="inlineStr"/>
+      <c r="Q442" s="2" t="inlineStr"/>
+      <c r="R442" s="2" t="inlineStr"/>
+      <c r="S442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinotekaAndre/</t>
+        </is>
+      </c>
+      <c r="T442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotekaandre/</t>
+        </is>
+      </c>
+      <c r="U442" s="2" t="inlineStr"/>
+      <c r="V442" s="2" t="inlineStr"/>
+      <c r="W442" s="2" t="inlineStr"/>
+      <c r="X442" s="2" t="inlineStr"/>
+      <c r="Y442" s="2" t="inlineStr"/>
+      <c r="Z442" s="2" t="inlineStr"/>
+      <c r="AA442" s="2" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>108846</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>Svit</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj, Poprad</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>208, 156 Mierová</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>059 21</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="J443" s="2" t="inlineStr"/>
+      <c r="K443" s="2" t="inlineStr"/>
+      <c r="L443" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M443" s="2" t="inlineStr"/>
+      <c r="N443" s="2" t="inlineStr">
+        <is>
+          <t>info@jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="O443" s="2" t="inlineStr">
+        <is>
+          <t>+421 52 123 45 67</t>
+        </is>
+      </c>
+      <c r="P443" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q443" s="2" t="inlineStr">
+        <is>
+          <t>46814973</t>
+        </is>
+      </c>
+      <c r="R443" s="2" t="inlineStr"/>
+      <c r="S443" s="2" t="inlineStr"/>
+      <c r="T443" s="2" t="inlineStr"/>
+      <c r="U443" s="2" t="inlineStr"/>
+      <c r="V443" s="2" t="inlineStr"/>
+      <c r="W443" s="2" t="inlineStr">
+        <is>
+          <t>Jan Filipsky</t>
+        </is>
+      </c>
+      <c r="X443" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y443" s="2" t="inlineStr"/>
+      <c r="Z443" s="2" t="inlineStr"/>
+      <c r="AA443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jan-filipsky-a96a5345/</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>108846</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>Svit</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj, Poprad</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>208, 156 Mierová</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>059 21</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="J444" s="2" t="inlineStr"/>
+      <c r="K444" s="2" t="inlineStr"/>
+      <c r="L444" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M444" s="2" t="inlineStr"/>
+      <c r="N444" s="2" t="inlineStr">
+        <is>
+          <t>info@jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="O444" s="2" t="inlineStr">
+        <is>
+          <t>+421 52 123 45 67</t>
+        </is>
+      </c>
+      <c r="P444" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q444" s="2" t="inlineStr">
+        <is>
+          <t>46814973</t>
+        </is>
+      </c>
+      <c r="R444" s="2" t="inlineStr"/>
+      <c r="S444" s="2" t="inlineStr"/>
+      <c r="T444" s="2" t="inlineStr"/>
+      <c r="U444" s="2" t="inlineStr"/>
+      <c r="V444" s="2" t="inlineStr"/>
+      <c r="W444" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Filipský</t>
+        </is>
+      </c>
+      <c r="X444" s="2" t="inlineStr">
+        <is>
+          <t>Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y444" s="2" t="inlineStr"/>
+      <c r="Z444" s="2" t="inlineStr"/>
+      <c r="AA444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-filipsk%C3%BD-73477383/</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>Reming, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>Reming, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>47015</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>Liptovsky Mikulas</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr"/>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>Moyzesova No. 4358/9</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>031 01</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>https://reming-sk.com</t>
+        </is>
+      </c>
+      <c r="J445" s="2" t="inlineStr"/>
+      <c r="K445" s="2" t="inlineStr"/>
+      <c r="L445" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M445" s="2" t="inlineStr"/>
+      <c r="N445" s="2" t="inlineStr">
+        <is>
+          <t>office@reming-sk.com</t>
+        </is>
+      </c>
+      <c r="O445" s="2" t="inlineStr"/>
+      <c r="P445" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q445" s="2" t="inlineStr">
+        <is>
+          <t>45605220</t>
+        </is>
+      </c>
+      <c r="R445" s="2" t="inlineStr"/>
+      <c r="S445" s="2" t="inlineStr"/>
+      <c r="T445" s="2" t="inlineStr"/>
+      <c r="U445" s="2" t="inlineStr"/>
+      <c r="V445" s="2" t="inlineStr"/>
+      <c r="W445" s="2" t="inlineStr"/>
+      <c r="X445" s="2" t="inlineStr"/>
+      <c r="Y445" s="2" t="inlineStr"/>
+      <c r="Z445" s="2" t="inlineStr"/>
+      <c r="AA445" s="2" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>Starosel Slovensko S.r.o.</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>Starosel Slovensko S.r.o.</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>20088</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>Michalovce</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>Kosický</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>Štefaniková 76</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>07101</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr">
+        <is>
+          <t>http://starosel.sk, https://www.staroselshop.sk</t>
+        </is>
+      </c>
+      <c r="J446" s="2" t="inlineStr"/>
+      <c r="K446" s="2" t="inlineStr"/>
+      <c r="L446" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M446" s="2" t="inlineStr"/>
+      <c r="N446" s="2" t="inlineStr">
+        <is>
+          <t>starosel@starosel.sk</t>
+        </is>
+      </c>
+      <c r="O446" s="2" t="inlineStr"/>
+      <c r="P446" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q446" s="2" t="inlineStr">
+        <is>
+          <t>47689901</t>
+        </is>
+      </c>
+      <c r="R446" s="2" t="inlineStr"/>
+      <c r="S446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/starosel.sk/</t>
+        </is>
+      </c>
+      <c r="T446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/staroselslovensko/</t>
+        </is>
+      </c>
+      <c r="U446" s="2" t="inlineStr"/>
+      <c r="V446" s="2" t="inlineStr"/>
+      <c r="W446" s="2" t="inlineStr"/>
+      <c r="X446" s="2" t="inlineStr"/>
+      <c r="Y446" s="2" t="inlineStr"/>
+      <c r="Z446" s="2" t="inlineStr"/>
+      <c r="AA446" s="2" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>Extraprodukty, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>Extraprodukty, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>20087</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>Šamorín</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj, Dunajská Streda</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>Vodárenská 2589/2A</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>931 01</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.extraprodukty.sk</t>
+        </is>
+      </c>
+      <c r="J447" s="2" t="inlineStr"/>
+      <c r="K447" s="2" t="inlineStr"/>
+      <c r="L447" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M447" s="2" t="inlineStr"/>
+      <c r="N447" s="2" t="inlineStr">
+        <is>
+          <t>obchod@extraprodukty.sk</t>
+        </is>
+      </c>
+      <c r="O447" s="2" t="inlineStr"/>
+      <c r="P447" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q447" s="2" t="inlineStr">
+        <is>
+          <t>46158880</t>
+        </is>
+      </c>
+      <c r="R447" s="2" t="inlineStr"/>
+      <c r="S447" s="2" t="inlineStr"/>
+      <c r="T447" s="2" t="inlineStr"/>
+      <c r="U447" s="2" t="inlineStr"/>
+      <c r="V447" s="2" t="inlineStr"/>
+      <c r="W447" s="2" t="inlineStr"/>
+      <c r="X447" s="2" t="inlineStr"/>
+      <c r="Y447" s="2" t="inlineStr"/>
+      <c r="Z447" s="2" t="inlineStr"/>
+      <c r="AA447" s="2" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>Mge Plus S.r.o.</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>Mge Plus S.r.o.</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>28275</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>Trenčianska Teplá</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj, Trenčín</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>Andreja Hlinku 34</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>914 01</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr">
+        <is>
+          <t>https://lacnevino.sk</t>
+        </is>
+      </c>
+      <c r="J448" s="2" t="inlineStr"/>
+      <c r="K448" s="2" t="inlineStr"/>
+      <c r="L448" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M448" s="2" t="inlineStr"/>
+      <c r="N448" s="2" t="inlineStr">
+        <is>
+          <t>mgeplus@centrum.sk</t>
+        </is>
+      </c>
+      <c r="O448" s="2" t="inlineStr"/>
+      <c r="P448" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q448" s="2" t="inlineStr">
+        <is>
+          <t>46198687</t>
+        </is>
+      </c>
+      <c r="R448" s="2" t="inlineStr"/>
+      <c r="S448" s="2" t="inlineStr"/>
+      <c r="T448" s="2" t="inlineStr"/>
+      <c r="U448" s="2" t="inlineStr"/>
+      <c r="V448" s="2" t="inlineStr"/>
+      <c r="W448" s="2" t="inlineStr">
+        <is>
+          <t>Monika Jančová</t>
+        </is>
+      </c>
+      <c r="X448" s="2" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="Y448" s="2" t="inlineStr"/>
+      <c r="Z448" s="2" t="inlineStr"/>
+      <c r="AA448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/monika-jan%C4%8Dov%C3%A1-7ab50a220/</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Pri Modrom Kostolíku</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Pri Modrom Kostolíku</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>49625</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj I</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>2541/2 Sienkiewiczova</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>811 09</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr">
+        <is>
+          <t>https://vinotekamodrykostolik.sk</t>
+        </is>
+      </c>
+      <c r="J449" s="2" t="inlineStr"/>
+      <c r="K449" s="2" t="inlineStr"/>
+      <c r="L449" s="2" t="inlineStr"/>
+      <c r="M449" s="2" t="inlineStr"/>
+      <c r="N449" s="2" t="inlineStr">
+        <is>
+          <t>vinoteka@modrykostolik.sk</t>
+        </is>
+      </c>
+      <c r="O449" s="2" t="inlineStr"/>
+      <c r="P449" s="2" t="inlineStr"/>
+      <c r="Q449" s="2" t="inlineStr"/>
+      <c r="R449" s="2" t="inlineStr"/>
+      <c r="S449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekaprimodromkostoliku/</t>
+        </is>
+      </c>
+      <c r="T449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_modry_kostolik/</t>
+        </is>
+      </c>
+      <c r="U449" s="2" t="inlineStr"/>
+      <c r="V449" s="2" t="inlineStr"/>
+      <c r="W449" s="2" t="inlineStr"/>
+      <c r="X449" s="2" t="inlineStr"/>
+      <c r="Y449" s="2" t="inlineStr"/>
+      <c r="Z449" s="2" t="inlineStr"/>
+      <c r="AA449" s="2" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>Lumarkt, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>Lumarkt, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>11890</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>Staré Mesto</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj, Košice I</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>1 Hutnícka</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>040 01</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lumarkt.sk</t>
+        </is>
+      </c>
+      <c r="J450" s="2" t="inlineStr"/>
+      <c r="K450" s="2" t="inlineStr"/>
+      <c r="L450" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M450" s="2" t="inlineStr"/>
+      <c r="N450" s="2" t="inlineStr">
+        <is>
+          <t>info@lumarkt.sk</t>
+        </is>
+      </c>
+      <c r="O450" s="2" t="inlineStr">
+        <is>
+          <t>+421 55 798 85 71</t>
+        </is>
+      </c>
+      <c r="P450" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q450" s="2" t="inlineStr">
+        <is>
+          <t>36216631</t>
+        </is>
+      </c>
+      <c r="R450" s="2" t="inlineStr"/>
+      <c r="S450" s="2" t="inlineStr"/>
+      <c r="T450" s="2" t="inlineStr"/>
+      <c r="U450" s="2" t="inlineStr"/>
+      <c r="V450" s="2" t="inlineStr"/>
+      <c r="W450" s="2" t="inlineStr">
+        <is>
+          <t>Janka Mrugova</t>
+        </is>
+      </c>
+      <c r="X450" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y450" s="2" t="inlineStr"/>
+      <c r="Z450" s="2" t="inlineStr"/>
+      <c r="AA450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/janka-mrugova-b5364047/</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>Karmen - Velkoobchod Potravín S.r.o.</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>Karmen - Velkoobchod Potravín S.r.o.</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>54186</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>Prešov</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>15 Strojnícka</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>080 06</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karmen.sk</t>
+        </is>
+      </c>
+      <c r="J451" s="2" t="inlineStr"/>
+      <c r="K451" s="2" t="inlineStr"/>
+      <c r="L451" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="M451" s="2" t="inlineStr"/>
+      <c r="N451" s="2" t="inlineStr">
+        <is>
+          <t>karmen@karmen.sk</t>
+        </is>
+      </c>
+      <c r="O451" s="2" t="inlineStr">
+        <is>
+          <t>+421 51/771 17 14</t>
+        </is>
+      </c>
+      <c r="P451" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q451" s="2" t="inlineStr">
+        <is>
+          <t>36447269</t>
+        </is>
+      </c>
+      <c r="R451" s="2" t="inlineStr"/>
+      <c r="S451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100063498972682</t>
+        </is>
+      </c>
+      <c r="T451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cba_karmen/</t>
+        </is>
+      </c>
+      <c r="U451" s="2" t="inlineStr"/>
+      <c r="V451" s="2" t="inlineStr"/>
+      <c r="W451" s="2" t="inlineStr"/>
+      <c r="X451" s="2" t="inlineStr"/>
+      <c r="Y451" s="2" t="inlineStr"/>
+      <c r="Z451" s="2" t="inlineStr"/>
+      <c r="AA451" s="2" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>Great Wines Cellar</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>Great Wines Cellar</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>24602</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>Ružinov</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava II</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>937 Koceľova</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>821 08</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>https://greatwinescellar.com</t>
+        </is>
+      </c>
+      <c r="J452" s="2" t="inlineStr"/>
+      <c r="K452" s="2" t="inlineStr"/>
+      <c r="L452" s="2" t="inlineStr"/>
+      <c r="M452" s="2" t="inlineStr"/>
+      <c r="N452" s="2" t="inlineStr">
+        <is>
+          <t>info@greatwinescellar.com</t>
+        </is>
+      </c>
+      <c r="O452" s="2" t="inlineStr">
+        <is>
+          <t>+43 1 9437915</t>
+        </is>
+      </c>
+      <c r="P452" s="2" t="inlineStr"/>
+      <c r="Q452" s="2" t="inlineStr"/>
+      <c r="R452" s="2" t="inlineStr"/>
+      <c r="S452" s="2" t="inlineStr"/>
+      <c r="T452" s="2" t="inlineStr"/>
+      <c r="U452" s="2" t="inlineStr"/>
+      <c r="V452" s="2" t="inlineStr"/>
+      <c r="W452" s="2" t="inlineStr">
+        <is>
+          <t>Denis Danilenko</t>
+        </is>
+      </c>
+      <c r="X452" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y452" s="2" t="inlineStr"/>
+      <c r="Z452" s="2" t="inlineStr"/>
+      <c r="AA452" s="2" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>Vineria S.r.o.</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>Vineria S.r.o.</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>108851</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>Topoľčany</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>Nitriansky kraj</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>958, 20 Československej armády</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>955 01</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vineria.sk</t>
+        </is>
+      </c>
+      <c r="J453" s="2" t="inlineStr"/>
+      <c r="K453" s="2" t="inlineStr"/>
+      <c r="L453" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M453" s="2" t="inlineStr"/>
+      <c r="N453" s="2" t="inlineStr">
+        <is>
+          <t>obchod@vineria.sk</t>
+        </is>
+      </c>
+      <c r="O453" s="2" t="inlineStr"/>
+      <c r="P453" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q453" s="2" t="inlineStr">
+        <is>
+          <t>46409165</t>
+        </is>
+      </c>
+      <c r="R453" s="2" t="inlineStr"/>
+      <c r="S453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Vineria-Topo%C4%BE%C4%8Dany-100027232792145/</t>
+        </is>
+      </c>
+      <c r="T453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_vineria_/</t>
+        </is>
+      </c>
+      <c r="U453" s="2" t="inlineStr"/>
+      <c r="V453" s="2" t="inlineStr"/>
+      <c r="W453" s="2" t="inlineStr"/>
+      <c r="X453" s="2" t="inlineStr"/>
+      <c r="Y453" s="2" t="inlineStr"/>
+      <c r="Z453" s="2" t="inlineStr"/>
+      <c r="AA453" s="2" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>Novino, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>Novino, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>108848</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava I</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>4087, 26 Krížna</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>811 07</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novino.sk</t>
+        </is>
+      </c>
+      <c r="J454" s="2" t="inlineStr"/>
+      <c r="K454" s="2" t="inlineStr"/>
+      <c r="L454" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M454" s="2" t="inlineStr"/>
+      <c r="N454" s="2" t="inlineStr">
+        <is>
+          <t>predaj@novino.sk</t>
+        </is>
+      </c>
+      <c r="O454" s="2" t="inlineStr"/>
+      <c r="P454" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q454" s="2" t="inlineStr">
+        <is>
+          <t>53348800</t>
+        </is>
+      </c>
+      <c r="R454" s="2" t="inlineStr"/>
+      <c r="S454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Novino.sk/</t>
+        </is>
+      </c>
+      <c r="T454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/novino_sk/</t>
+        </is>
+      </c>
+      <c r="U454" s="2" t="inlineStr"/>
+      <c r="V454" s="2" t="inlineStr"/>
+      <c r="W454" s="2" t="inlineStr">
+        <is>
+          <t>Marek Paulen</t>
+        </is>
+      </c>
+      <c r="X454" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y454" s="2" t="inlineStr"/>
+      <c r="Z454" s="2" t="inlineStr"/>
+      <c r="AA454" s="2" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>ENERGY TRANS, spol. s r.o.</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>Dom Vína žilina</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>11919</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>Rosina</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr"/>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>Rosina 1057</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>013 22</t>
+        </is>
+      </c>
+      <c r="I455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kupvino.sk</t>
+        </is>
+      </c>
+      <c r="J455" s="2" t="inlineStr"/>
+      <c r="K455" s="2" t="inlineStr"/>
+      <c r="L455" s="2" t="inlineStr"/>
+      <c r="M455" s="2" t="inlineStr"/>
+      <c r="N455" s="2" t="inlineStr">
+        <is>
+          <t>kupvino@kupvino.sk</t>
+        </is>
+      </c>
+      <c r="O455" s="2" t="inlineStr"/>
+      <c r="P455" s="2" t="inlineStr"/>
+      <c r="Q455" s="2" t="inlineStr"/>
+      <c r="R455" s="2" t="inlineStr"/>
+      <c r="S455" s="2" t="inlineStr"/>
+      <c r="T455" s="2" t="inlineStr"/>
+      <c r="U455" s="2" t="inlineStr"/>
+      <c r="V455" s="2" t="inlineStr"/>
+      <c r="W455" s="2" t="inlineStr"/>
+      <c r="X455" s="2" t="inlineStr"/>
+      <c r="Y455" s="2" t="inlineStr"/>
+      <c r="Z455" s="2" t="inlineStr"/>
+      <c r="AA455" s="2" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>Vinalma, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>Vinalma, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>11903</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>76 Opatovská</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>911 01</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>http://www.vinalma.sk</t>
+        </is>
+      </c>
+      <c r="J456" s="2" t="inlineStr"/>
+      <c r="K456" s="2" t="inlineStr"/>
+      <c r="L456" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M456" s="2" t="inlineStr"/>
+      <c r="N456" s="2" t="inlineStr">
+        <is>
+          <t>office@vinalma.sk</t>
+        </is>
+      </c>
+      <c r="O456" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/744 58 12</t>
+        </is>
+      </c>
+      <c r="P456" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q456" s="2" t="inlineStr">
+        <is>
+          <t>35697768</t>
+        </is>
+      </c>
+      <c r="R456" s="2" t="inlineStr"/>
+      <c r="S456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinalmaSro/</t>
+        </is>
+      </c>
+      <c r="T456" s="2" t="inlineStr"/>
+      <c r="U456" s="2" t="inlineStr"/>
+      <c r="V456" s="2" t="inlineStr"/>
+      <c r="W456" s="2" t="inlineStr">
+        <is>
+          <t>Edita Durcova</t>
+        </is>
+      </c>
+      <c r="X456" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y456" s="2" t="inlineStr"/>
+      <c r="Z456" s="2" t="inlineStr"/>
+      <c r="AA456" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/edita-durcova-4856203a</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>Pálinkás-Szicsek sro</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>Szicsek Slovakia</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>20089</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>Dunajská Streda</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>39, 29 Hlavná</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>929 01</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.palinkas.sk</t>
+        </is>
+      </c>
+      <c r="J457" s="2" t="inlineStr"/>
+      <c r="K457" s="2" t="inlineStr"/>
+      <c r="L457" s="2" t="inlineStr"/>
+      <c r="M457" s="2" t="inlineStr"/>
+      <c r="N457" s="2" t="inlineStr">
+        <is>
+          <t>palinka-wine@palinkas.sk</t>
+        </is>
+      </c>
+      <c r="O457" s="2" t="inlineStr"/>
+      <c r="P457" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q457" s="2" t="inlineStr">
+        <is>
+          <t>33934363</t>
+        </is>
+      </c>
+      <c r="R457" s="2" t="inlineStr"/>
+      <c r="S457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SzicsekSlovensko</t>
+        </is>
+      </c>
+      <c r="T457" s="2" t="inlineStr"/>
+      <c r="U457" s="2" t="inlineStr"/>
+      <c r="V457" s="2" t="inlineStr"/>
+      <c r="W457" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Pálinkás</t>
+        </is>
+      </c>
+      <c r="X457" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y457" s="2" t="inlineStr"/>
+      <c r="Z457" s="2" t="inlineStr"/>
+      <c r="AA457" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/gabriel-pálinkás-440998a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Sklié, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>La Vie en Rose</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>31686</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava I</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>4 Radlinského</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>811 07</t>
+        </is>
+      </c>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lavieenrose.sk</t>
+        </is>
+      </c>
+      <c r="J458" s="2" t="inlineStr"/>
+      <c r="K458" s="2" t="inlineStr"/>
+      <c r="L458" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M458" s="2" t="inlineStr"/>
+      <c r="N458" s="2" t="inlineStr">
+        <is>
+          <t>info@lavieenrose.sk</t>
+        </is>
+      </c>
+      <c r="O458" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/524 927 42</t>
+        </is>
+      </c>
+      <c r="P458" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q458" s="2" t="inlineStr">
+        <is>
+          <t>35950978</t>
+        </is>
+      </c>
+      <c r="R458" s="2" t="inlineStr"/>
+      <c r="S458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinotekaLaVieenRose/</t>
+        </is>
+      </c>
+      <c r="T458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotekalavieenrose/</t>
+        </is>
+      </c>
+      <c r="U458" s="2" t="inlineStr"/>
+      <c r="V458" s="2" t="inlineStr"/>
+      <c r="W458" s="2" t="inlineStr"/>
+      <c r="X458" s="2" t="inlineStr"/>
+      <c r="Y458" s="2" t="inlineStr"/>
+      <c r="Z458" s="2" t="inlineStr"/>
+      <c r="AA458" s="2" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>Belvet, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>Belvet, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>11913</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>Križovany nad Dudváhom</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj, Trnava</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>Križovany Nad Dudváhom 511</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>919 24</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>https://belvet.sk</t>
+        </is>
+      </c>
+      <c r="J459" s="2" t="inlineStr"/>
+      <c r="K459" s="2" t="inlineStr"/>
+      <c r="L459" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M459" s="2" t="inlineStr"/>
+      <c r="N459" s="2" t="inlineStr">
+        <is>
+          <t>belvet@belvet.sk</t>
+        </is>
+      </c>
+      <c r="O459" s="2" t="inlineStr"/>
+      <c r="P459" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q459" s="2" t="inlineStr">
+        <is>
+          <t>46284699</t>
+        </is>
+      </c>
+      <c r="R459" s="2" t="inlineStr"/>
+      <c r="S459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/belvet.eshop</t>
+        </is>
+      </c>
+      <c r="T459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/belvet.sk.lubos/</t>
+        </is>
+      </c>
+      <c r="U459" s="2" t="inlineStr"/>
+      <c r="V459" s="2" t="inlineStr"/>
+      <c r="W459" s="2" t="inlineStr"/>
+      <c r="X459" s="2" t="inlineStr"/>
+      <c r="Y459" s="2" t="inlineStr"/>
+      <c r="Z459" s="2" t="inlineStr"/>
+      <c r="AA459" s="2" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>Vinocentrum S. R. O.</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>Vinocentrum S. R. O.</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>58758</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>Banska Stiavnica</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr"/>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>Kammerhofská 178/2</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>96901</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>https://vinocentrum.sk</t>
+        </is>
+      </c>
+      <c r="J460" s="2" t="inlineStr"/>
+      <c r="K460" s="2" t="inlineStr"/>
+      <c r="L460" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M460" s="2" t="inlineStr"/>
+      <c r="N460" s="2" t="inlineStr">
+        <is>
+          <t>vinocentrum@gmail.com</t>
+        </is>
+      </c>
+      <c r="O460" s="2" t="inlineStr"/>
+      <c r="P460" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q460" s="2" t="inlineStr">
+        <is>
+          <t>53125967</t>
+        </is>
+      </c>
+      <c r="R460" s="2" t="inlineStr"/>
+      <c r="S460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinocentrum/</t>
+        </is>
+      </c>
+      <c r="T460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinocentrum/</t>
+        </is>
+      </c>
+      <c r="U460" s="2" t="inlineStr"/>
+      <c r="V460" s="2" t="inlineStr"/>
+      <c r="W460" s="2" t="inlineStr">
+        <is>
+          <t>Brano Bahna</t>
+        </is>
+      </c>
+      <c r="X460" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y460" s="2" t="inlineStr"/>
+      <c r="Z460" s="2" t="inlineStr"/>
+      <c r="AA460" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/brano-bahna-a394978b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>58756</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>Trnava Region, Trnava District</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov 464</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>919 22</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoteka-cassalle.sk</t>
+        </is>
+      </c>
+      <c r="J461" s="2" t="inlineStr"/>
+      <c r="K461" s="2" t="inlineStr"/>
+      <c r="L461" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M461" s="2" t="inlineStr"/>
+      <c r="N461" s="2" t="inlineStr">
+        <is>
+          <t>cassalle.vinoteka@gmail.com</t>
+        </is>
+      </c>
+      <c r="O461" s="2" t="inlineStr"/>
+      <c r="P461" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q461" s="2" t="inlineStr">
+        <is>
+          <t>46829679</t>
+        </is>
+      </c>
+      <c r="R461" s="2" t="inlineStr"/>
+      <c r="S461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekacassalletrnava/</t>
+        </is>
+      </c>
+      <c r="T461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cassallevinoteka</t>
+        </is>
+      </c>
+      <c r="U461" s="2" t="inlineStr"/>
+      <c r="V461" s="2" t="inlineStr"/>
+      <c r="W461" s="2" t="inlineStr">
+        <is>
+          <t>Marcel Kuracina</t>
+        </is>
+      </c>
+      <c r="X461" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y461" s="2" t="inlineStr"/>
+      <c r="Z461" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA461" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/marcel-kuracina-0464b9a5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>58756</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Trnava Region, Trnava District</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov 464</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>919 22</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoteka-cassalle.sk</t>
+        </is>
+      </c>
+      <c r="J462" s="2" t="inlineStr"/>
+      <c r="K462" s="2" t="inlineStr"/>
+      <c r="L462" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M462" s="2" t="inlineStr"/>
+      <c r="N462" s="2" t="inlineStr">
+        <is>
+          <t>cassalle.vinoteka@gmail.com</t>
+        </is>
+      </c>
+      <c r="O462" s="2" t="inlineStr"/>
+      <c r="P462" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q462" s="2" t="inlineStr">
+        <is>
+          <t>46829679</t>
+        </is>
+      </c>
+      <c r="R462" s="2" t="inlineStr"/>
+      <c r="S462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekacassalletrnava/</t>
+        </is>
+      </c>
+      <c r="T462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cassallevinoteka</t>
+        </is>
+      </c>
+      <c r="U462" s="2" t="inlineStr"/>
+      <c r="V462" s="2" t="inlineStr"/>
+      <c r="W462" s="2" t="inlineStr">
+        <is>
+          <t>Andrej Kleštinec</t>
+        </is>
+      </c>
+      <c r="X462" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y462" s="2" t="inlineStr"/>
+      <c r="Z462" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA462" s="2" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>Michal Heinz - Obchod S Vínom</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>Michal Heinz - Obchod S Vínom</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>20097</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>97, 41 Horná</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>974 01</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>http://www.somelier.sk</t>
+        </is>
+      </c>
+      <c r="J463" s="2" t="inlineStr"/>
+      <c r="K463" s="2" t="inlineStr"/>
+      <c r="L463" s="2" t="inlineStr"/>
+      <c r="M463" s="2" t="inlineStr"/>
+      <c r="N463" s="2" t="inlineStr">
+        <is>
+          <t>somelier@somelier.sk</t>
+        </is>
+      </c>
+      <c r="O463" s="2" t="inlineStr"/>
+      <c r="P463" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q463" s="2" t="inlineStr">
+        <is>
+          <t>40888789</t>
+        </is>
+      </c>
+      <c r="R463" s="2" t="inlineStr"/>
+      <c r="S463" s="2" t="inlineStr"/>
+      <c r="T463" s="2" t="inlineStr"/>
+      <c r="U463" s="2" t="inlineStr"/>
+      <c r="V463" s="2" t="inlineStr"/>
+      <c r="W463" s="2" t="inlineStr"/>
+      <c r="X463" s="2" t="inlineStr"/>
+      <c r="Y463" s="2" t="inlineStr"/>
+      <c r="Z463" s="2" t="inlineStr"/>
+      <c r="AA463" s="2" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>54060</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr"/>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavská 923 (INDUSTRIAL PARK)</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>https://pima.sk</t>
+        </is>
+      </c>
+      <c r="J464" s="2" t="inlineStr"/>
+      <c r="K464" s="2" t="inlineStr"/>
+      <c r="L464" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M464" s="2" t="inlineStr"/>
+      <c r="N464" s="2" t="inlineStr">
+        <is>
+          <t>obchod@pima.sk</t>
+        </is>
+      </c>
+      <c r="O464" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/743 09 11</t>
+        </is>
+      </c>
+      <c r="P464" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q464" s="2" t="inlineStr">
+        <is>
+          <t>36350036</t>
+        </is>
+      </c>
+      <c r="R464" s="2" t="inlineStr"/>
+      <c r="S464" s="2" t="inlineStr"/>
+      <c r="T464" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pima.sk</t>
+        </is>
+      </c>
+      <c r="U464" s="2" t="inlineStr"/>
+      <c r="V464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC4phGWgVZeTSxNP3V23gzgQ</t>
+        </is>
+      </c>
+      <c r="W464" s="2" t="inlineStr">
+        <is>
+          <t>Rudolf Ďatko</t>
+        </is>
+      </c>
+      <c r="X464" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Managing Director </t>
+        </is>
+      </c>
+      <c r="Y464" s="2" t="inlineStr"/>
+      <c r="Z464" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA464" s="2" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>54060</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr"/>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavská 923 (INDUSTRIAL PARK)</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>https://pima.sk</t>
+        </is>
+      </c>
+      <c r="J465" s="2" t="inlineStr"/>
+      <c r="K465" s="2" t="inlineStr"/>
+      <c r="L465" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M465" s="2" t="inlineStr"/>
+      <c r="N465" s="2" t="inlineStr">
+        <is>
+          <t>obchod@pima.sk</t>
+        </is>
+      </c>
+      <c r="O465" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/743 09 11</t>
+        </is>
+      </c>
+      <c r="P465" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q465" s="2" t="inlineStr">
+        <is>
+          <t>36350036</t>
+        </is>
+      </c>
+      <c r="R465" s="2" t="inlineStr"/>
+      <c r="S465" s="2" t="inlineStr"/>
+      <c r="T465" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pima.sk</t>
+        </is>
+      </c>
+      <c r="U465" s="2" t="inlineStr"/>
+      <c r="V465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC4phGWgVZeTSxNP3V23gzgQ</t>
+        </is>
+      </c>
+      <c r="W465" s="2" t="inlineStr">
+        <is>
+          <t>Martin Kotrha</t>
+        </is>
+      </c>
+      <c r="X465" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales Director </t>
+        </is>
+      </c>
+      <c r="Y465" s="2" t="inlineStr"/>
+      <c r="Z465" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA465" s="2" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>11882</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>49 Vlárska</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>https://akevino.sk</t>
+        </is>
+      </c>
+      <c r="J466" s="2" t="inlineStr"/>
+      <c r="K466" s="2" t="inlineStr"/>
+      <c r="L466" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M466" s="2" t="inlineStr"/>
+      <c r="N466" s="2" t="inlineStr">
+        <is>
+          <t>obchod@akevino.sk</t>
+        </is>
+      </c>
+      <c r="O466" s="2" t="inlineStr"/>
+      <c r="P466" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q466" s="2" t="inlineStr">
+        <is>
+          <t>45704163</t>
+        </is>
+      </c>
+      <c r="R466" s="2" t="inlineStr"/>
+      <c r="S466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/akevino.sk/</t>
+        </is>
+      </c>
+      <c r="T466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/akevinosk</t>
+        </is>
+      </c>
+      <c r="U466" s="2" t="inlineStr"/>
+      <c r="V466" s="2" t="inlineStr"/>
+      <c r="W466" s="2" t="inlineStr">
+        <is>
+          <t>Matej Poláčik</t>
+        </is>
+      </c>
+      <c r="X466" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y466" s="2" t="inlineStr"/>
+      <c r="Z466" s="2" t="inlineStr"/>
+      <c r="AA466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/matej-pol%C3%A1%C4%8Dik-8b519519b</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>11882</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>49 Vlárska</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>https://akevino.sk</t>
+        </is>
+      </c>
+      <c r="J467" s="2" t="inlineStr"/>
+      <c r="K467" s="2" t="inlineStr"/>
+      <c r="L467" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M467" s="2" t="inlineStr"/>
+      <c r="N467" s="2" t="inlineStr">
+        <is>
+          <t>obchod@akevino.sk</t>
+        </is>
+      </c>
+      <c r="O467" s="2" t="inlineStr"/>
+      <c r="P467" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q467" s="2" t="inlineStr">
+        <is>
+          <t>45704163</t>
+        </is>
+      </c>
+      <c r="R467" s="2" t="inlineStr"/>
+      <c r="S467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/akevino.sk/</t>
+        </is>
+      </c>
+      <c r="T467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/akevinosk</t>
+        </is>
+      </c>
+      <c r="U467" s="2" t="inlineStr"/>
+      <c r="V467" s="2" t="inlineStr"/>
+      <c r="W467" s="2" t="inlineStr">
+        <is>
+          <t>Juraj Drozd</t>
+        </is>
+      </c>
+      <c r="X467" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y467" s="2" t="inlineStr"/>
+      <c r="Z467" s="2" t="inlineStr"/>
+      <c r="AA467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/juraj-drozd-8ab51a19a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>Ing. Anton Minčík - Amicomp</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>Ing. Anton Minčík - Amicomp</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>53942</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>Košice</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj, Košice IV</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>7 Omská</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>040 01</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amicomp1.sk</t>
+        </is>
+      </c>
+      <c r="J468" s="2" t="inlineStr"/>
+      <c r="K468" s="2" t="inlineStr"/>
+      <c r="L468" s="2" t="inlineStr"/>
+      <c r="M468" s="2" t="inlineStr"/>
+      <c r="N468" s="2" t="inlineStr">
+        <is>
+          <t>amicomp1@amicomp1.sk</t>
+        </is>
+      </c>
+      <c r="O468" s="2" t="inlineStr"/>
+      <c r="P468" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q468" s="2" t="inlineStr">
+        <is>
+          <t>30673275</t>
+        </is>
+      </c>
+      <c r="R468" s="2" t="inlineStr"/>
+      <c r="S468" s="2" t="inlineStr"/>
+      <c r="T468" s="2" t="inlineStr"/>
+      <c r="U468" s="2" t="inlineStr"/>
+      <c r="V468" s="2" t="inlineStr"/>
+      <c r="W468" s="2" t="inlineStr">
+        <is>
+          <t>Anton Minčík</t>
+        </is>
+      </c>
+      <c r="X468" s="2" t="inlineStr">
+        <is>
+          <t>Owner - Manager</t>
+        </is>
+      </c>
+      <c r="Y468" s="2" t="inlineStr"/>
+      <c r="Z468" s="2" t="inlineStr"/>
+      <c r="AA468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anton-mincik-43b691101/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>Vk Suma Sro</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>Vk Suma Sro</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>53809</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>Veľký Krtíš</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>27 Osloboditeľov</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>990 01</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vksuma.sk</t>
+        </is>
+      </c>
+      <c r="J469" s="2" t="inlineStr"/>
+      <c r="K469" s="2" t="inlineStr"/>
+      <c r="L469" s="2" t="inlineStr"/>
+      <c r="M469" s="2" t="inlineStr"/>
+      <c r="N469" s="2" t="inlineStr">
+        <is>
+          <t>karolszuma@gmail.com</t>
+        </is>
+      </c>
+      <c r="O469" s="2" t="inlineStr">
+        <is>
+          <t>+421 47 483 11 00</t>
+        </is>
+      </c>
+      <c r="P469" s="2" t="inlineStr"/>
+      <c r="Q469" s="2" t="inlineStr"/>
+      <c r="R469" s="2" t="inlineStr"/>
+      <c r="S469" s="2" t="inlineStr"/>
+      <c r="T469" s="2" t="inlineStr"/>
+      <c r="U469" s="2" t="inlineStr"/>
+      <c r="V469" s="2" t="inlineStr"/>
+      <c r="W469" s="2" t="inlineStr"/>
+      <c r="X469" s="2" t="inlineStr"/>
+      <c r="Y469" s="2" t="inlineStr"/>
+      <c r="Z469" s="2" t="inlineStr"/>
+      <c r="AA469" s="2" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj IV</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>28a Jána Stanislava</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>841 05</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koft.sk</t>
+        </is>
+      </c>
+      <c r="J470" s="2" t="inlineStr"/>
+      <c r="K470" s="2" t="inlineStr"/>
+      <c r="L470" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M470" s="2" t="inlineStr"/>
+      <c r="N470" s="2" t="inlineStr">
+        <is>
+          <t>infokoft@koft.sk</t>
+        </is>
+      </c>
+      <c r="O470" s="2" t="inlineStr">
+        <is>
+          <t>+421 2 502 052 00</t>
+        </is>
+      </c>
+      <c r="P470" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q470" s="2" t="inlineStr">
+        <is>
+          <t>17335248</t>
+        </is>
+      </c>
+      <c r="R470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/koft-s-r-o/</t>
+        </is>
+      </c>
+      <c r="S470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/otazkavoflasi</t>
+        </is>
+      </c>
+      <c r="T470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/koft.sk</t>
+        </is>
+      </c>
+      <c r="U470" s="2" t="inlineStr"/>
+      <c r="V470" s="2" t="inlineStr"/>
+      <c r="W470" s="2" t="inlineStr">
+        <is>
+          <t>Branislav Machovič</t>
+        </is>
+      </c>
+      <c r="X470" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y470" s="2" t="inlineStr"/>
+      <c r="Z470" s="2" t="inlineStr"/>
+      <c r="AA470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/branislav-machovič-53a57085</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj IV</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>28a Jána Stanislava</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>841 05</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koft.sk</t>
+        </is>
+      </c>
+      <c r="J471" s="2" t="inlineStr"/>
+      <c r="K471" s="2" t="inlineStr"/>
+      <c r="L471" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M471" s="2" t="inlineStr"/>
+      <c r="N471" s="2" t="inlineStr">
+        <is>
+          <t>infokoft@koft.sk</t>
+        </is>
+      </c>
+      <c r="O471" s="2" t="inlineStr">
+        <is>
+          <t>+421 2 502 052 00</t>
+        </is>
+      </c>
+      <c r="P471" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q471" s="2" t="inlineStr">
+        <is>
+          <t>17335248</t>
+        </is>
+      </c>
+      <c r="R471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/koft-s-r-o/</t>
+        </is>
+      </c>
+      <c r="S471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/otazkavoflasi</t>
+        </is>
+      </c>
+      <c r="T471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/koft.sk</t>
+        </is>
+      </c>
+      <c r="U471" s="2" t="inlineStr"/>
+      <c r="V471" s="2" t="inlineStr"/>
+      <c r="W471" s="2" t="inlineStr">
+        <is>
+          <t>Martin Lešo</t>
+        </is>
+      </c>
+      <c r="X471" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y471" s="2" t="inlineStr"/>
+      <c r="Z471" s="2" t="inlineStr"/>
+      <c r="AA471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martin-le%C5%A1o-8536aa34/?originalSubdomain=sk</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>Valsesia, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>Valsesia, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>11929</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>Budča</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj, Zvolen</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>10 Stromová</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>962 33</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vino-obchod.sk</t>
+        </is>
+      </c>
+      <c r="J472" s="2" t="inlineStr"/>
+      <c r="K472" s="2" t="inlineStr"/>
+      <c r="L472" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M472" s="2" t="inlineStr"/>
+      <c r="N472" s="2" t="inlineStr">
+        <is>
+          <t>info@vino-obchod.sk</t>
+        </is>
+      </c>
+      <c r="O472" s="2" t="inlineStr"/>
+      <c r="P472" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q472" s="2" t="inlineStr">
+        <is>
+          <t>36626031</t>
+        </is>
+      </c>
+      <c r="R472" s="2" t="inlineStr"/>
+      <c r="S472" s="2" t="inlineStr"/>
+      <c r="T472" s="2" t="inlineStr"/>
+      <c r="U472" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Valsesiasro</t>
+        </is>
+      </c>
+      <c r="V472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCAnww4K_EunrRxjdBi6EfvQ</t>
+        </is>
+      </c>
+      <c r="W472" s="2" t="inlineStr">
+        <is>
+          <t>Róbert Mráz</t>
+        </is>
+      </c>
+      <c r="X472" s="2" t="inlineStr">
+        <is>
+          <t>Executive Manager</t>
+        </is>
+      </c>
+      <c r="Y472" s="2" t="inlineStr"/>
+      <c r="Z472" s="2" t="inlineStr"/>
+      <c r="AA472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/r%C3%B3bert-mr%C3%A1z-718436153/</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>Diskonto S.r.o.</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>Diskonto S.r.o.</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>54205</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>Spišská Nová Ves</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>17 Radlinského</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>052 01</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.diskonto.sk</t>
+        </is>
+      </c>
+      <c r="J473" s="2" t="inlineStr"/>
+      <c r="K473" s="2" t="inlineStr"/>
+      <c r="L473" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M473" s="2" t="inlineStr"/>
+      <c r="N473" s="2" t="inlineStr">
+        <is>
+          <t>diskonto@diskonto.sk</t>
+        </is>
+      </c>
+      <c r="O473" s="2" t="inlineStr"/>
+      <c r="P473" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q473" s="2" t="inlineStr">
+        <is>
+          <t>44541473</t>
+        </is>
+      </c>
+      <c r="R473" s="2" t="inlineStr"/>
+      <c r="S473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/diskontoSK/</t>
+        </is>
+      </c>
+      <c r="T473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diskonto_sk/</t>
+        </is>
+      </c>
+      <c r="U473" s="2" t="inlineStr"/>
+      <c r="V473" s="2" t="inlineStr"/>
+      <c r="W473" s="2" t="inlineStr"/>
+      <c r="X473" s="2" t="inlineStr"/>
+      <c r="Y473" s="2" t="inlineStr"/>
+      <c r="Z473" s="2" t="inlineStr"/>
+      <c r="AA473" s="2" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>Vino Sardo S. R. O.</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>Vino Sardo S. R. O.</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>20247</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>Myjava</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>524/19 Nám. M. R. Štefánika</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>907 01</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>https://vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="J474" s="2" t="inlineStr"/>
+      <c r="K474" s="2" t="inlineStr"/>
+      <c r="L474" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M474" s="2" t="inlineStr"/>
+      <c r="N474" s="2" t="inlineStr">
+        <is>
+          <t>info@vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="O474" s="2" t="inlineStr">
+        <is>
+          <t>+421 34/653 81 85</t>
+        </is>
+      </c>
+      <c r="P474" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q474" s="2" t="inlineStr">
+        <is>
+          <t>46833625</t>
+        </is>
+      </c>
+      <c r="R474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vino-sardo</t>
+        </is>
+      </c>
+      <c r="S474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="T474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinosardo</t>
+        </is>
+      </c>
+      <c r="U474" s="2" t="inlineStr"/>
+      <c r="V474" s="2" t="inlineStr"/>
+      <c r="W474" s="2" t="inlineStr">
+        <is>
+          <t>Veronika Lhotska</t>
+        </is>
+      </c>
+      <c r="X474" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y474" s="2" t="inlineStr"/>
+      <c r="Z474" s="2" t="inlineStr"/>
+      <c r="AA474" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/veronika-lhotska-00808511a</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>Fine Wines S.r.o.</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>Fine Wines S.r.o.</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>11880</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>Staré Grunty 7A</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>841 04</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.finewines.sk</t>
+        </is>
+      </c>
+      <c r="J475" s="2" t="inlineStr"/>
+      <c r="K475" s="2" t="inlineStr"/>
+      <c r="L475" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M475" s="2" t="inlineStr"/>
+      <c r="N475" s="2" t="inlineStr">
+        <is>
+          <t>office@finewines.sk</t>
+        </is>
+      </c>
+      <c r="O475" s="2" t="inlineStr"/>
+      <c r="P475" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q475" s="2" t="inlineStr">
+        <is>
+          <t>35752173</t>
+        </is>
+      </c>
+      <c r="R475" s="2" t="inlineStr"/>
+      <c r="S475" s="2" t="inlineStr"/>
+      <c r="T475" s="2" t="inlineStr"/>
+      <c r="U475" s="2" t="inlineStr"/>
+      <c r="V475" s="2" t="inlineStr"/>
+      <c r="W475" s="2" t="inlineStr"/>
+      <c r="X475" s="2" t="inlineStr"/>
+      <c r="Y475" s="2" t="inlineStr"/>
+      <c r="Z475" s="2" t="inlineStr"/>
+      <c r="AA475" s="2" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>Cromatop, S.r.o</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>Cromatop, S.r.o</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>54109</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>Hôrka nad Váhom</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj, Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>Hôrka Nad Váhom 1</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>916 32</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>https://croma.sk, https://www.flaskomat.sk</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="inlineStr"/>
+      <c r="K476" s="2" t="inlineStr"/>
+      <c r="L476" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M476" s="2" t="inlineStr"/>
+      <c r="N476" s="2" t="inlineStr">
+        <is>
+          <t>croma@croma.sk</t>
+        </is>
+      </c>
+      <c r="O476" s="2" t="inlineStr"/>
+      <c r="P476" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q476" s="2" t="inlineStr">
+        <is>
+          <t>36338893</t>
+        </is>
+      </c>
+      <c r="R476" s="2" t="inlineStr"/>
+      <c r="S476" s="2" t="inlineStr"/>
+      <c r="T476" s="2" t="inlineStr"/>
+      <c r="U476" s="2" t="inlineStr"/>
+      <c r="V476" s="2" t="inlineStr"/>
+      <c r="W476" s="2" t="inlineStr">
+        <is>
+          <t>Miloslav Králik</t>
+        </is>
+      </c>
+      <c r="X476" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y476" s="2" t="inlineStr"/>
+      <c r="Z476" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA476" s="2" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>Gourmand Sk S. R. O.</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>Gourmand Sk S. R. O.</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>11918</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>12573, 50E Tomášikova</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>https://vinopolis.sk</t>
+        </is>
+      </c>
+      <c r="J477" s="2" t="inlineStr"/>
+      <c r="K477" s="2" t="inlineStr"/>
+      <c r="L477" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M477" s="2" t="inlineStr"/>
+      <c r="N477" s="2" t="inlineStr">
+        <is>
+          <t>info@vinopolis.sk</t>
+        </is>
+      </c>
+      <c r="O477" s="2" t="inlineStr"/>
+      <c r="P477" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q477" s="2" t="inlineStr">
+        <is>
+          <t>46005188</t>
+        </is>
+      </c>
+      <c r="R477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinopolis-sk/</t>
+        </is>
+      </c>
+      <c r="S477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinopolis.sk/</t>
+        </is>
+      </c>
+      <c r="T477" s="2" t="inlineStr"/>
+      <c r="U477" s="2" t="inlineStr"/>
+      <c r="V477" s="2" t="inlineStr"/>
+      <c r="W477" s="2" t="inlineStr">
+        <is>
+          <t>Tibor Körmendi</t>
+        </is>
+      </c>
+      <c r="X477" s="2" t="inlineStr">
+        <is>
+          <t>Responsible</t>
+        </is>
+      </c>
+      <c r="Y477" s="2" t="inlineStr"/>
+      <c r="Z477" s="2" t="inlineStr"/>
+      <c r="AA477" s="2" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>Ll Wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>Ll Wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>42564</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj V</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>7 Bosákova</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>851 04</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.llwine.sk</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr"/>
+      <c r="K478" s="2" t="inlineStr"/>
+      <c r="L478" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M478" s="2" t="inlineStr"/>
+      <c r="N478" s="2" t="inlineStr">
+        <is>
+          <t>lipka@llwine.sk</t>
+        </is>
+      </c>
+      <c r="O478" s="2" t="inlineStr"/>
+      <c r="P478" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q478" s="2" t="inlineStr">
+        <is>
+          <t>45895813</t>
+        </is>
+      </c>
+      <c r="R478" s="2" t="inlineStr"/>
+      <c r="S478" s="2" t="inlineStr"/>
+      <c r="T478" s="2" t="inlineStr"/>
+      <c r="U478" s="2" t="inlineStr"/>
+      <c r="V478" s="2" t="inlineStr"/>
+      <c r="W478" s="2" t="inlineStr"/>
+      <c r="X478" s="2" t="inlineStr"/>
+      <c r="Y478" s="2" t="inlineStr"/>
+      <c r="Z478" s="2" t="inlineStr"/>
+      <c r="AA478" s="2" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>Barbara Mincíková - Vinopolitan</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Vinopolitan</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>32100</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj I</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>6 Námestie SNP</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>811 06</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinopolitan.sk</t>
+        </is>
+      </c>
+      <c r="J479" s="2" t="inlineStr"/>
+      <c r="K479" s="2" t="inlineStr"/>
+      <c r="L479" s="2" t="inlineStr"/>
+      <c r="M479" s="2" t="inlineStr"/>
+      <c r="N479" s="2" t="inlineStr">
+        <is>
+          <t>info@vinopolitan.sk</t>
+        </is>
+      </c>
+      <c r="O479" s="2" t="inlineStr"/>
+      <c r="P479" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q479" s="2" t="inlineStr">
+        <is>
+          <t>47657235</t>
+        </is>
+      </c>
+      <c r="R479" s="2" t="inlineStr"/>
+      <c r="S479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinopolitanbratislava/</t>
+        </is>
+      </c>
+      <c r="T479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinopolitan_wineshop/</t>
+        </is>
+      </c>
+      <c r="U479" s="2" t="inlineStr"/>
+      <c r="V479" s="2" t="inlineStr"/>
+      <c r="W479" s="2" t="inlineStr"/>
+      <c r="X479" s="2" t="inlineStr"/>
+      <c r="Y479" s="2" t="inlineStr"/>
+      <c r="Z479" s="2" t="inlineStr"/>
+      <c r="AA479" s="2" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J480" s="2" t="inlineStr"/>
+      <c r="K480" s="2" t="inlineStr"/>
+      <c r="L480" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M480" s="2" t="inlineStr"/>
+      <c r="N480" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O480" s="2" t="inlineStr"/>
+      <c r="P480" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q480" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R480" s="2" t="inlineStr"/>
+      <c r="S480" s="2" t="inlineStr"/>
+      <c r="T480" s="2" t="inlineStr"/>
+      <c r="U480" s="2" t="inlineStr"/>
+      <c r="V480" s="2" t="inlineStr"/>
+      <c r="W480" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Vrska</t>
+        </is>
+      </c>
+      <c r="X480" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y480" s="2" t="inlineStr"/>
+      <c r="Z480" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA480" s="2" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J481" s="2" t="inlineStr"/>
+      <c r="K481" s="2" t="inlineStr"/>
+      <c r="L481" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M481" s="2" t="inlineStr"/>
+      <c r="N481" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O481" s="2" t="inlineStr"/>
+      <c r="P481" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q481" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R481" s="2" t="inlineStr"/>
+      <c r="S481" s="2" t="inlineStr"/>
+      <c r="T481" s="2" t="inlineStr"/>
+      <c r="U481" s="2" t="inlineStr"/>
+      <c r="V481" s="2" t="inlineStr"/>
+      <c r="W481" s="2" t="inlineStr">
+        <is>
+          <t>Štefan Ondrúš</t>
+        </is>
+      </c>
+      <c r="X481" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y481" s="2" t="inlineStr"/>
+      <c r="Z481" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA481" s="2" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I482" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J482" s="2" t="inlineStr"/>
+      <c r="K482" s="2" t="inlineStr"/>
+      <c r="L482" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M482" s="2" t="inlineStr"/>
+      <c r="N482" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O482" s="2" t="inlineStr"/>
+      <c r="P482" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q482" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R482" s="2" t="inlineStr"/>
+      <c r="S482" s="2" t="inlineStr"/>
+      <c r="T482" s="2" t="inlineStr"/>
+      <c r="U482" s="2" t="inlineStr"/>
+      <c r="V482" s="2" t="inlineStr"/>
+      <c r="W482" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Bošanský</t>
+        </is>
+      </c>
+      <c r="X482" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y482" s="2" t="inlineStr"/>
+      <c r="Z482" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA482" s="2" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="inlineStr"/>
+      <c r="K483" s="2" t="inlineStr"/>
+      <c r="L483" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M483" s="2" t="inlineStr"/>
+      <c r="N483" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O483" s="2" t="inlineStr"/>
+      <c r="P483" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q483" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R483" s="2" t="inlineStr"/>
+      <c r="S483" s="2" t="inlineStr"/>
+      <c r="T483" s="2" t="inlineStr"/>
+      <c r="U483" s="2" t="inlineStr"/>
+      <c r="V483" s="2" t="inlineStr"/>
+      <c r="W483" s="2" t="inlineStr">
+        <is>
+          <t>Pavol Pavlus</t>
+        </is>
+      </c>
+      <c r="X483" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y483" s="2" t="inlineStr"/>
+      <c r="Z483" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA483" s="2" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J484" s="2" t="inlineStr"/>
+      <c r="K484" s="2" t="inlineStr"/>
+      <c r="L484" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M484" s="2" t="inlineStr"/>
+      <c r="N484" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O484" s="2" t="inlineStr"/>
+      <c r="P484" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q484" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R484" s="2" t="inlineStr"/>
+      <c r="S484" s="2" t="inlineStr"/>
+      <c r="T484" s="2" t="inlineStr"/>
+      <c r="U484" s="2" t="inlineStr"/>
+      <c r="V484" s="2" t="inlineStr"/>
+      <c r="W484" s="2" t="inlineStr">
+        <is>
+          <t>Martin Cehula</t>
+        </is>
+      </c>
+      <c r="X484" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y484" s="2" t="inlineStr"/>
+      <c r="Z484" s="2" t="inlineStr"/>
+      <c r="AA484" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA484"/>
+  <dimension ref="A1:AA547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -48693,6 +48693,5773 @@
       <c r="Z484" s="2" t="inlineStr"/>
       <c r="AA484" s="2" t="inlineStr"/>
     </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>Víno Az, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>Víno Az, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>21731</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>1069, 4 Pivovarská</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>010 01</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoaz.sk</t>
+        </is>
+      </c>
+      <c r="J485" s="2" t="inlineStr"/>
+      <c r="K485" s="2" t="inlineStr"/>
+      <c r="L485" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M485" s="2" t="inlineStr"/>
+      <c r="N485" s="2" t="inlineStr">
+        <is>
+          <t>vanko@vinoaz.sk</t>
+        </is>
+      </c>
+      <c r="O485" s="2" t="inlineStr"/>
+      <c r="P485" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q485" s="2" t="inlineStr">
+        <is>
+          <t>44009275</t>
+        </is>
+      </c>
+      <c r="R485" s="2" t="inlineStr"/>
+      <c r="S485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Víno-AZ-sro-452044938181291</t>
+        </is>
+      </c>
+      <c r="T485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoaz_s.r.o/</t>
+        </is>
+      </c>
+      <c r="U485" s="2" t="inlineStr"/>
+      <c r="V485" s="2" t="inlineStr"/>
+      <c r="W485" s="2" t="inlineStr"/>
+      <c r="X485" s="2" t="inlineStr"/>
+      <c r="Y485" s="2" t="inlineStr"/>
+      <c r="Z485" s="2" t="inlineStr"/>
+      <c r="AA485" s="2" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>Bodnar Vino Olio Ecoproducts</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>Bodnar Vino Olio Ecoproducts</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>43488</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>Kosice</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>Kosický</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>Lesná 25</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>040 01</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr">
+        <is>
+          <t>http://ekoprodukty.sk</t>
+        </is>
+      </c>
+      <c r="J486" s="2" t="inlineStr"/>
+      <c r="K486" s="2" t="inlineStr"/>
+      <c r="L486" s="2" t="inlineStr"/>
+      <c r="M486" s="2" t="inlineStr"/>
+      <c r="N486" s="2" t="inlineStr">
+        <is>
+          <t>mail@ekoprodukty.sk</t>
+        </is>
+      </c>
+      <c r="O486" s="2" t="inlineStr"/>
+      <c r="P486" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q486" s="2" t="inlineStr">
+        <is>
+          <t>17159440</t>
+        </is>
+      </c>
+      <c r="R486" s="2" t="inlineStr"/>
+      <c r="S486" s="2" t="inlineStr"/>
+      <c r="T486" s="2" t="inlineStr"/>
+      <c r="U486" s="2" t="inlineStr"/>
+      <c r="V486" s="2" t="inlineStr"/>
+      <c r="W486" s="2" t="inlineStr"/>
+      <c r="X486" s="2" t="inlineStr"/>
+      <c r="Y486" s="2" t="inlineStr"/>
+      <c r="Z486" s="2" t="inlineStr"/>
+      <c r="AA486" s="2" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>Caste Sk, A. S.</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>Caste Sk, A. S.</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>54751</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>Juh</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj, Košice IV</t>
+        </is>
+      </c>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>1 Jazerná</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>040 12</t>
+        </is>
+      </c>
+      <c r="I487" s="2" t="inlineStr">
+        <is>
+          <t>https://caste.sk</t>
+        </is>
+      </c>
+      <c r="J487" s="2" t="inlineStr"/>
+      <c r="K487" s="2" t="inlineStr"/>
+      <c r="L487" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M487" s="2" t="inlineStr"/>
+      <c r="N487" s="2" t="inlineStr">
+        <is>
+          <t>libiak@caste.sk</t>
+        </is>
+      </c>
+      <c r="O487" s="2" t="inlineStr"/>
+      <c r="P487" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q487" s="2" t="inlineStr">
+        <is>
+          <t>52292568</t>
+        </is>
+      </c>
+      <c r="R487" s="2" t="inlineStr"/>
+      <c r="S487" s="2" t="inlineStr"/>
+      <c r="T487" s="2" t="inlineStr"/>
+      <c r="U487" s="2" t="inlineStr"/>
+      <c r="V487" s="2" t="inlineStr"/>
+      <c r="W487" s="2" t="inlineStr">
+        <is>
+          <t>Cakoci Stefan</t>
+        </is>
+      </c>
+      <c r="X487" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y487" s="2" t="inlineStr"/>
+      <c r="Z487" s="2" t="inlineStr"/>
+      <c r="AA487" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cakoci-stefan-0000ba170/</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>Caste Sk, A. S.</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>Caste Sk, A. S.</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>54751</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>Juh</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj, Košice IV</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>1 Jazerná</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>040 12</t>
+        </is>
+      </c>
+      <c r="I488" s="2" t="inlineStr">
+        <is>
+          <t>https://caste.sk</t>
+        </is>
+      </c>
+      <c r="J488" s="2" t="inlineStr"/>
+      <c r="K488" s="2" t="inlineStr"/>
+      <c r="L488" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M488" s="2" t="inlineStr"/>
+      <c r="N488" s="2" t="inlineStr">
+        <is>
+          <t>libiak@caste.sk</t>
+        </is>
+      </c>
+      <c r="O488" s="2" t="inlineStr"/>
+      <c r="P488" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q488" s="2" t="inlineStr">
+        <is>
+          <t>52292568</t>
+        </is>
+      </c>
+      <c r="R488" s="2" t="inlineStr"/>
+      <c r="S488" s="2" t="inlineStr"/>
+      <c r="T488" s="2" t="inlineStr"/>
+      <c r="U488" s="2" t="inlineStr"/>
+      <c r="V488" s="2" t="inlineStr"/>
+      <c r="W488" s="2" t="inlineStr">
+        <is>
+          <t>Rastislav Libiak</t>
+        </is>
+      </c>
+      <c r="X488" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y488" s="2" t="inlineStr"/>
+      <c r="Z488" s="2" t="inlineStr"/>
+      <c r="AA488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rastislav-libiak-15371a96/</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>Tip Top Gastro S.r.o</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>Tip Top Gastro S.r.o</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>108850</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>Biely Kostol</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj, Trnava</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>5458, 1 Pionierske námestie</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>919 34</t>
+        </is>
+      </c>
+      <c r="I489" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiptopgastro.sk</t>
+        </is>
+      </c>
+      <c r="J489" s="2" t="inlineStr"/>
+      <c r="K489" s="2" t="inlineStr"/>
+      <c r="L489" s="2" t="inlineStr"/>
+      <c r="M489" s="2" t="inlineStr"/>
+      <c r="N489" s="2" t="inlineStr">
+        <is>
+          <t>objednavky@tiptopgastro.sk</t>
+        </is>
+      </c>
+      <c r="O489" s="2" t="inlineStr">
+        <is>
+          <t>+421 33 533 33 35</t>
+        </is>
+      </c>
+      <c r="P489" s="2" t="inlineStr"/>
+      <c r="Q489" s="2" t="inlineStr"/>
+      <c r="R489" s="2" t="inlineStr"/>
+      <c r="S489" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TipTopGastro/</t>
+        </is>
+      </c>
+      <c r="T489" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tiptopgastro</t>
+        </is>
+      </c>
+      <c r="U489" s="2" t="inlineStr"/>
+      <c r="V489" s="2" t="inlineStr"/>
+      <c r="W489" s="2" t="inlineStr"/>
+      <c r="X489" s="2" t="inlineStr"/>
+      <c r="Y489" s="2" t="inlineStr"/>
+      <c r="Z489" s="2" t="inlineStr"/>
+      <c r="AA489" s="2" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>Augera S.r.o.</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>Augera S.r.o.</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>56911</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>Modra</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Pezinok</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>Harmónia 3590</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>900 01</t>
+        </is>
+      </c>
+      <c r="I490" s="2" t="inlineStr">
+        <is>
+          <t>http://vino-augera.sk</t>
+        </is>
+      </c>
+      <c r="J490" s="2" t="inlineStr"/>
+      <c r="K490" s="2" t="inlineStr"/>
+      <c r="L490" s="2" t="inlineStr"/>
+      <c r="M490" s="2" t="inlineStr"/>
+      <c r="N490" s="2" t="inlineStr">
+        <is>
+          <t>augera@augera.sk</t>
+        </is>
+      </c>
+      <c r="O490" s="2" t="inlineStr"/>
+      <c r="P490" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q490" s="2" t="inlineStr">
+        <is>
+          <t>35895578</t>
+        </is>
+      </c>
+      <c r="R490" s="2" t="inlineStr"/>
+      <c r="S490" s="2" t="inlineStr"/>
+      <c r="T490" s="2" t="inlineStr"/>
+      <c r="U490" s="2" t="inlineStr"/>
+      <c r="V490" s="2" t="inlineStr"/>
+      <c r="W490" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Werchol</t>
+        </is>
+      </c>
+      <c r="X490" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y490" s="2" t="inlineStr"/>
+      <c r="Z490" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/k-miroslav-werchol-aacute-8529ba40</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>Augera S.r.o.</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>Augera S.r.o.</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>56911</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>Modra</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Pezinok</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>Harmónia 3590</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>900 01</t>
+        </is>
+      </c>
+      <c r="I491" s="2" t="inlineStr">
+        <is>
+          <t>http://vino-augera.sk</t>
+        </is>
+      </c>
+      <c r="J491" s="2" t="inlineStr"/>
+      <c r="K491" s="2" t="inlineStr"/>
+      <c r="L491" s="2" t="inlineStr"/>
+      <c r="M491" s="2" t="inlineStr"/>
+      <c r="N491" s="2" t="inlineStr">
+        <is>
+          <t>augera@augera.sk</t>
+        </is>
+      </c>
+      <c r="O491" s="2" t="inlineStr"/>
+      <c r="P491" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q491" s="2" t="inlineStr">
+        <is>
+          <t>35895578</t>
+        </is>
+      </c>
+      <c r="R491" s="2" t="inlineStr"/>
+      <c r="S491" s="2" t="inlineStr"/>
+      <c r="T491" s="2" t="inlineStr"/>
+      <c r="U491" s="2" t="inlineStr"/>
+      <c r="V491" s="2" t="inlineStr"/>
+      <c r="W491" s="2" t="inlineStr">
+        <is>
+          <t>Gabriela Wercholáková</t>
+        </is>
+      </c>
+      <c r="X491" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y491" s="2" t="inlineStr"/>
+      <c r="Z491" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA491" s="2" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>Grandi Vini, S. R. O.</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>Grandi Vini, S. R. O.</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>36311</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>16 Škultétyho</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>831 03</t>
+        </is>
+      </c>
+      <c r="I492" s="2" t="inlineStr">
+        <is>
+          <t>https://grandivini.eu</t>
+        </is>
+      </c>
+      <c r="J492" s="2" t="inlineStr"/>
+      <c r="K492" s="2" t="inlineStr"/>
+      <c r="L492" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M492" s="2" t="inlineStr"/>
+      <c r="N492" s="2" t="inlineStr">
+        <is>
+          <t>grandivini1@gmail.com</t>
+        </is>
+      </c>
+      <c r="O492" s="2" t="inlineStr"/>
+      <c r="P492" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q492" s="2" t="inlineStr">
+        <is>
+          <t>36779610</t>
+        </is>
+      </c>
+      <c r="R492" s="2" t="inlineStr"/>
+      <c r="S492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/grandivini.eu/</t>
+        </is>
+      </c>
+      <c r="T492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grandivini_eu/</t>
+        </is>
+      </c>
+      <c r="U492" s="2" t="inlineStr"/>
+      <c r="V492" s="2" t="inlineStr"/>
+      <c r="W492" s="2" t="inlineStr">
+        <is>
+          <t>Alex Pothe</t>
+        </is>
+      </c>
+      <c r="X492" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y492" s="2" t="inlineStr"/>
+      <c r="Z492" s="2" t="inlineStr"/>
+      <c r="AA492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alex-pothe-396620179/?originalSubdomain=sk</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>Bottleshop Sk, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>Bottleshop Sk, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>20064</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj I</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>2 Tallerova</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>811 02</t>
+        </is>
+      </c>
+      <c r="I493" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bottleshop.sk</t>
+        </is>
+      </c>
+      <c r="J493" s="2" t="inlineStr"/>
+      <c r="K493" s="2" t="inlineStr"/>
+      <c r="L493" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M493" s="2" t="inlineStr"/>
+      <c r="N493" s="2" t="inlineStr">
+        <is>
+          <t>info@bottleshop.sk</t>
+        </is>
+      </c>
+      <c r="O493" s="2" t="inlineStr"/>
+      <c r="P493" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q493" s="2" t="inlineStr">
+        <is>
+          <t>45906149</t>
+        </is>
+      </c>
+      <c r="R493" s="2" t="inlineStr"/>
+      <c r="S493" s="2" t="inlineStr"/>
+      <c r="T493" s="2" t="inlineStr"/>
+      <c r="U493" s="2" t="inlineStr"/>
+      <c r="V493" s="2" t="inlineStr"/>
+      <c r="W493" s="2" t="inlineStr">
+        <is>
+          <t>Juraj Sketa</t>
+        </is>
+      </c>
+      <c r="X493" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y493" s="2" t="inlineStr"/>
+      <c r="Z493" s="2" t="inlineStr"/>
+      <c r="AA493" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/juraj-sketa-02a61518</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>Finest Rum Store, S. R. O.</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>Finest Rum Store, S. R. O.</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>27125</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>Miloslavov</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Senec</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>1999 Obchodná</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>900 42</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>https://dobryrum.sk</t>
+        </is>
+      </c>
+      <c r="J494" s="2" t="inlineStr"/>
+      <c r="K494" s="2" t="inlineStr"/>
+      <c r="L494" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M494" s="2" t="inlineStr"/>
+      <c r="N494" s="2" t="inlineStr">
+        <is>
+          <t>info@dobryrum.sk</t>
+        </is>
+      </c>
+      <c r="O494" s="2" t="inlineStr"/>
+      <c r="P494" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q494" s="2" t="inlineStr">
+        <is>
+          <t>50559541</t>
+        </is>
+      </c>
+      <c r="R494" s="2" t="inlineStr"/>
+      <c r="S494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dobryrum</t>
+        </is>
+      </c>
+      <c r="T494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dobry_rum/</t>
+        </is>
+      </c>
+      <c r="U494" s="2" t="inlineStr"/>
+      <c r="V494" s="2" t="inlineStr"/>
+      <c r="W494" s="2" t="inlineStr"/>
+      <c r="X494" s="2" t="inlineStr"/>
+      <c r="Y494" s="2" t="inlineStr"/>
+      <c r="Z494" s="2" t="inlineStr"/>
+      <c r="AA494" s="2" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>Topwine.sk</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>Topwine.sk</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>11930</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>Budča</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj, Zvolen</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>463 Stromová</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>962 33</t>
+        </is>
+      </c>
+      <c r="I495" s="2" t="inlineStr">
+        <is>
+          <t>https://www.topwine.sk</t>
+        </is>
+      </c>
+      <c r="J495" s="2" t="inlineStr"/>
+      <c r="K495" s="2" t="inlineStr"/>
+      <c r="L495" s="2" t="inlineStr"/>
+      <c r="M495" s="2" t="inlineStr"/>
+      <c r="N495" s="2" t="inlineStr">
+        <is>
+          <t>info@topwine.sk</t>
+        </is>
+      </c>
+      <c r="O495" s="2" t="inlineStr"/>
+      <c r="P495" s="2" t="inlineStr"/>
+      <c r="Q495" s="2" t="inlineStr"/>
+      <c r="R495" s="2" t="inlineStr"/>
+      <c r="S495" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Topwinesk-61550639900124/</t>
+        </is>
+      </c>
+      <c r="T495" s="2" t="inlineStr"/>
+      <c r="U495" s="2" t="inlineStr"/>
+      <c r="V495" s="2" t="inlineStr"/>
+      <c r="W495" s="2" t="inlineStr"/>
+      <c r="X495" s="2" t="inlineStr"/>
+      <c r="Y495" s="2" t="inlineStr"/>
+      <c r="Z495" s="2" t="inlineStr"/>
+      <c r="AA495" s="2" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>Shop4wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>Shop4wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>11926</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>Piešťany</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>2149 Hodžova</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>921 01</t>
+        </is>
+      </c>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>https://shop4wine.sk</t>
+        </is>
+      </c>
+      <c r="J496" s="2" t="inlineStr"/>
+      <c r="K496" s="2" t="inlineStr"/>
+      <c r="L496" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M496" s="2" t="inlineStr"/>
+      <c r="N496" s="2" t="inlineStr">
+        <is>
+          <t>info@shop4wine.sk</t>
+        </is>
+      </c>
+      <c r="O496" s="2" t="inlineStr"/>
+      <c r="P496" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q496" s="2" t="inlineStr">
+        <is>
+          <t>45909911</t>
+        </is>
+      </c>
+      <c r="R496" s="2" t="inlineStr"/>
+      <c r="S496" s="2" t="inlineStr"/>
+      <c r="T496" s="2" t="inlineStr"/>
+      <c r="U496" s="2" t="inlineStr"/>
+      <c r="V496" s="2" t="inlineStr"/>
+      <c r="W496" s="2" t="inlineStr"/>
+      <c r="X496" s="2" t="inlineStr"/>
+      <c r="Y496" s="2" t="inlineStr"/>
+      <c r="Z496" s="2" t="inlineStr"/>
+      <c r="AA496" s="2" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>Komfos Prešov, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>Komfos Prešov, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>103173</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>Ľubotice</t>
+        </is>
+      </c>
+      <c r="F497" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj, Prešov</t>
+        </is>
+      </c>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>2 Ľubochnianska</t>
+        </is>
+      </c>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>080 06</t>
+        </is>
+      </c>
+      <c r="I497" s="2" t="inlineStr">
+        <is>
+          <t>https://cbashop.sk, https://www.komfos.sk</t>
+        </is>
+      </c>
+      <c r="J497" s="2" t="inlineStr"/>
+      <c r="K497" s="2" t="inlineStr"/>
+      <c r="L497" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="M497" s="2" t="inlineStr"/>
+      <c r="N497" s="2" t="inlineStr">
+        <is>
+          <t>office@komfos.sk</t>
+        </is>
+      </c>
+      <c r="O497" s="2" t="inlineStr"/>
+      <c r="P497" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q497" s="2" t="inlineStr">
+        <is>
+          <t>36454184</t>
+        </is>
+      </c>
+      <c r="R497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cba-komfos/</t>
+        </is>
+      </c>
+      <c r="S497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CBAKomfos</t>
+        </is>
+      </c>
+      <c r="T497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cbakomfos/</t>
+        </is>
+      </c>
+      <c r="U497" s="2" t="inlineStr"/>
+      <c r="V497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@komfospresovs.r.o.-velkoob8582/</t>
+        </is>
+      </c>
+      <c r="W497" s="2" t="inlineStr">
+        <is>
+          <t>Slavko Koncar</t>
+        </is>
+      </c>
+      <c r="X497" s="2" t="inlineStr">
+        <is>
+          <t>Area Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y497" s="2" t="inlineStr"/>
+      <c r="Z497" s="2" t="inlineStr"/>
+      <c r="AA497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/slavko-koncar-2817a726/</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>Alko90</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>Alko90</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>29347</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>Most pri Bratislave</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Senec</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>775, Bratislavská</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>900 46</t>
+        </is>
+      </c>
+      <c r="I498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alko90.sk</t>
+        </is>
+      </c>
+      <c r="J498" s="2" t="inlineStr"/>
+      <c r="K498" s="2" t="inlineStr"/>
+      <c r="L498" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M498" s="2" t="inlineStr"/>
+      <c r="N498" s="2" t="inlineStr">
+        <is>
+          <t>info@alko90.sk</t>
+        </is>
+      </c>
+      <c r="O498" s="2" t="inlineStr"/>
+      <c r="P498" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q498" s="2" t="inlineStr">
+        <is>
+          <t>50484800</t>
+        </is>
+      </c>
+      <c r="R498" s="2" t="inlineStr"/>
+      <c r="S498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/alko90sk/</t>
+        </is>
+      </c>
+      <c r="T498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alko90sk/</t>
+        </is>
+      </c>
+      <c r="U498" s="2" t="inlineStr"/>
+      <c r="V498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@alko90sk/</t>
+        </is>
+      </c>
+      <c r="W498" s="2" t="inlineStr">
+        <is>
+          <t>Andrej Slavik</t>
+        </is>
+      </c>
+      <c r="X498" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y498" s="2" t="inlineStr"/>
+      <c r="Z498" s="2" t="inlineStr"/>
+      <c r="AA498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrej-sl%C3%A1vik-91808758/</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>27285</t>
+        </is>
+      </c>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F499" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>18 Jakuba Hašku</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I499" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="J499" s="2" t="inlineStr"/>
+      <c r="K499" s="2" t="inlineStr"/>
+      <c r="L499" s="2" t="inlineStr"/>
+      <c r="M499" s="2" t="inlineStr"/>
+      <c r="N499" s="2" t="inlineStr">
+        <is>
+          <t>hornisova.maria@vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="O499" s="2" t="inlineStr"/>
+      <c r="P499" s="2" t="inlineStr"/>
+      <c r="Q499" s="2" t="inlineStr"/>
+      <c r="R499" s="2" t="inlineStr"/>
+      <c r="S499" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekahornis/</t>
+        </is>
+      </c>
+      <c r="T499" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_hornis/</t>
+        </is>
+      </c>
+      <c r="U499" s="2" t="inlineStr"/>
+      <c r="V499" s="2" t="inlineStr"/>
+      <c r="W499" s="2" t="inlineStr">
+        <is>
+          <t>Viliam Horniš</t>
+        </is>
+      </c>
+      <c r="X499" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y499" s="2" t="inlineStr"/>
+      <c r="Z499" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA499" s="2" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>27285</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>18 Jakuba Hašku</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="J500" s="2" t="inlineStr"/>
+      <c r="K500" s="2" t="inlineStr"/>
+      <c r="L500" s="2" t="inlineStr"/>
+      <c r="M500" s="2" t="inlineStr"/>
+      <c r="N500" s="2" t="inlineStr">
+        <is>
+          <t>hornisova.maria@vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="O500" s="2" t="inlineStr"/>
+      <c r="P500" s="2" t="inlineStr"/>
+      <c r="Q500" s="2" t="inlineStr"/>
+      <c r="R500" s="2" t="inlineStr"/>
+      <c r="S500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekahornis/</t>
+        </is>
+      </c>
+      <c r="T500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_hornis/</t>
+        </is>
+      </c>
+      <c r="U500" s="2" t="inlineStr"/>
+      <c r="V500" s="2" t="inlineStr"/>
+      <c r="W500" s="2" t="inlineStr">
+        <is>
+          <t>Mária Hornišová</t>
+        </is>
+      </c>
+      <c r="X500" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y500" s="2" t="inlineStr"/>
+      <c r="Z500" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA500" s="2" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>Radničná Vinotéka Pezinok</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>Radničná Vinotéka Pezinok</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>41106</t>
+        </is>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>Pezinok</t>
+        </is>
+      </c>
+      <c r="F501" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj</t>
+        </is>
+      </c>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>1, 1 M. R. Štefánika</t>
+        </is>
+      </c>
+      <c r="H501" s="2" t="inlineStr">
+        <is>
+          <t>902 01</t>
+        </is>
+      </c>
+      <c r="I501" s="2" t="inlineStr">
+        <is>
+          <t>http://vinoradnica.sk, https://ratuzky.sk</t>
+        </is>
+      </c>
+      <c r="J501" s="2" t="inlineStr"/>
+      <c r="K501" s="2" t="inlineStr"/>
+      <c r="L501" s="2" t="inlineStr"/>
+      <c r="M501" s="2" t="inlineStr"/>
+      <c r="N501" s="2" t="inlineStr">
+        <is>
+          <t>info@vinoradnica.sk</t>
+        </is>
+      </c>
+      <c r="O501" s="2" t="inlineStr"/>
+      <c r="P501" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q501" s="2" t="inlineStr">
+        <is>
+          <t>34675493</t>
+        </is>
+      </c>
+      <c r="R501" s="2" t="inlineStr"/>
+      <c r="S501" s="2" t="inlineStr"/>
+      <c r="T501" s="2" t="inlineStr"/>
+      <c r="U501" s="2" t="inlineStr"/>
+      <c r="V501" s="2" t="inlineStr"/>
+      <c r="W501" s="2" t="inlineStr"/>
+      <c r="X501" s="2" t="inlineStr"/>
+      <c r="Y501" s="2" t="inlineStr"/>
+      <c r="Z501" s="2" t="inlineStr"/>
+      <c r="AA501" s="2" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka One More</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka One More</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>21140</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>10301, 108 Vajnorská</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I502" s="2" t="inlineStr">
+        <is>
+          <t>https://onemore.sk</t>
+        </is>
+      </c>
+      <c r="J502" s="2" t="inlineStr"/>
+      <c r="K502" s="2" t="inlineStr"/>
+      <c r="L502" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M502" s="2" t="inlineStr"/>
+      <c r="N502" s="2" t="inlineStr">
+        <is>
+          <t>info@onemore.sk</t>
+        </is>
+      </c>
+      <c r="O502" s="2" t="inlineStr"/>
+      <c r="P502" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q502" s="2" t="inlineStr">
+        <is>
+          <t>46896961</t>
+        </is>
+      </c>
+      <c r="R502" s="2" t="inlineStr"/>
+      <c r="S502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/onemore.wine/</t>
+        </is>
+      </c>
+      <c r="T502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onemore_wine/</t>
+        </is>
+      </c>
+      <c r="U502" s="2" t="inlineStr"/>
+      <c r="V502" s="2" t="inlineStr"/>
+      <c r="W502" s="2" t="inlineStr"/>
+      <c r="X502" s="2" t="inlineStr"/>
+      <c r="Y502" s="2" t="inlineStr"/>
+      <c r="Z502" s="2" t="inlineStr"/>
+      <c r="AA502" s="2" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>40555</t>
+        </is>
+      </c>
+      <c r="D503" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F503" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský</t>
+        </is>
+      </c>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>Laurinská 210/8</t>
+        </is>
+      </c>
+      <c r="H503" s="2" t="inlineStr">
+        <is>
+          <t>811 05</t>
+        </is>
+      </c>
+      <c r="I503" s="2" t="inlineStr">
+        <is>
+          <t>https://bwd.sk</t>
+        </is>
+      </c>
+      <c r="J503" s="2" t="inlineStr"/>
+      <c r="K503" s="2" t="inlineStr"/>
+      <c r="L503" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M503" s="2" t="inlineStr"/>
+      <c r="N503" s="2" t="inlineStr">
+        <is>
+          <t>info@bwd.sk</t>
+        </is>
+      </c>
+      <c r="O503" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/207 824 67</t>
+        </is>
+      </c>
+      <c r="P503" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q503" s="2" t="inlineStr">
+        <is>
+          <t>50444271</t>
+        </is>
+      </c>
+      <c r="R503" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/best-wines-distribution/</t>
+        </is>
+      </c>
+      <c r="S503" s="2" t="inlineStr"/>
+      <c r="T503" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bwd.sk/</t>
+        </is>
+      </c>
+      <c r="U503" s="2" t="inlineStr"/>
+      <c r="V503" s="2" t="inlineStr"/>
+      <c r="W503" s="2" t="inlineStr">
+        <is>
+          <t>Marco Masutti</t>
+        </is>
+      </c>
+      <c r="X503" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y503" s="2" t="inlineStr"/>
+      <c r="Z503" s="2" t="inlineStr"/>
+      <c r="AA503" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marco-masutti-056b12203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>40555</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>Laurinská 210/8</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="inlineStr">
+        <is>
+          <t>811 05</t>
+        </is>
+      </c>
+      <c r="I504" s="2" t="inlineStr">
+        <is>
+          <t>https://bwd.sk</t>
+        </is>
+      </c>
+      <c r="J504" s="2" t="inlineStr"/>
+      <c r="K504" s="2" t="inlineStr"/>
+      <c r="L504" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M504" s="2" t="inlineStr"/>
+      <c r="N504" s="2" t="inlineStr">
+        <is>
+          <t>info@bwd.sk</t>
+        </is>
+      </c>
+      <c r="O504" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/207 824 67</t>
+        </is>
+      </c>
+      <c r="P504" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q504" s="2" t="inlineStr">
+        <is>
+          <t>50444271</t>
+        </is>
+      </c>
+      <c r="R504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/best-wines-distribution/</t>
+        </is>
+      </c>
+      <c r="S504" s="2" t="inlineStr"/>
+      <c r="T504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bwd.sk/</t>
+        </is>
+      </c>
+      <c r="U504" s="2" t="inlineStr"/>
+      <c r="V504" s="2" t="inlineStr"/>
+      <c r="W504" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Kollar</t>
+        </is>
+      </c>
+      <c r="X504" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier/ Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y504" s="2" t="inlineStr"/>
+      <c r="Z504" s="2" t="inlineStr"/>
+      <c r="AA504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gabriel-kollar-5996183a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka André, Sro</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka André, Sro</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>41101</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>1 Obchodné centrum Turiec</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>036 01</t>
+        </is>
+      </c>
+      <c r="I505" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoteka-andre.sk</t>
+        </is>
+      </c>
+      <c r="J505" s="2" t="inlineStr"/>
+      <c r="K505" s="2" t="inlineStr"/>
+      <c r="L505" s="2" t="inlineStr"/>
+      <c r="M505" s="2" t="inlineStr"/>
+      <c r="N505" s="2" t="inlineStr">
+        <is>
+          <t>info@vinoteka-andre.sk</t>
+        </is>
+      </c>
+      <c r="O505" s="2" t="inlineStr"/>
+      <c r="P505" s="2" t="inlineStr"/>
+      <c r="Q505" s="2" t="inlineStr"/>
+      <c r="R505" s="2" t="inlineStr"/>
+      <c r="S505" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinotekaAndre/</t>
+        </is>
+      </c>
+      <c r="T505" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotekaandre/</t>
+        </is>
+      </c>
+      <c r="U505" s="2" t="inlineStr"/>
+      <c r="V505" s="2" t="inlineStr"/>
+      <c r="W505" s="2" t="inlineStr"/>
+      <c r="X505" s="2" t="inlineStr"/>
+      <c r="Y505" s="2" t="inlineStr"/>
+      <c r="Z505" s="2" t="inlineStr"/>
+      <c r="AA505" s="2" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>108846</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>Svit</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj, Poprad</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>208, 156 Mierová</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>059 21</t>
+        </is>
+      </c>
+      <c r="I506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="J506" s="2" t="inlineStr"/>
+      <c r="K506" s="2" t="inlineStr"/>
+      <c r="L506" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M506" s="2" t="inlineStr"/>
+      <c r="N506" s="2" t="inlineStr">
+        <is>
+          <t>info@jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="O506" s="2" t="inlineStr">
+        <is>
+          <t>+421 52 123 45 67</t>
+        </is>
+      </c>
+      <c r="P506" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q506" s="2" t="inlineStr">
+        <is>
+          <t>46814973</t>
+        </is>
+      </c>
+      <c r="R506" s="2" t="inlineStr"/>
+      <c r="S506" s="2" t="inlineStr"/>
+      <c r="T506" s="2" t="inlineStr"/>
+      <c r="U506" s="2" t="inlineStr"/>
+      <c r="V506" s="2" t="inlineStr"/>
+      <c r="W506" s="2" t="inlineStr">
+        <is>
+          <t>Jan Filipsky</t>
+        </is>
+      </c>
+      <c r="X506" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y506" s="2" t="inlineStr"/>
+      <c r="Z506" s="2" t="inlineStr"/>
+      <c r="AA506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jan-filipsky-a96a5345/</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>108846</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>Svit</t>
+        </is>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj, Poprad</t>
+        </is>
+      </c>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>208, 156 Mierová</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>059 21</t>
+        </is>
+      </c>
+      <c r="I507" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="J507" s="2" t="inlineStr"/>
+      <c r="K507" s="2" t="inlineStr"/>
+      <c r="L507" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M507" s="2" t="inlineStr"/>
+      <c r="N507" s="2" t="inlineStr">
+        <is>
+          <t>info@jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="O507" s="2" t="inlineStr">
+        <is>
+          <t>+421 52 123 45 67</t>
+        </is>
+      </c>
+      <c r="P507" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q507" s="2" t="inlineStr">
+        <is>
+          <t>46814973</t>
+        </is>
+      </c>
+      <c r="R507" s="2" t="inlineStr"/>
+      <c r="S507" s="2" t="inlineStr"/>
+      <c r="T507" s="2" t="inlineStr"/>
+      <c r="U507" s="2" t="inlineStr"/>
+      <c r="V507" s="2" t="inlineStr"/>
+      <c r="W507" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Filipský</t>
+        </is>
+      </c>
+      <c r="X507" s="2" t="inlineStr">
+        <is>
+          <t>Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y507" s="2" t="inlineStr"/>
+      <c r="Z507" s="2" t="inlineStr"/>
+      <c r="AA507" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-filipsk%C3%BD-73477383/</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>Reming, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>Reming, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>47015</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>Liptovsky Mikulas</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr"/>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>Moyzesova No. 4358/9</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>031 01</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr">
+        <is>
+          <t>https://reming-sk.com</t>
+        </is>
+      </c>
+      <c r="J508" s="2" t="inlineStr"/>
+      <c r="K508" s="2" t="inlineStr"/>
+      <c r="L508" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M508" s="2" t="inlineStr"/>
+      <c r="N508" s="2" t="inlineStr">
+        <is>
+          <t>office@reming-sk.com</t>
+        </is>
+      </c>
+      <c r="O508" s="2" t="inlineStr"/>
+      <c r="P508" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q508" s="2" t="inlineStr">
+        <is>
+          <t>45605220</t>
+        </is>
+      </c>
+      <c r="R508" s="2" t="inlineStr"/>
+      <c r="S508" s="2" t="inlineStr"/>
+      <c r="T508" s="2" t="inlineStr"/>
+      <c r="U508" s="2" t="inlineStr"/>
+      <c r="V508" s="2" t="inlineStr"/>
+      <c r="W508" s="2" t="inlineStr"/>
+      <c r="X508" s="2" t="inlineStr"/>
+      <c r="Y508" s="2" t="inlineStr"/>
+      <c r="Z508" s="2" t="inlineStr"/>
+      <c r="AA508" s="2" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>Starosel Slovensko S.r.o.</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>Starosel Slovensko S.r.o.</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>20088</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>Michalovce</t>
+        </is>
+      </c>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>Kosický</t>
+        </is>
+      </c>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>Štefaniková 76</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>07101</t>
+        </is>
+      </c>
+      <c r="I509" s="2" t="inlineStr">
+        <is>
+          <t>http://starosel.sk, https://www.staroselshop.sk</t>
+        </is>
+      </c>
+      <c r="J509" s="2" t="inlineStr"/>
+      <c r="K509" s="2" t="inlineStr"/>
+      <c r="L509" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M509" s="2" t="inlineStr"/>
+      <c r="N509" s="2" t="inlineStr">
+        <is>
+          <t>starosel@starosel.sk</t>
+        </is>
+      </c>
+      <c r="O509" s="2" t="inlineStr"/>
+      <c r="P509" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q509" s="2" t="inlineStr">
+        <is>
+          <t>47689901</t>
+        </is>
+      </c>
+      <c r="R509" s="2" t="inlineStr"/>
+      <c r="S509" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/starosel.sk/</t>
+        </is>
+      </c>
+      <c r="T509" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/staroselslovensko/</t>
+        </is>
+      </c>
+      <c r="U509" s="2" t="inlineStr"/>
+      <c r="V509" s="2" t="inlineStr"/>
+      <c r="W509" s="2" t="inlineStr"/>
+      <c r="X509" s="2" t="inlineStr"/>
+      <c r="Y509" s="2" t="inlineStr"/>
+      <c r="Z509" s="2" t="inlineStr"/>
+      <c r="AA509" s="2" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>Extraprodukty, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>Extraprodukty, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>20087</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>Šamorín</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj, Dunajská Streda</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>Vodárenská 2589/2A</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>931 01</t>
+        </is>
+      </c>
+      <c r="I510" s="2" t="inlineStr">
+        <is>
+          <t>https://www.extraprodukty.sk</t>
+        </is>
+      </c>
+      <c r="J510" s="2" t="inlineStr"/>
+      <c r="K510" s="2" t="inlineStr"/>
+      <c r="L510" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M510" s="2" t="inlineStr"/>
+      <c r="N510" s="2" t="inlineStr">
+        <is>
+          <t>obchod@extraprodukty.sk</t>
+        </is>
+      </c>
+      <c r="O510" s="2" t="inlineStr"/>
+      <c r="P510" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q510" s="2" t="inlineStr">
+        <is>
+          <t>46158880</t>
+        </is>
+      </c>
+      <c r="R510" s="2" t="inlineStr"/>
+      <c r="S510" s="2" t="inlineStr"/>
+      <c r="T510" s="2" t="inlineStr"/>
+      <c r="U510" s="2" t="inlineStr"/>
+      <c r="V510" s="2" t="inlineStr"/>
+      <c r="W510" s="2" t="inlineStr"/>
+      <c r="X510" s="2" t="inlineStr"/>
+      <c r="Y510" s="2" t="inlineStr"/>
+      <c r="Z510" s="2" t="inlineStr"/>
+      <c r="AA510" s="2" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>Mge Plus S.r.o.</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>Mge Plus S.r.o.</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>28275</t>
+        </is>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>Trenčianska Teplá</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj, Trenčín</t>
+        </is>
+      </c>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>Andreja Hlinku 34</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>914 01</t>
+        </is>
+      </c>
+      <c r="I511" s="2" t="inlineStr">
+        <is>
+          <t>https://lacnevino.sk</t>
+        </is>
+      </c>
+      <c r="J511" s="2" t="inlineStr"/>
+      <c r="K511" s="2" t="inlineStr"/>
+      <c r="L511" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M511" s="2" t="inlineStr"/>
+      <c r="N511" s="2" t="inlineStr">
+        <is>
+          <t>mgeplus@centrum.sk</t>
+        </is>
+      </c>
+      <c r="O511" s="2" t="inlineStr"/>
+      <c r="P511" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q511" s="2" t="inlineStr">
+        <is>
+          <t>46198687</t>
+        </is>
+      </c>
+      <c r="R511" s="2" t="inlineStr"/>
+      <c r="S511" s="2" t="inlineStr"/>
+      <c r="T511" s="2" t="inlineStr"/>
+      <c r="U511" s="2" t="inlineStr"/>
+      <c r="V511" s="2" t="inlineStr"/>
+      <c r="W511" s="2" t="inlineStr">
+        <is>
+          <t>Monika Jančová</t>
+        </is>
+      </c>
+      <c r="X511" s="2" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="Y511" s="2" t="inlineStr"/>
+      <c r="Z511" s="2" t="inlineStr"/>
+      <c r="AA511" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/monika-jan%C4%8Dov%C3%A1-7ab50a220/</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Pri Modrom Kostolíku</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Pri Modrom Kostolíku</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>49625</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj I</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>2541/2 Sienkiewiczova</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>811 09</t>
+        </is>
+      </c>
+      <c r="I512" s="2" t="inlineStr">
+        <is>
+          <t>https://vinotekamodrykostolik.sk</t>
+        </is>
+      </c>
+      <c r="J512" s="2" t="inlineStr"/>
+      <c r="K512" s="2" t="inlineStr"/>
+      <c r="L512" s="2" t="inlineStr"/>
+      <c r="M512" s="2" t="inlineStr"/>
+      <c r="N512" s="2" t="inlineStr">
+        <is>
+          <t>vinoteka@modrykostolik.sk</t>
+        </is>
+      </c>
+      <c r="O512" s="2" t="inlineStr"/>
+      <c r="P512" s="2" t="inlineStr"/>
+      <c r="Q512" s="2" t="inlineStr"/>
+      <c r="R512" s="2" t="inlineStr"/>
+      <c r="S512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekaprimodromkostoliku/</t>
+        </is>
+      </c>
+      <c r="T512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_modry_kostolik/</t>
+        </is>
+      </c>
+      <c r="U512" s="2" t="inlineStr"/>
+      <c r="V512" s="2" t="inlineStr"/>
+      <c r="W512" s="2" t="inlineStr"/>
+      <c r="X512" s="2" t="inlineStr"/>
+      <c r="Y512" s="2" t="inlineStr"/>
+      <c r="Z512" s="2" t="inlineStr"/>
+      <c r="AA512" s="2" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>Lumarkt, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>Lumarkt, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>11890</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>Staré Mesto</t>
+        </is>
+      </c>
+      <c r="F513" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj, Košice I</t>
+        </is>
+      </c>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>1 Hutnícka</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>040 01</t>
+        </is>
+      </c>
+      <c r="I513" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lumarkt.sk</t>
+        </is>
+      </c>
+      <c r="J513" s="2" t="inlineStr"/>
+      <c r="K513" s="2" t="inlineStr"/>
+      <c r="L513" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M513" s="2" t="inlineStr"/>
+      <c r="N513" s="2" t="inlineStr">
+        <is>
+          <t>info@lumarkt.sk</t>
+        </is>
+      </c>
+      <c r="O513" s="2" t="inlineStr">
+        <is>
+          <t>+421 55 798 85 71</t>
+        </is>
+      </c>
+      <c r="P513" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q513" s="2" t="inlineStr">
+        <is>
+          <t>36216631</t>
+        </is>
+      </c>
+      <c r="R513" s="2" t="inlineStr"/>
+      <c r="S513" s="2" t="inlineStr"/>
+      <c r="T513" s="2" t="inlineStr"/>
+      <c r="U513" s="2" t="inlineStr"/>
+      <c r="V513" s="2" t="inlineStr"/>
+      <c r="W513" s="2" t="inlineStr">
+        <is>
+          <t>Janka Mrugova</t>
+        </is>
+      </c>
+      <c r="X513" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y513" s="2" t="inlineStr"/>
+      <c r="Z513" s="2" t="inlineStr"/>
+      <c r="AA513" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/janka-mrugova-b5364047/</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>Karmen - Velkoobchod Potravín S.r.o.</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>Karmen - Velkoobchod Potravín S.r.o.</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>54186</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>Prešov</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>15 Strojnícka</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>080 06</t>
+        </is>
+      </c>
+      <c r="I514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karmen.sk</t>
+        </is>
+      </c>
+      <c r="J514" s="2" t="inlineStr"/>
+      <c r="K514" s="2" t="inlineStr"/>
+      <c r="L514" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="M514" s="2" t="inlineStr"/>
+      <c r="N514" s="2" t="inlineStr">
+        <is>
+          <t>karmen@karmen.sk</t>
+        </is>
+      </c>
+      <c r="O514" s="2" t="inlineStr">
+        <is>
+          <t>+421 51/771 17 14</t>
+        </is>
+      </c>
+      <c r="P514" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q514" s="2" t="inlineStr">
+        <is>
+          <t>36447269</t>
+        </is>
+      </c>
+      <c r="R514" s="2" t="inlineStr"/>
+      <c r="S514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100063498972682</t>
+        </is>
+      </c>
+      <c r="T514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cba_karmen/</t>
+        </is>
+      </c>
+      <c r="U514" s="2" t="inlineStr"/>
+      <c r="V514" s="2" t="inlineStr"/>
+      <c r="W514" s="2" t="inlineStr"/>
+      <c r="X514" s="2" t="inlineStr"/>
+      <c r="Y514" s="2" t="inlineStr"/>
+      <c r="Z514" s="2" t="inlineStr"/>
+      <c r="AA514" s="2" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>Great Wines Cellar</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>Great Wines Cellar</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>24602</t>
+        </is>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>Ružinov</t>
+        </is>
+      </c>
+      <c r="F515" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava II</t>
+        </is>
+      </c>
+      <c r="G515" s="2" t="inlineStr">
+        <is>
+          <t>937 Koceľova</t>
+        </is>
+      </c>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>821 08</t>
+        </is>
+      </c>
+      <c r="I515" s="2" t="inlineStr">
+        <is>
+          <t>https://greatwinescellar.com</t>
+        </is>
+      </c>
+      <c r="J515" s="2" t="inlineStr"/>
+      <c r="K515" s="2" t="inlineStr"/>
+      <c r="L515" s="2" t="inlineStr"/>
+      <c r="M515" s="2" t="inlineStr"/>
+      <c r="N515" s="2" t="inlineStr">
+        <is>
+          <t>info@greatwinescellar.com</t>
+        </is>
+      </c>
+      <c r="O515" s="2" t="inlineStr">
+        <is>
+          <t>+43 1 9437915</t>
+        </is>
+      </c>
+      <c r="P515" s="2" t="inlineStr"/>
+      <c r="Q515" s="2" t="inlineStr"/>
+      <c r="R515" s="2" t="inlineStr"/>
+      <c r="S515" s="2" t="inlineStr"/>
+      <c r="T515" s="2" t="inlineStr"/>
+      <c r="U515" s="2" t="inlineStr"/>
+      <c r="V515" s="2" t="inlineStr"/>
+      <c r="W515" s="2" t="inlineStr">
+        <is>
+          <t>Denis Danilenko</t>
+        </is>
+      </c>
+      <c r="X515" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y515" s="2" t="inlineStr"/>
+      <c r="Z515" s="2" t="inlineStr"/>
+      <c r="AA515" s="2" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>Vineria S.r.o.</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>Vineria S.r.o.</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>108851</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>Topoľčany</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>Nitriansky kraj</t>
+        </is>
+      </c>
+      <c r="G516" s="2" t="inlineStr">
+        <is>
+          <t>958, 20 Československej armády</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>955 01</t>
+        </is>
+      </c>
+      <c r="I516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vineria.sk</t>
+        </is>
+      </c>
+      <c r="J516" s="2" t="inlineStr"/>
+      <c r="K516" s="2" t="inlineStr"/>
+      <c r="L516" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M516" s="2" t="inlineStr"/>
+      <c r="N516" s="2" t="inlineStr">
+        <is>
+          <t>obchod@vineria.sk</t>
+        </is>
+      </c>
+      <c r="O516" s="2" t="inlineStr"/>
+      <c r="P516" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q516" s="2" t="inlineStr">
+        <is>
+          <t>46409165</t>
+        </is>
+      </c>
+      <c r="R516" s="2" t="inlineStr"/>
+      <c r="S516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Vineria-Topo%C4%BE%C4%8Dany-100027232792145/</t>
+        </is>
+      </c>
+      <c r="T516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_vineria_/</t>
+        </is>
+      </c>
+      <c r="U516" s="2" t="inlineStr"/>
+      <c r="V516" s="2" t="inlineStr"/>
+      <c r="W516" s="2" t="inlineStr"/>
+      <c r="X516" s="2" t="inlineStr"/>
+      <c r="Y516" s="2" t="inlineStr"/>
+      <c r="Z516" s="2" t="inlineStr"/>
+      <c r="AA516" s="2" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>Novino, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>Novino, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>108848</t>
+        </is>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava I</t>
+        </is>
+      </c>
+      <c r="G517" s="2" t="inlineStr">
+        <is>
+          <t>4087, 26 Krížna</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="inlineStr">
+        <is>
+          <t>811 07</t>
+        </is>
+      </c>
+      <c r="I517" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novino.sk</t>
+        </is>
+      </c>
+      <c r="J517" s="2" t="inlineStr"/>
+      <c r="K517" s="2" t="inlineStr"/>
+      <c r="L517" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M517" s="2" t="inlineStr"/>
+      <c r="N517" s="2" t="inlineStr">
+        <is>
+          <t>predaj@novino.sk</t>
+        </is>
+      </c>
+      <c r="O517" s="2" t="inlineStr"/>
+      <c r="P517" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q517" s="2" t="inlineStr">
+        <is>
+          <t>53348800</t>
+        </is>
+      </c>
+      <c r="R517" s="2" t="inlineStr"/>
+      <c r="S517" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Novino.sk/</t>
+        </is>
+      </c>
+      <c r="T517" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/novino_sk/</t>
+        </is>
+      </c>
+      <c r="U517" s="2" t="inlineStr"/>
+      <c r="V517" s="2" t="inlineStr"/>
+      <c r="W517" s="2" t="inlineStr">
+        <is>
+          <t>Marek Paulen</t>
+        </is>
+      </c>
+      <c r="X517" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y517" s="2" t="inlineStr"/>
+      <c r="Z517" s="2" t="inlineStr"/>
+      <c r="AA517" s="2" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>ENERGY TRANS, spol. s r.o.</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>Dom Vína žilina</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>11919</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>Rosina</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr"/>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t>Rosina 1057</t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>013 22</t>
+        </is>
+      </c>
+      <c r="I518" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kupvino.sk</t>
+        </is>
+      </c>
+      <c r="J518" s="2" t="inlineStr"/>
+      <c r="K518" s="2" t="inlineStr"/>
+      <c r="L518" s="2" t="inlineStr"/>
+      <c r="M518" s="2" t="inlineStr"/>
+      <c r="N518" s="2" t="inlineStr">
+        <is>
+          <t>kupvino@kupvino.sk</t>
+        </is>
+      </c>
+      <c r="O518" s="2" t="inlineStr"/>
+      <c r="P518" s="2" t="inlineStr"/>
+      <c r="Q518" s="2" t="inlineStr"/>
+      <c r="R518" s="2" t="inlineStr"/>
+      <c r="S518" s="2" t="inlineStr"/>
+      <c r="T518" s="2" t="inlineStr"/>
+      <c r="U518" s="2" t="inlineStr"/>
+      <c r="V518" s="2" t="inlineStr"/>
+      <c r="W518" s="2" t="inlineStr"/>
+      <c r="X518" s="2" t="inlineStr"/>
+      <c r="Y518" s="2" t="inlineStr"/>
+      <c r="Z518" s="2" t="inlineStr"/>
+      <c r="AA518" s="2" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>Vinalma, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>Vinalma, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>11903</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F519" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G519" s="2" t="inlineStr">
+        <is>
+          <t>76 Opatovská</t>
+        </is>
+      </c>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>911 01</t>
+        </is>
+      </c>
+      <c r="I519" s="2" t="inlineStr">
+        <is>
+          <t>http://www.vinalma.sk</t>
+        </is>
+      </c>
+      <c r="J519" s="2" t="inlineStr"/>
+      <c r="K519" s="2" t="inlineStr"/>
+      <c r="L519" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M519" s="2" t="inlineStr"/>
+      <c r="N519" s="2" t="inlineStr">
+        <is>
+          <t>office@vinalma.sk</t>
+        </is>
+      </c>
+      <c r="O519" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/744 58 12</t>
+        </is>
+      </c>
+      <c r="P519" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q519" s="2" t="inlineStr">
+        <is>
+          <t>35697768</t>
+        </is>
+      </c>
+      <c r="R519" s="2" t="inlineStr"/>
+      <c r="S519" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinalmaSro/</t>
+        </is>
+      </c>
+      <c r="T519" s="2" t="inlineStr"/>
+      <c r="U519" s="2" t="inlineStr"/>
+      <c r="V519" s="2" t="inlineStr"/>
+      <c r="W519" s="2" t="inlineStr">
+        <is>
+          <t>Edita Durcova</t>
+        </is>
+      </c>
+      <c r="X519" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y519" s="2" t="inlineStr"/>
+      <c r="Z519" s="2" t="inlineStr"/>
+      <c r="AA519" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/edita-durcova-4856203a</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>Pálinkás-Szicsek sro</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>Szicsek Slovakia</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>20089</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>Dunajská Streda</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj</t>
+        </is>
+      </c>
+      <c r="G520" s="2" t="inlineStr">
+        <is>
+          <t>39, 29 Hlavná</t>
+        </is>
+      </c>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>929 01</t>
+        </is>
+      </c>
+      <c r="I520" s="2" t="inlineStr">
+        <is>
+          <t>https://www.palinkas.sk</t>
+        </is>
+      </c>
+      <c r="J520" s="2" t="inlineStr"/>
+      <c r="K520" s="2" t="inlineStr"/>
+      <c r="L520" s="2" t="inlineStr"/>
+      <c r="M520" s="2" t="inlineStr"/>
+      <c r="N520" s="2" t="inlineStr">
+        <is>
+          <t>palinka-wine@palinkas.sk</t>
+        </is>
+      </c>
+      <c r="O520" s="2" t="inlineStr"/>
+      <c r="P520" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q520" s="2" t="inlineStr">
+        <is>
+          <t>33934363</t>
+        </is>
+      </c>
+      <c r="R520" s="2" t="inlineStr"/>
+      <c r="S520" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SzicsekSlovensko</t>
+        </is>
+      </c>
+      <c r="T520" s="2" t="inlineStr"/>
+      <c r="U520" s="2" t="inlineStr"/>
+      <c r="V520" s="2" t="inlineStr"/>
+      <c r="W520" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Pálinkás</t>
+        </is>
+      </c>
+      <c r="X520" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y520" s="2" t="inlineStr"/>
+      <c r="Z520" s="2" t="inlineStr"/>
+      <c r="AA520" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/gabriel-pálinkás-440998a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>Sklié, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>La Vie en Rose</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>31686</t>
+        </is>
+      </c>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F521" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava I</t>
+        </is>
+      </c>
+      <c r="G521" s="2" t="inlineStr">
+        <is>
+          <t>4 Radlinského</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="inlineStr">
+        <is>
+          <t>811 07</t>
+        </is>
+      </c>
+      <c r="I521" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lavieenrose.sk</t>
+        </is>
+      </c>
+      <c r="J521" s="2" t="inlineStr"/>
+      <c r="K521" s="2" t="inlineStr"/>
+      <c r="L521" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M521" s="2" t="inlineStr"/>
+      <c r="N521" s="2" t="inlineStr">
+        <is>
+          <t>info@lavieenrose.sk</t>
+        </is>
+      </c>
+      <c r="O521" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/524 927 42</t>
+        </is>
+      </c>
+      <c r="P521" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q521" s="2" t="inlineStr">
+        <is>
+          <t>35950978</t>
+        </is>
+      </c>
+      <c r="R521" s="2" t="inlineStr"/>
+      <c r="S521" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinotekaLaVieenRose/</t>
+        </is>
+      </c>
+      <c r="T521" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotekalavieenrose/</t>
+        </is>
+      </c>
+      <c r="U521" s="2" t="inlineStr"/>
+      <c r="V521" s="2" t="inlineStr"/>
+      <c r="W521" s="2" t="inlineStr"/>
+      <c r="X521" s="2" t="inlineStr"/>
+      <c r="Y521" s="2" t="inlineStr"/>
+      <c r="Z521" s="2" t="inlineStr"/>
+      <c r="AA521" s="2" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>Belvet, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>Belvet, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>11913</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>Križovany nad Dudváhom</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj, Trnava</t>
+        </is>
+      </c>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>Križovany Nad Dudváhom 511</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="inlineStr">
+        <is>
+          <t>919 24</t>
+        </is>
+      </c>
+      <c r="I522" s="2" t="inlineStr">
+        <is>
+          <t>https://belvet.sk</t>
+        </is>
+      </c>
+      <c r="J522" s="2" t="inlineStr"/>
+      <c r="K522" s="2" t="inlineStr"/>
+      <c r="L522" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M522" s="2" t="inlineStr"/>
+      <c r="N522" s="2" t="inlineStr">
+        <is>
+          <t>belvet@belvet.sk</t>
+        </is>
+      </c>
+      <c r="O522" s="2" t="inlineStr"/>
+      <c r="P522" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q522" s="2" t="inlineStr">
+        <is>
+          <t>46284699</t>
+        </is>
+      </c>
+      <c r="R522" s="2" t="inlineStr"/>
+      <c r="S522" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/belvet.eshop</t>
+        </is>
+      </c>
+      <c r="T522" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/belvet.sk.lubos/</t>
+        </is>
+      </c>
+      <c r="U522" s="2" t="inlineStr"/>
+      <c r="V522" s="2" t="inlineStr"/>
+      <c r="W522" s="2" t="inlineStr"/>
+      <c r="X522" s="2" t="inlineStr"/>
+      <c r="Y522" s="2" t="inlineStr"/>
+      <c r="Z522" s="2" t="inlineStr"/>
+      <c r="AA522" s="2" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>Vinocentrum S. R. O.</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>Vinocentrum S. R. O.</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>58758</t>
+        </is>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>Banska Stiavnica</t>
+        </is>
+      </c>
+      <c r="F523" s="2" t="inlineStr"/>
+      <c r="G523" s="2" t="inlineStr">
+        <is>
+          <t>Kammerhofská 178/2</t>
+        </is>
+      </c>
+      <c r="H523" s="2" t="inlineStr">
+        <is>
+          <t>96901</t>
+        </is>
+      </c>
+      <c r="I523" s="2" t="inlineStr">
+        <is>
+          <t>https://vinocentrum.sk</t>
+        </is>
+      </c>
+      <c r="J523" s="2" t="inlineStr"/>
+      <c r="K523" s="2" t="inlineStr"/>
+      <c r="L523" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M523" s="2" t="inlineStr"/>
+      <c r="N523" s="2" t="inlineStr">
+        <is>
+          <t>vinocentrum@gmail.com</t>
+        </is>
+      </c>
+      <c r="O523" s="2" t="inlineStr"/>
+      <c r="P523" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q523" s="2" t="inlineStr">
+        <is>
+          <t>53125967</t>
+        </is>
+      </c>
+      <c r="R523" s="2" t="inlineStr"/>
+      <c r="S523" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinocentrum/</t>
+        </is>
+      </c>
+      <c r="T523" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinocentrum/</t>
+        </is>
+      </c>
+      <c r="U523" s="2" t="inlineStr"/>
+      <c r="V523" s="2" t="inlineStr"/>
+      <c r="W523" s="2" t="inlineStr">
+        <is>
+          <t>Brano Bahna</t>
+        </is>
+      </c>
+      <c r="X523" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y523" s="2" t="inlineStr"/>
+      <c r="Z523" s="2" t="inlineStr"/>
+      <c r="AA523" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/brano-bahna-a394978b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>58756</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>Trnava Region, Trnava District</t>
+        </is>
+      </c>
+      <c r="G524" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov 464</t>
+        </is>
+      </c>
+      <c r="H524" s="2" t="inlineStr">
+        <is>
+          <t>919 22</t>
+        </is>
+      </c>
+      <c r="I524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoteka-cassalle.sk</t>
+        </is>
+      </c>
+      <c r="J524" s="2" t="inlineStr"/>
+      <c r="K524" s="2" t="inlineStr"/>
+      <c r="L524" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M524" s="2" t="inlineStr"/>
+      <c r="N524" s="2" t="inlineStr">
+        <is>
+          <t>cassalle.vinoteka@gmail.com</t>
+        </is>
+      </c>
+      <c r="O524" s="2" t="inlineStr"/>
+      <c r="P524" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q524" s="2" t="inlineStr">
+        <is>
+          <t>46829679</t>
+        </is>
+      </c>
+      <c r="R524" s="2" t="inlineStr"/>
+      <c r="S524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekacassalletrnava/</t>
+        </is>
+      </c>
+      <c r="T524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cassallevinoteka</t>
+        </is>
+      </c>
+      <c r="U524" s="2" t="inlineStr"/>
+      <c r="V524" s="2" t="inlineStr"/>
+      <c r="W524" s="2" t="inlineStr">
+        <is>
+          <t>Marcel Kuracina</t>
+        </is>
+      </c>
+      <c r="X524" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y524" s="2" t="inlineStr"/>
+      <c r="Z524" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA524" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/marcel-kuracina-0464b9a5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>58756</t>
+        </is>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov</t>
+        </is>
+      </c>
+      <c r="F525" s="2" t="inlineStr">
+        <is>
+          <t>Trnava Region, Trnava District</t>
+        </is>
+      </c>
+      <c r="G525" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov 464</t>
+        </is>
+      </c>
+      <c r="H525" s="2" t="inlineStr">
+        <is>
+          <t>919 22</t>
+        </is>
+      </c>
+      <c r="I525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoteka-cassalle.sk</t>
+        </is>
+      </c>
+      <c r="J525" s="2" t="inlineStr"/>
+      <c r="K525" s="2" t="inlineStr"/>
+      <c r="L525" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M525" s="2" t="inlineStr"/>
+      <c r="N525" s="2" t="inlineStr">
+        <is>
+          <t>cassalle.vinoteka@gmail.com</t>
+        </is>
+      </c>
+      <c r="O525" s="2" t="inlineStr"/>
+      <c r="P525" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q525" s="2" t="inlineStr">
+        <is>
+          <t>46829679</t>
+        </is>
+      </c>
+      <c r="R525" s="2" t="inlineStr"/>
+      <c r="S525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekacassalletrnava/</t>
+        </is>
+      </c>
+      <c r="T525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cassallevinoteka</t>
+        </is>
+      </c>
+      <c r="U525" s="2" t="inlineStr"/>
+      <c r="V525" s="2" t="inlineStr"/>
+      <c r="W525" s="2" t="inlineStr">
+        <is>
+          <t>Andrej Kleštinec</t>
+        </is>
+      </c>
+      <c r="X525" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y525" s="2" t="inlineStr"/>
+      <c r="Z525" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA525" s="2" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>Michal Heinz - Obchod S Vínom</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>Michal Heinz - Obchod S Vínom</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>20097</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj</t>
+        </is>
+      </c>
+      <c r="G526" s="2" t="inlineStr">
+        <is>
+          <t>97, 41 Horná</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>974 01</t>
+        </is>
+      </c>
+      <c r="I526" s="2" t="inlineStr">
+        <is>
+          <t>http://www.somelier.sk</t>
+        </is>
+      </c>
+      <c r="J526" s="2" t="inlineStr"/>
+      <c r="K526" s="2" t="inlineStr"/>
+      <c r="L526" s="2" t="inlineStr"/>
+      <c r="M526" s="2" t="inlineStr"/>
+      <c r="N526" s="2" t="inlineStr">
+        <is>
+          <t>somelier@somelier.sk</t>
+        </is>
+      </c>
+      <c r="O526" s="2" t="inlineStr"/>
+      <c r="P526" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q526" s="2" t="inlineStr">
+        <is>
+          <t>40888789</t>
+        </is>
+      </c>
+      <c r="R526" s="2" t="inlineStr"/>
+      <c r="S526" s="2" t="inlineStr"/>
+      <c r="T526" s="2" t="inlineStr"/>
+      <c r="U526" s="2" t="inlineStr"/>
+      <c r="V526" s="2" t="inlineStr"/>
+      <c r="W526" s="2" t="inlineStr"/>
+      <c r="X526" s="2" t="inlineStr"/>
+      <c r="Y526" s="2" t="inlineStr"/>
+      <c r="Z526" s="2" t="inlineStr"/>
+      <c r="AA526" s="2" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>54060</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F527" s="2" t="inlineStr"/>
+      <c r="G527" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavská 923 (INDUSTRIAL PARK)</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I527" s="2" t="inlineStr">
+        <is>
+          <t>https://pima.sk</t>
+        </is>
+      </c>
+      <c r="J527" s="2" t="inlineStr"/>
+      <c r="K527" s="2" t="inlineStr"/>
+      <c r="L527" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M527" s="2" t="inlineStr"/>
+      <c r="N527" s="2" t="inlineStr">
+        <is>
+          <t>obchod@pima.sk</t>
+        </is>
+      </c>
+      <c r="O527" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/743 09 11</t>
+        </is>
+      </c>
+      <c r="P527" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q527" s="2" t="inlineStr">
+        <is>
+          <t>36350036</t>
+        </is>
+      </c>
+      <c r="R527" s="2" t="inlineStr"/>
+      <c r="S527" s="2" t="inlineStr"/>
+      <c r="T527" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pima.sk</t>
+        </is>
+      </c>
+      <c r="U527" s="2" t="inlineStr"/>
+      <c r="V527" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC4phGWgVZeTSxNP3V23gzgQ</t>
+        </is>
+      </c>
+      <c r="W527" s="2" t="inlineStr">
+        <is>
+          <t>Rudolf Ďatko</t>
+        </is>
+      </c>
+      <c r="X527" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Managing Director </t>
+        </is>
+      </c>
+      <c r="Y527" s="2" t="inlineStr"/>
+      <c r="Z527" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA527" s="2" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>54060</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr"/>
+      <c r="G528" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavská 923 (INDUSTRIAL PARK)</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I528" s="2" t="inlineStr">
+        <is>
+          <t>https://pima.sk</t>
+        </is>
+      </c>
+      <c r="J528" s="2" t="inlineStr"/>
+      <c r="K528" s="2" t="inlineStr"/>
+      <c r="L528" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M528" s="2" t="inlineStr"/>
+      <c r="N528" s="2" t="inlineStr">
+        <is>
+          <t>obchod@pima.sk</t>
+        </is>
+      </c>
+      <c r="O528" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/743 09 11</t>
+        </is>
+      </c>
+      <c r="P528" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q528" s="2" t="inlineStr">
+        <is>
+          <t>36350036</t>
+        </is>
+      </c>
+      <c r="R528" s="2" t="inlineStr"/>
+      <c r="S528" s="2" t="inlineStr"/>
+      <c r="T528" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pima.sk</t>
+        </is>
+      </c>
+      <c r="U528" s="2" t="inlineStr"/>
+      <c r="V528" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC4phGWgVZeTSxNP3V23gzgQ</t>
+        </is>
+      </c>
+      <c r="W528" s="2" t="inlineStr">
+        <is>
+          <t>Martin Kotrha</t>
+        </is>
+      </c>
+      <c r="X528" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales Director </t>
+        </is>
+      </c>
+      <c r="Y528" s="2" t="inlineStr"/>
+      <c r="Z528" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA528" s="2" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>11882</t>
+        </is>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F529" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G529" s="2" t="inlineStr">
+        <is>
+          <t>49 Vlárska</t>
+        </is>
+      </c>
+      <c r="H529" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I529" s="2" t="inlineStr">
+        <is>
+          <t>https://akevino.sk</t>
+        </is>
+      </c>
+      <c r="J529" s="2" t="inlineStr"/>
+      <c r="K529" s="2" t="inlineStr"/>
+      <c r="L529" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M529" s="2" t="inlineStr"/>
+      <c r="N529" s="2" t="inlineStr">
+        <is>
+          <t>obchod@akevino.sk</t>
+        </is>
+      </c>
+      <c r="O529" s="2" t="inlineStr"/>
+      <c r="P529" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q529" s="2" t="inlineStr">
+        <is>
+          <t>45704163</t>
+        </is>
+      </c>
+      <c r="R529" s="2" t="inlineStr"/>
+      <c r="S529" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/akevino.sk/</t>
+        </is>
+      </c>
+      <c r="T529" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/akevinosk</t>
+        </is>
+      </c>
+      <c r="U529" s="2" t="inlineStr"/>
+      <c r="V529" s="2" t="inlineStr"/>
+      <c r="W529" s="2" t="inlineStr">
+        <is>
+          <t>Matej Poláčik</t>
+        </is>
+      </c>
+      <c r="X529" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y529" s="2" t="inlineStr"/>
+      <c r="Z529" s="2" t="inlineStr"/>
+      <c r="AA529" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/matej-pol%C3%A1%C4%8Dik-8b519519b</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>11882</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G530" s="2" t="inlineStr">
+        <is>
+          <t>49 Vlárska</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I530" s="2" t="inlineStr">
+        <is>
+          <t>https://akevino.sk</t>
+        </is>
+      </c>
+      <c r="J530" s="2" t="inlineStr"/>
+      <c r="K530" s="2" t="inlineStr"/>
+      <c r="L530" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M530" s="2" t="inlineStr"/>
+      <c r="N530" s="2" t="inlineStr">
+        <is>
+          <t>obchod@akevino.sk</t>
+        </is>
+      </c>
+      <c r="O530" s="2" t="inlineStr"/>
+      <c r="P530" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q530" s="2" t="inlineStr">
+        <is>
+          <t>45704163</t>
+        </is>
+      </c>
+      <c r="R530" s="2" t="inlineStr"/>
+      <c r="S530" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/akevino.sk/</t>
+        </is>
+      </c>
+      <c r="T530" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/akevinosk</t>
+        </is>
+      </c>
+      <c r="U530" s="2" t="inlineStr"/>
+      <c r="V530" s="2" t="inlineStr"/>
+      <c r="W530" s="2" t="inlineStr">
+        <is>
+          <t>Juraj Drozd</t>
+        </is>
+      </c>
+      <c r="X530" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y530" s="2" t="inlineStr"/>
+      <c r="Z530" s="2" t="inlineStr"/>
+      <c r="AA530" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/juraj-drozd-8ab51a19a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>Ing. Anton Minčík - Amicomp</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <t>Ing. Anton Minčík - Amicomp</t>
+        </is>
+      </c>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>53942</t>
+        </is>
+      </c>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>Košice</t>
+        </is>
+      </c>
+      <c r="F531" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj, Košice IV</t>
+        </is>
+      </c>
+      <c r="G531" s="2" t="inlineStr">
+        <is>
+          <t>7 Omská</t>
+        </is>
+      </c>
+      <c r="H531" s="2" t="inlineStr">
+        <is>
+          <t>040 01</t>
+        </is>
+      </c>
+      <c r="I531" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amicomp1.sk</t>
+        </is>
+      </c>
+      <c r="J531" s="2" t="inlineStr"/>
+      <c r="K531" s="2" t="inlineStr"/>
+      <c r="L531" s="2" t="inlineStr"/>
+      <c r="M531" s="2" t="inlineStr"/>
+      <c r="N531" s="2" t="inlineStr">
+        <is>
+          <t>amicomp1@amicomp1.sk</t>
+        </is>
+      </c>
+      <c r="O531" s="2" t="inlineStr"/>
+      <c r="P531" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q531" s="2" t="inlineStr">
+        <is>
+          <t>30673275</t>
+        </is>
+      </c>
+      <c r="R531" s="2" t="inlineStr"/>
+      <c r="S531" s="2" t="inlineStr"/>
+      <c r="T531" s="2" t="inlineStr"/>
+      <c r="U531" s="2" t="inlineStr"/>
+      <c r="V531" s="2" t="inlineStr"/>
+      <c r="W531" s="2" t="inlineStr">
+        <is>
+          <t>Anton Minčík</t>
+        </is>
+      </c>
+      <c r="X531" s="2" t="inlineStr">
+        <is>
+          <t>Owner - Manager</t>
+        </is>
+      </c>
+      <c r="Y531" s="2" t="inlineStr"/>
+      <c r="Z531" s="2" t="inlineStr"/>
+      <c r="AA531" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anton-mincik-43b691101/</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>Vk Suma Sro</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>Vk Suma Sro</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>53809</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>Veľký Krtíš</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="inlineStr">
+        <is>
+          <t>27 Osloboditeľov</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>990 01</t>
+        </is>
+      </c>
+      <c r="I532" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vksuma.sk</t>
+        </is>
+      </c>
+      <c r="J532" s="2" t="inlineStr"/>
+      <c r="K532" s="2" t="inlineStr"/>
+      <c r="L532" s="2" t="inlineStr"/>
+      <c r="M532" s="2" t="inlineStr"/>
+      <c r="N532" s="2" t="inlineStr">
+        <is>
+          <t>karolszuma@gmail.com</t>
+        </is>
+      </c>
+      <c r="O532" s="2" t="inlineStr">
+        <is>
+          <t>+421 47 483 11 00</t>
+        </is>
+      </c>
+      <c r="P532" s="2" t="inlineStr"/>
+      <c r="Q532" s="2" t="inlineStr"/>
+      <c r="R532" s="2" t="inlineStr"/>
+      <c r="S532" s="2" t="inlineStr"/>
+      <c r="T532" s="2" t="inlineStr"/>
+      <c r="U532" s="2" t="inlineStr"/>
+      <c r="V532" s="2" t="inlineStr"/>
+      <c r="W532" s="2" t="inlineStr"/>
+      <c r="X532" s="2" t="inlineStr"/>
+      <c r="Y532" s="2" t="inlineStr"/>
+      <c r="Z532" s="2" t="inlineStr"/>
+      <c r="AA532" s="2" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj IV</t>
+        </is>
+      </c>
+      <c r="G533" s="2" t="inlineStr">
+        <is>
+          <t>28a Jána Stanislava</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="inlineStr">
+        <is>
+          <t>841 05</t>
+        </is>
+      </c>
+      <c r="I533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koft.sk</t>
+        </is>
+      </c>
+      <c r="J533" s="2" t="inlineStr"/>
+      <c r="K533" s="2" t="inlineStr"/>
+      <c r="L533" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M533" s="2" t="inlineStr"/>
+      <c r="N533" s="2" t="inlineStr">
+        <is>
+          <t>infokoft@koft.sk</t>
+        </is>
+      </c>
+      <c r="O533" s="2" t="inlineStr">
+        <is>
+          <t>+421 2 502 052 00</t>
+        </is>
+      </c>
+      <c r="P533" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q533" s="2" t="inlineStr">
+        <is>
+          <t>17335248</t>
+        </is>
+      </c>
+      <c r="R533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/koft-s-r-o/</t>
+        </is>
+      </c>
+      <c r="S533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/otazkavoflasi</t>
+        </is>
+      </c>
+      <c r="T533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/koft.sk</t>
+        </is>
+      </c>
+      <c r="U533" s="2" t="inlineStr"/>
+      <c r="V533" s="2" t="inlineStr"/>
+      <c r="W533" s="2" t="inlineStr">
+        <is>
+          <t>Branislav Machovič</t>
+        </is>
+      </c>
+      <c r="X533" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y533" s="2" t="inlineStr"/>
+      <c r="Z533" s="2" t="inlineStr"/>
+      <c r="AA533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/branislav-machovič-53a57085</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj IV</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>28a Jána Stanislava</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>841 05</t>
+        </is>
+      </c>
+      <c r="I534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koft.sk</t>
+        </is>
+      </c>
+      <c r="J534" s="2" t="inlineStr"/>
+      <c r="K534" s="2" t="inlineStr"/>
+      <c r="L534" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M534" s="2" t="inlineStr"/>
+      <c r="N534" s="2" t="inlineStr">
+        <is>
+          <t>infokoft@koft.sk</t>
+        </is>
+      </c>
+      <c r="O534" s="2" t="inlineStr">
+        <is>
+          <t>+421 2 502 052 00</t>
+        </is>
+      </c>
+      <c r="P534" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q534" s="2" t="inlineStr">
+        <is>
+          <t>17335248</t>
+        </is>
+      </c>
+      <c r="R534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/koft-s-r-o/</t>
+        </is>
+      </c>
+      <c r="S534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/otazkavoflasi</t>
+        </is>
+      </c>
+      <c r="T534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/koft.sk</t>
+        </is>
+      </c>
+      <c r="U534" s="2" t="inlineStr"/>
+      <c r="V534" s="2" t="inlineStr"/>
+      <c r="W534" s="2" t="inlineStr">
+        <is>
+          <t>Martin Lešo</t>
+        </is>
+      </c>
+      <c r="X534" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y534" s="2" t="inlineStr"/>
+      <c r="Z534" s="2" t="inlineStr"/>
+      <c r="AA534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martin-le%C5%A1o-8536aa34/?originalSubdomain=sk</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>Valsesia, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>Valsesia, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>11929</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>Budča</t>
+        </is>
+      </c>
+      <c r="F535" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj, Zvolen</t>
+        </is>
+      </c>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>10 Stromová</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>962 33</t>
+        </is>
+      </c>
+      <c r="I535" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vino-obchod.sk</t>
+        </is>
+      </c>
+      <c r="J535" s="2" t="inlineStr"/>
+      <c r="K535" s="2" t="inlineStr"/>
+      <c r="L535" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M535" s="2" t="inlineStr"/>
+      <c r="N535" s="2" t="inlineStr">
+        <is>
+          <t>info@vino-obchod.sk</t>
+        </is>
+      </c>
+      <c r="O535" s="2" t="inlineStr"/>
+      <c r="P535" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q535" s="2" t="inlineStr">
+        <is>
+          <t>36626031</t>
+        </is>
+      </c>
+      <c r="R535" s="2" t="inlineStr"/>
+      <c r="S535" s="2" t="inlineStr"/>
+      <c r="T535" s="2" t="inlineStr"/>
+      <c r="U535" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Valsesiasro</t>
+        </is>
+      </c>
+      <c r="V535" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCAnww4K_EunrRxjdBi6EfvQ</t>
+        </is>
+      </c>
+      <c r="W535" s="2" t="inlineStr">
+        <is>
+          <t>Róbert Mráz</t>
+        </is>
+      </c>
+      <c r="X535" s="2" t="inlineStr">
+        <is>
+          <t>Executive Manager</t>
+        </is>
+      </c>
+      <c r="Y535" s="2" t="inlineStr"/>
+      <c r="Z535" s="2" t="inlineStr"/>
+      <c r="AA535" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/r%C3%B3bert-mr%C3%A1z-718436153/</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>Diskonto S.r.o.</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>Diskonto S.r.o.</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>54205</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>Spišská Nová Ves</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>17 Radlinského</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>052 01</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.diskonto.sk</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="inlineStr"/>
+      <c r="K536" s="2" t="inlineStr"/>
+      <c r="L536" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M536" s="2" t="inlineStr"/>
+      <c r="N536" s="2" t="inlineStr">
+        <is>
+          <t>diskonto@diskonto.sk</t>
+        </is>
+      </c>
+      <c r="O536" s="2" t="inlineStr"/>
+      <c r="P536" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q536" s="2" t="inlineStr">
+        <is>
+          <t>44541473</t>
+        </is>
+      </c>
+      <c r="R536" s="2" t="inlineStr"/>
+      <c r="S536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/diskontoSK/</t>
+        </is>
+      </c>
+      <c r="T536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diskonto_sk/</t>
+        </is>
+      </c>
+      <c r="U536" s="2" t="inlineStr"/>
+      <c r="V536" s="2" t="inlineStr"/>
+      <c r="W536" s="2" t="inlineStr"/>
+      <c r="X536" s="2" t="inlineStr"/>
+      <c r="Y536" s="2" t="inlineStr"/>
+      <c r="Z536" s="2" t="inlineStr"/>
+      <c r="AA536" s="2" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>Vino Sardo S. R. O.</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>Vino Sardo S. R. O.</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>20247</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>Myjava</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>524/19 Nám. M. R. Štefánika</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>907 01</t>
+        </is>
+      </c>
+      <c r="I537" s="2" t="inlineStr">
+        <is>
+          <t>https://vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="J537" s="2" t="inlineStr"/>
+      <c r="K537" s="2" t="inlineStr"/>
+      <c r="L537" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M537" s="2" t="inlineStr"/>
+      <c r="N537" s="2" t="inlineStr">
+        <is>
+          <t>info@vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="O537" s="2" t="inlineStr">
+        <is>
+          <t>+421 34/653 81 85</t>
+        </is>
+      </c>
+      <c r="P537" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q537" s="2" t="inlineStr">
+        <is>
+          <t>46833625</t>
+        </is>
+      </c>
+      <c r="R537" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vino-sardo</t>
+        </is>
+      </c>
+      <c r="S537" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="T537" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinosardo</t>
+        </is>
+      </c>
+      <c r="U537" s="2" t="inlineStr"/>
+      <c r="V537" s="2" t="inlineStr"/>
+      <c r="W537" s="2" t="inlineStr">
+        <is>
+          <t>Veronika Lhotska</t>
+        </is>
+      </c>
+      <c r="X537" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y537" s="2" t="inlineStr"/>
+      <c r="Z537" s="2" t="inlineStr"/>
+      <c r="AA537" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/veronika-lhotska-00808511a</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>Fine Wines S.r.o.</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>Fine Wines S.r.o.</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>11880</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>Staré Grunty 7A</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>841 04</t>
+        </is>
+      </c>
+      <c r="I538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.finewines.sk</t>
+        </is>
+      </c>
+      <c r="J538" s="2" t="inlineStr"/>
+      <c r="K538" s="2" t="inlineStr"/>
+      <c r="L538" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M538" s="2" t="inlineStr"/>
+      <c r="N538" s="2" t="inlineStr">
+        <is>
+          <t>office@finewines.sk</t>
+        </is>
+      </c>
+      <c r="O538" s="2" t="inlineStr"/>
+      <c r="P538" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q538" s="2" t="inlineStr">
+        <is>
+          <t>35752173</t>
+        </is>
+      </c>
+      <c r="R538" s="2" t="inlineStr"/>
+      <c r="S538" s="2" t="inlineStr"/>
+      <c r="T538" s="2" t="inlineStr"/>
+      <c r="U538" s="2" t="inlineStr"/>
+      <c r="V538" s="2" t="inlineStr"/>
+      <c r="W538" s="2" t="inlineStr"/>
+      <c r="X538" s="2" t="inlineStr"/>
+      <c r="Y538" s="2" t="inlineStr"/>
+      <c r="Z538" s="2" t="inlineStr"/>
+      <c r="AA538" s="2" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>Cromatop, S.r.o</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>Cromatop, S.r.o</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>54109</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>Hôrka nad Váhom</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj, Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>Hôrka Nad Váhom 1</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>916 32</t>
+        </is>
+      </c>
+      <c r="I539" s="2" t="inlineStr">
+        <is>
+          <t>https://croma.sk, https://www.flaskomat.sk</t>
+        </is>
+      </c>
+      <c r="J539" s="2" t="inlineStr"/>
+      <c r="K539" s="2" t="inlineStr"/>
+      <c r="L539" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M539" s="2" t="inlineStr"/>
+      <c r="N539" s="2" t="inlineStr">
+        <is>
+          <t>croma@croma.sk</t>
+        </is>
+      </c>
+      <c r="O539" s="2" t="inlineStr"/>
+      <c r="P539" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q539" s="2" t="inlineStr">
+        <is>
+          <t>36338893</t>
+        </is>
+      </c>
+      <c r="R539" s="2" t="inlineStr"/>
+      <c r="S539" s="2" t="inlineStr"/>
+      <c r="T539" s="2" t="inlineStr"/>
+      <c r="U539" s="2" t="inlineStr"/>
+      <c r="V539" s="2" t="inlineStr"/>
+      <c r="W539" s="2" t="inlineStr">
+        <is>
+          <t>Miloslav Králik</t>
+        </is>
+      </c>
+      <c r="X539" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y539" s="2" t="inlineStr"/>
+      <c r="Z539" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA539" s="2" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>Gourmand Sk S. R. O.</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>Gourmand Sk S. R. O.</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>11918</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>12573, 50E Tomášikova</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>https://vinopolis.sk</t>
+        </is>
+      </c>
+      <c r="J540" s="2" t="inlineStr"/>
+      <c r="K540" s="2" t="inlineStr"/>
+      <c r="L540" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M540" s="2" t="inlineStr"/>
+      <c r="N540" s="2" t="inlineStr">
+        <is>
+          <t>info@vinopolis.sk</t>
+        </is>
+      </c>
+      <c r="O540" s="2" t="inlineStr"/>
+      <c r="P540" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q540" s="2" t="inlineStr">
+        <is>
+          <t>46005188</t>
+        </is>
+      </c>
+      <c r="R540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinopolis-sk/</t>
+        </is>
+      </c>
+      <c r="S540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinopolis.sk/</t>
+        </is>
+      </c>
+      <c r="T540" s="2" t="inlineStr"/>
+      <c r="U540" s="2" t="inlineStr"/>
+      <c r="V540" s="2" t="inlineStr"/>
+      <c r="W540" s="2" t="inlineStr">
+        <is>
+          <t>Tibor Körmendi</t>
+        </is>
+      </c>
+      <c r="X540" s="2" t="inlineStr">
+        <is>
+          <t>Responsible</t>
+        </is>
+      </c>
+      <c r="Y540" s="2" t="inlineStr"/>
+      <c r="Z540" s="2" t="inlineStr"/>
+      <c r="AA540" s="2" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>Ll Wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>Ll Wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>42564</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj V</t>
+        </is>
+      </c>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>7 Bosákova</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>851 04</t>
+        </is>
+      </c>
+      <c r="I541" s="2" t="inlineStr">
+        <is>
+          <t>https://www.llwine.sk</t>
+        </is>
+      </c>
+      <c r="J541" s="2" t="inlineStr"/>
+      <c r="K541" s="2" t="inlineStr"/>
+      <c r="L541" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M541" s="2" t="inlineStr"/>
+      <c r="N541" s="2" t="inlineStr">
+        <is>
+          <t>lipka@llwine.sk</t>
+        </is>
+      </c>
+      <c r="O541" s="2" t="inlineStr"/>
+      <c r="P541" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q541" s="2" t="inlineStr">
+        <is>
+          <t>45895813</t>
+        </is>
+      </c>
+      <c r="R541" s="2" t="inlineStr"/>
+      <c r="S541" s="2" t="inlineStr"/>
+      <c r="T541" s="2" t="inlineStr"/>
+      <c r="U541" s="2" t="inlineStr"/>
+      <c r="V541" s="2" t="inlineStr"/>
+      <c r="W541" s="2" t="inlineStr"/>
+      <c r="X541" s="2" t="inlineStr"/>
+      <c r="Y541" s="2" t="inlineStr"/>
+      <c r="Z541" s="2" t="inlineStr"/>
+      <c r="AA541" s="2" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>Barbara Mincíková - Vinopolitan</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Vinopolitan</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>32100</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj I</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>6 Námestie SNP</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>811 06</t>
+        </is>
+      </c>
+      <c r="I542" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinopolitan.sk</t>
+        </is>
+      </c>
+      <c r="J542" s="2" t="inlineStr"/>
+      <c r="K542" s="2" t="inlineStr"/>
+      <c r="L542" s="2" t="inlineStr"/>
+      <c r="M542" s="2" t="inlineStr"/>
+      <c r="N542" s="2" t="inlineStr">
+        <is>
+          <t>info@vinopolitan.sk</t>
+        </is>
+      </c>
+      <c r="O542" s="2" t="inlineStr"/>
+      <c r="P542" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q542" s="2" t="inlineStr">
+        <is>
+          <t>47657235</t>
+        </is>
+      </c>
+      <c r="R542" s="2" t="inlineStr"/>
+      <c r="S542" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinopolitanbratislava/</t>
+        </is>
+      </c>
+      <c r="T542" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinopolitan_wineshop/</t>
+        </is>
+      </c>
+      <c r="U542" s="2" t="inlineStr"/>
+      <c r="V542" s="2" t="inlineStr"/>
+      <c r="W542" s="2" t="inlineStr"/>
+      <c r="X542" s="2" t="inlineStr"/>
+      <c r="Y542" s="2" t="inlineStr"/>
+      <c r="Z542" s="2" t="inlineStr"/>
+      <c r="AA542" s="2" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G543" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I543" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J543" s="2" t="inlineStr"/>
+      <c r="K543" s="2" t="inlineStr"/>
+      <c r="L543" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M543" s="2" t="inlineStr"/>
+      <c r="N543" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O543" s="2" t="inlineStr"/>
+      <c r="P543" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q543" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R543" s="2" t="inlineStr"/>
+      <c r="S543" s="2" t="inlineStr"/>
+      <c r="T543" s="2" t="inlineStr"/>
+      <c r="U543" s="2" t="inlineStr"/>
+      <c r="V543" s="2" t="inlineStr"/>
+      <c r="W543" s="2" t="inlineStr">
+        <is>
+          <t>Štefan Ondrúš</t>
+        </is>
+      </c>
+      <c r="X543" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y543" s="2" t="inlineStr"/>
+      <c r="Z543" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA543" s="2" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I544" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J544" s="2" t="inlineStr"/>
+      <c r="K544" s="2" t="inlineStr"/>
+      <c r="L544" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M544" s="2" t="inlineStr"/>
+      <c r="N544" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O544" s="2" t="inlineStr"/>
+      <c r="P544" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q544" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R544" s="2" t="inlineStr"/>
+      <c r="S544" s="2" t="inlineStr"/>
+      <c r="T544" s="2" t="inlineStr"/>
+      <c r="U544" s="2" t="inlineStr"/>
+      <c r="V544" s="2" t="inlineStr"/>
+      <c r="W544" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Bošanský</t>
+        </is>
+      </c>
+      <c r="X544" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y544" s="2" t="inlineStr"/>
+      <c r="Z544" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA544" s="2" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G545" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I545" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J545" s="2" t="inlineStr"/>
+      <c r="K545" s="2" t="inlineStr"/>
+      <c r="L545" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M545" s="2" t="inlineStr"/>
+      <c r="N545" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O545" s="2" t="inlineStr"/>
+      <c r="P545" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q545" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R545" s="2" t="inlineStr"/>
+      <c r="S545" s="2" t="inlineStr"/>
+      <c r="T545" s="2" t="inlineStr"/>
+      <c r="U545" s="2" t="inlineStr"/>
+      <c r="V545" s="2" t="inlineStr"/>
+      <c r="W545" s="2" t="inlineStr">
+        <is>
+          <t>Pavol Pavlus</t>
+        </is>
+      </c>
+      <c r="X545" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y545" s="2" t="inlineStr"/>
+      <c r="Z545" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA545" s="2" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I546" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J546" s="2" t="inlineStr"/>
+      <c r="K546" s="2" t="inlineStr"/>
+      <c r="L546" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M546" s="2" t="inlineStr"/>
+      <c r="N546" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O546" s="2" t="inlineStr"/>
+      <c r="P546" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q546" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R546" s="2" t="inlineStr"/>
+      <c r="S546" s="2" t="inlineStr"/>
+      <c r="T546" s="2" t="inlineStr"/>
+      <c r="U546" s="2" t="inlineStr"/>
+      <c r="V546" s="2" t="inlineStr"/>
+      <c r="W546" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Vrska</t>
+        </is>
+      </c>
+      <c r="X546" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y546" s="2" t="inlineStr"/>
+      <c r="Z546" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA546" s="2" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G547" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I547" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J547" s="2" t="inlineStr"/>
+      <c r="K547" s="2" t="inlineStr"/>
+      <c r="L547" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M547" s="2" t="inlineStr"/>
+      <c r="N547" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O547" s="2" t="inlineStr"/>
+      <c r="P547" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q547" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R547" s="2" t="inlineStr"/>
+      <c r="S547" s="2" t="inlineStr"/>
+      <c r="T547" s="2" t="inlineStr"/>
+      <c r="U547" s="2" t="inlineStr"/>
+      <c r="V547" s="2" t="inlineStr"/>
+      <c r="W547" s="2" t="inlineStr">
+        <is>
+          <t>Martin Cehula</t>
+        </is>
+      </c>
+      <c r="X547" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y547" s="2" t="inlineStr"/>
+      <c r="Z547" s="2" t="inlineStr"/>
+      <c r="AA547" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA547"/>
+  <dimension ref="A1:AA612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -54460,6 +54460,5947 @@
       <c r="Z547" s="2" t="inlineStr"/>
       <c r="AA547" s="2" t="inlineStr"/>
     </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>Wine Expert, S. R. O.</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>Wine Expert, S. R. O.</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>26921</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava IV</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>8433, 49B Bratislavská</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>841 06</t>
+        </is>
+      </c>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>https://wineexpert.sk</t>
+        </is>
+      </c>
+      <c r="J548" s="2" t="inlineStr"/>
+      <c r="K548" s="2" t="inlineStr"/>
+      <c r="L548" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M548" s="2" t="inlineStr"/>
+      <c r="N548" s="2" t="inlineStr">
+        <is>
+          <t>info@wineexpert.sk</t>
+        </is>
+      </c>
+      <c r="O548" s="2" t="inlineStr"/>
+      <c r="P548" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q548" s="2" t="inlineStr">
+        <is>
+          <t>46214232</t>
+        </is>
+      </c>
+      <c r="R548" s="2" t="inlineStr"/>
+      <c r="S548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineexpert.sk/</t>
+        </is>
+      </c>
+      <c r="T548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineexpert.sk/</t>
+        </is>
+      </c>
+      <c r="U548" s="2" t="inlineStr"/>
+      <c r="V548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@WineExpert</t>
+        </is>
+      </c>
+      <c r="W548" s="2" t="inlineStr">
+        <is>
+          <t>David Winter</t>
+        </is>
+      </c>
+      <c r="X548" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y548" s="2" t="inlineStr"/>
+      <c r="Z548" s="2" t="inlineStr"/>
+      <c r="AA548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/winter-david-4437062a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>Kubbo Select</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>Kubbo Select</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>20093</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>Košice</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr"/>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>Rastislavova 88</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr"/>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kubboselect.sk</t>
+        </is>
+      </c>
+      <c r="J549" s="2" t="inlineStr"/>
+      <c r="K549" s="2" t="inlineStr"/>
+      <c r="L549" s="2" t="inlineStr"/>
+      <c r="M549" s="2" t="inlineStr"/>
+      <c r="N549" s="2" t="inlineStr">
+        <is>
+          <t>info@kubboselect.sk</t>
+        </is>
+      </c>
+      <c r="O549" s="2" t="inlineStr"/>
+      <c r="P549" s="2" t="inlineStr"/>
+      <c r="Q549" s="2" t="inlineStr"/>
+      <c r="R549" s="2" t="inlineStr"/>
+      <c r="S549" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kubboselect</t>
+        </is>
+      </c>
+      <c r="T549" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kubboselect</t>
+        </is>
+      </c>
+      <c r="U549" s="2" t="inlineStr"/>
+      <c r="V549" s="2" t="inlineStr"/>
+      <c r="W549" s="2" t="inlineStr"/>
+      <c r="X549" s="2" t="inlineStr"/>
+      <c r="Y549" s="2" t="inlineStr"/>
+      <c r="Z549" s="2" t="inlineStr"/>
+      <c r="AA549" s="2" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>Víno Az, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>Víno Az, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>21731</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>1069, 4 Pivovarská</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>010 01</t>
+        </is>
+      </c>
+      <c r="I550" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoaz.sk</t>
+        </is>
+      </c>
+      <c r="J550" s="2" t="inlineStr"/>
+      <c r="K550" s="2" t="inlineStr"/>
+      <c r="L550" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M550" s="2" t="inlineStr"/>
+      <c r="N550" s="2" t="inlineStr">
+        <is>
+          <t>vanko@vinoaz.sk</t>
+        </is>
+      </c>
+      <c r="O550" s="2" t="inlineStr"/>
+      <c r="P550" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q550" s="2" t="inlineStr">
+        <is>
+          <t>44009275</t>
+        </is>
+      </c>
+      <c r="R550" s="2" t="inlineStr"/>
+      <c r="S550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Víno-AZ-sro-452044938181291</t>
+        </is>
+      </c>
+      <c r="T550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoaz_s.r.o/</t>
+        </is>
+      </c>
+      <c r="U550" s="2" t="inlineStr"/>
+      <c r="V550" s="2" t="inlineStr"/>
+      <c r="W550" s="2" t="inlineStr"/>
+      <c r="X550" s="2" t="inlineStr"/>
+      <c r="Y550" s="2" t="inlineStr"/>
+      <c r="Z550" s="2" t="inlineStr"/>
+      <c r="AA550" s="2" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>Bodnar Vino Olio Ecoproducts</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>Bodnar Vino Olio Ecoproducts</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>43488</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>Kosice</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>Kosický</t>
+        </is>
+      </c>
+      <c r="G551" s="2" t="inlineStr">
+        <is>
+          <t>Lesná 25</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>040 01</t>
+        </is>
+      </c>
+      <c r="I551" s="2" t="inlineStr">
+        <is>
+          <t>http://ekoprodukty.sk</t>
+        </is>
+      </c>
+      <c r="J551" s="2" t="inlineStr"/>
+      <c r="K551" s="2" t="inlineStr"/>
+      <c r="L551" s="2" t="inlineStr"/>
+      <c r="M551" s="2" t="inlineStr"/>
+      <c r="N551" s="2" t="inlineStr">
+        <is>
+          <t>mail@ekoprodukty.sk</t>
+        </is>
+      </c>
+      <c r="O551" s="2" t="inlineStr"/>
+      <c r="P551" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q551" s="2" t="inlineStr">
+        <is>
+          <t>17159440</t>
+        </is>
+      </c>
+      <c r="R551" s="2" t="inlineStr"/>
+      <c r="S551" s="2" t="inlineStr"/>
+      <c r="T551" s="2" t="inlineStr"/>
+      <c r="U551" s="2" t="inlineStr"/>
+      <c r="V551" s="2" t="inlineStr"/>
+      <c r="W551" s="2" t="inlineStr"/>
+      <c r="X551" s="2" t="inlineStr"/>
+      <c r="Y551" s="2" t="inlineStr"/>
+      <c r="Z551" s="2" t="inlineStr"/>
+      <c r="AA551" s="2" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>Caste Sk, A. S.</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>Caste Sk, A. S.</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>54751</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>Juh</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj, Košice IV</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>1 Jazerná</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>040 12</t>
+        </is>
+      </c>
+      <c r="I552" s="2" t="inlineStr">
+        <is>
+          <t>https://caste.sk</t>
+        </is>
+      </c>
+      <c r="J552" s="2" t="inlineStr"/>
+      <c r="K552" s="2" t="inlineStr"/>
+      <c r="L552" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M552" s="2" t="inlineStr"/>
+      <c r="N552" s="2" t="inlineStr">
+        <is>
+          <t>libiak@caste.sk</t>
+        </is>
+      </c>
+      <c r="O552" s="2" t="inlineStr"/>
+      <c r="P552" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q552" s="2" t="inlineStr">
+        <is>
+          <t>52292568</t>
+        </is>
+      </c>
+      <c r="R552" s="2" t="inlineStr"/>
+      <c r="S552" s="2" t="inlineStr"/>
+      <c r="T552" s="2" t="inlineStr"/>
+      <c r="U552" s="2" t="inlineStr"/>
+      <c r="V552" s="2" t="inlineStr"/>
+      <c r="W552" s="2" t="inlineStr">
+        <is>
+          <t>Cakoci Stefan</t>
+        </is>
+      </c>
+      <c r="X552" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y552" s="2" t="inlineStr"/>
+      <c r="Z552" s="2" t="inlineStr"/>
+      <c r="AA552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cakoci-stefan-0000ba170/</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>Caste Sk, A. S.</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>Caste Sk, A. S.</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>54751</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>Juh</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj, Košice IV</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="inlineStr">
+        <is>
+          <t>1 Jazerná</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>040 12</t>
+        </is>
+      </c>
+      <c r="I553" s="2" t="inlineStr">
+        <is>
+          <t>https://caste.sk</t>
+        </is>
+      </c>
+      <c r="J553" s="2" t="inlineStr"/>
+      <c r="K553" s="2" t="inlineStr"/>
+      <c r="L553" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M553" s="2" t="inlineStr"/>
+      <c r="N553" s="2" t="inlineStr">
+        <is>
+          <t>libiak@caste.sk</t>
+        </is>
+      </c>
+      <c r="O553" s="2" t="inlineStr"/>
+      <c r="P553" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q553" s="2" t="inlineStr">
+        <is>
+          <t>52292568</t>
+        </is>
+      </c>
+      <c r="R553" s="2" t="inlineStr"/>
+      <c r="S553" s="2" t="inlineStr"/>
+      <c r="T553" s="2" t="inlineStr"/>
+      <c r="U553" s="2" t="inlineStr"/>
+      <c r="V553" s="2" t="inlineStr"/>
+      <c r="W553" s="2" t="inlineStr">
+        <is>
+          <t>Rastislav Libiak</t>
+        </is>
+      </c>
+      <c r="X553" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y553" s="2" t="inlineStr"/>
+      <c r="Z553" s="2" t="inlineStr"/>
+      <c r="AA553" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rastislav-libiak-15371a96/</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>Tip Top Gastro S.r.o</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>Tip Top Gastro S.r.o</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>108850</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>Biely Kostol</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj, Trnava</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>5458, 1 Pionierske námestie</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>919 34</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiptopgastro.sk</t>
+        </is>
+      </c>
+      <c r="J554" s="2" t="inlineStr"/>
+      <c r="K554" s="2" t="inlineStr"/>
+      <c r="L554" s="2" t="inlineStr"/>
+      <c r="M554" s="2" t="inlineStr"/>
+      <c r="N554" s="2" t="inlineStr">
+        <is>
+          <t>objednavky@tiptopgastro.sk</t>
+        </is>
+      </c>
+      <c r="O554" s="2" t="inlineStr">
+        <is>
+          <t>+421 33 533 33 35</t>
+        </is>
+      </c>
+      <c r="P554" s="2" t="inlineStr"/>
+      <c r="Q554" s="2" t="inlineStr"/>
+      <c r="R554" s="2" t="inlineStr"/>
+      <c r="S554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TipTopGastro/</t>
+        </is>
+      </c>
+      <c r="T554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tiptopgastro</t>
+        </is>
+      </c>
+      <c r="U554" s="2" t="inlineStr"/>
+      <c r="V554" s="2" t="inlineStr"/>
+      <c r="W554" s="2" t="inlineStr"/>
+      <c r="X554" s="2" t="inlineStr"/>
+      <c r="Y554" s="2" t="inlineStr"/>
+      <c r="Z554" s="2" t="inlineStr"/>
+      <c r="AA554" s="2" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>Augera S.r.o.</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>Augera S.r.o.</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>56911</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>Modra</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Pezinok</t>
+        </is>
+      </c>
+      <c r="G555" s="2" t="inlineStr">
+        <is>
+          <t>Harmónia 3590</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>900 01</t>
+        </is>
+      </c>
+      <c r="I555" s="2" t="inlineStr">
+        <is>
+          <t>http://vino-augera.sk</t>
+        </is>
+      </c>
+      <c r="J555" s="2" t="inlineStr"/>
+      <c r="K555" s="2" t="inlineStr"/>
+      <c r="L555" s="2" t="inlineStr"/>
+      <c r="M555" s="2" t="inlineStr"/>
+      <c r="N555" s="2" t="inlineStr">
+        <is>
+          <t>augera@augera.sk</t>
+        </is>
+      </c>
+      <c r="O555" s="2" t="inlineStr"/>
+      <c r="P555" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q555" s="2" t="inlineStr">
+        <is>
+          <t>35895578</t>
+        </is>
+      </c>
+      <c r="R555" s="2" t="inlineStr"/>
+      <c r="S555" s="2" t="inlineStr"/>
+      <c r="T555" s="2" t="inlineStr"/>
+      <c r="U555" s="2" t="inlineStr"/>
+      <c r="V555" s="2" t="inlineStr"/>
+      <c r="W555" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Werchol</t>
+        </is>
+      </c>
+      <c r="X555" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y555" s="2" t="inlineStr"/>
+      <c r="Z555" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA555" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/k-miroslav-werchol-aacute-8529ba40</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>Augera S.r.o.</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>Augera S.r.o.</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>56911</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>Modra</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Pezinok</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>Harmónia 3590</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>900 01</t>
+        </is>
+      </c>
+      <c r="I556" s="2" t="inlineStr">
+        <is>
+          <t>http://vino-augera.sk</t>
+        </is>
+      </c>
+      <c r="J556" s="2" t="inlineStr"/>
+      <c r="K556" s="2" t="inlineStr"/>
+      <c r="L556" s="2" t="inlineStr"/>
+      <c r="M556" s="2" t="inlineStr"/>
+      <c r="N556" s="2" t="inlineStr">
+        <is>
+          <t>augera@augera.sk</t>
+        </is>
+      </c>
+      <c r="O556" s="2" t="inlineStr"/>
+      <c r="P556" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q556" s="2" t="inlineStr">
+        <is>
+          <t>35895578</t>
+        </is>
+      </c>
+      <c r="R556" s="2" t="inlineStr"/>
+      <c r="S556" s="2" t="inlineStr"/>
+      <c r="T556" s="2" t="inlineStr"/>
+      <c r="U556" s="2" t="inlineStr"/>
+      <c r="V556" s="2" t="inlineStr"/>
+      <c r="W556" s="2" t="inlineStr">
+        <is>
+          <t>Gabriela Wercholáková</t>
+        </is>
+      </c>
+      <c r="X556" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y556" s="2" t="inlineStr"/>
+      <c r="Z556" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA556" s="2" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>Grandi Vini, S. R. O.</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>Grandi Vini, S. R. O.</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>36311</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G557" s="2" t="inlineStr">
+        <is>
+          <t>16 Škultétyho</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="inlineStr">
+        <is>
+          <t>831 03</t>
+        </is>
+      </c>
+      <c r="I557" s="2" t="inlineStr">
+        <is>
+          <t>https://grandivini.eu</t>
+        </is>
+      </c>
+      <c r="J557" s="2" t="inlineStr"/>
+      <c r="K557" s="2" t="inlineStr"/>
+      <c r="L557" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M557" s="2" t="inlineStr"/>
+      <c r="N557" s="2" t="inlineStr">
+        <is>
+          <t>grandivini1@gmail.com</t>
+        </is>
+      </c>
+      <c r="O557" s="2" t="inlineStr"/>
+      <c r="P557" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q557" s="2" t="inlineStr">
+        <is>
+          <t>36779610</t>
+        </is>
+      </c>
+      <c r="R557" s="2" t="inlineStr"/>
+      <c r="S557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/grandivini.eu/</t>
+        </is>
+      </c>
+      <c r="T557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grandivini_eu/</t>
+        </is>
+      </c>
+      <c r="U557" s="2" t="inlineStr"/>
+      <c r="V557" s="2" t="inlineStr"/>
+      <c r="W557" s="2" t="inlineStr">
+        <is>
+          <t>Alex Pothe</t>
+        </is>
+      </c>
+      <c r="X557" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y557" s="2" t="inlineStr"/>
+      <c r="Z557" s="2" t="inlineStr"/>
+      <c r="AA557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alex-pothe-396620179/?originalSubdomain=sk</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>Bottleshop Sk, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>Bottleshop Sk, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>20064</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj I</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>2 Tallerova</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>811 02</t>
+        </is>
+      </c>
+      <c r="I558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bottleshop.sk</t>
+        </is>
+      </c>
+      <c r="J558" s="2" t="inlineStr"/>
+      <c r="K558" s="2" t="inlineStr"/>
+      <c r="L558" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M558" s="2" t="inlineStr"/>
+      <c r="N558" s="2" t="inlineStr">
+        <is>
+          <t>info@bottleshop.sk</t>
+        </is>
+      </c>
+      <c r="O558" s="2" t="inlineStr"/>
+      <c r="P558" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q558" s="2" t="inlineStr">
+        <is>
+          <t>45906149</t>
+        </is>
+      </c>
+      <c r="R558" s="2" t="inlineStr"/>
+      <c r="S558" s="2" t="inlineStr"/>
+      <c r="T558" s="2" t="inlineStr"/>
+      <c r="U558" s="2" t="inlineStr"/>
+      <c r="V558" s="2" t="inlineStr"/>
+      <c r="W558" s="2" t="inlineStr">
+        <is>
+          <t>Juraj Sketa</t>
+        </is>
+      </c>
+      <c r="X558" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y558" s="2" t="inlineStr"/>
+      <c r="Z558" s="2" t="inlineStr"/>
+      <c r="AA558" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/juraj-sketa-02a61518</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>Finest Rum Store, S. R. O.</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>Finest Rum Store, S. R. O.</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>27125</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>Miloslavov</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Senec</t>
+        </is>
+      </c>
+      <c r="G559" s="2" t="inlineStr">
+        <is>
+          <t>1999 Obchodná</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>900 42</t>
+        </is>
+      </c>
+      <c r="I559" s="2" t="inlineStr">
+        <is>
+          <t>https://dobryrum.sk</t>
+        </is>
+      </c>
+      <c r="J559" s="2" t="inlineStr"/>
+      <c r="K559" s="2" t="inlineStr"/>
+      <c r="L559" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M559" s="2" t="inlineStr"/>
+      <c r="N559" s="2" t="inlineStr">
+        <is>
+          <t>info@dobryrum.sk</t>
+        </is>
+      </c>
+      <c r="O559" s="2" t="inlineStr"/>
+      <c r="P559" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q559" s="2" t="inlineStr">
+        <is>
+          <t>50559541</t>
+        </is>
+      </c>
+      <c r="R559" s="2" t="inlineStr"/>
+      <c r="S559" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dobryrum</t>
+        </is>
+      </c>
+      <c r="T559" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dobry_rum/</t>
+        </is>
+      </c>
+      <c r="U559" s="2" t="inlineStr"/>
+      <c r="V559" s="2" t="inlineStr"/>
+      <c r="W559" s="2" t="inlineStr"/>
+      <c r="X559" s="2" t="inlineStr"/>
+      <c r="Y559" s="2" t="inlineStr"/>
+      <c r="Z559" s="2" t="inlineStr"/>
+      <c r="AA559" s="2" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>Topwine.sk</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>Topwine.sk</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>11930</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>Budča</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj, Zvolen</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr">
+        <is>
+          <t>463 Stromová</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>962 33</t>
+        </is>
+      </c>
+      <c r="I560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.topwine.sk</t>
+        </is>
+      </c>
+      <c r="J560" s="2" t="inlineStr"/>
+      <c r="K560" s="2" t="inlineStr"/>
+      <c r="L560" s="2" t="inlineStr"/>
+      <c r="M560" s="2" t="inlineStr"/>
+      <c r="N560" s="2" t="inlineStr">
+        <is>
+          <t>info@topwine.sk</t>
+        </is>
+      </c>
+      <c r="O560" s="2" t="inlineStr"/>
+      <c r="P560" s="2" t="inlineStr"/>
+      <c r="Q560" s="2" t="inlineStr"/>
+      <c r="R560" s="2" t="inlineStr"/>
+      <c r="S560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Topwinesk-61550639900124/</t>
+        </is>
+      </c>
+      <c r="T560" s="2" t="inlineStr"/>
+      <c r="U560" s="2" t="inlineStr"/>
+      <c r="V560" s="2" t="inlineStr"/>
+      <c r="W560" s="2" t="inlineStr"/>
+      <c r="X560" s="2" t="inlineStr"/>
+      <c r="Y560" s="2" t="inlineStr"/>
+      <c r="Z560" s="2" t="inlineStr"/>
+      <c r="AA560" s="2" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>Shop4wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>Shop4wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>11926</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>Piešťany</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj</t>
+        </is>
+      </c>
+      <c r="G561" s="2" t="inlineStr">
+        <is>
+          <t>2149 Hodžova</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="inlineStr">
+        <is>
+          <t>921 01</t>
+        </is>
+      </c>
+      <c r="I561" s="2" t="inlineStr">
+        <is>
+          <t>https://shop4wine.sk</t>
+        </is>
+      </c>
+      <c r="J561" s="2" t="inlineStr"/>
+      <c r="K561" s="2" t="inlineStr"/>
+      <c r="L561" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M561" s="2" t="inlineStr"/>
+      <c r="N561" s="2" t="inlineStr">
+        <is>
+          <t>info@shop4wine.sk</t>
+        </is>
+      </c>
+      <c r="O561" s="2" t="inlineStr"/>
+      <c r="P561" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q561" s="2" t="inlineStr">
+        <is>
+          <t>45909911</t>
+        </is>
+      </c>
+      <c r="R561" s="2" t="inlineStr"/>
+      <c r="S561" s="2" t="inlineStr"/>
+      <c r="T561" s="2" t="inlineStr"/>
+      <c r="U561" s="2" t="inlineStr"/>
+      <c r="V561" s="2" t="inlineStr"/>
+      <c r="W561" s="2" t="inlineStr"/>
+      <c r="X561" s="2" t="inlineStr"/>
+      <c r="Y561" s="2" t="inlineStr"/>
+      <c r="Z561" s="2" t="inlineStr"/>
+      <c r="AA561" s="2" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>Komfos Prešov, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>Komfos Prešov, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>103173</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>Ľubotice</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj, Prešov</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>2 Ľubochnianska</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="inlineStr">
+        <is>
+          <t>080 06</t>
+        </is>
+      </c>
+      <c r="I562" s="2" t="inlineStr">
+        <is>
+          <t>https://cbashop.sk, https://www.komfos.sk</t>
+        </is>
+      </c>
+      <c r="J562" s="2" t="inlineStr"/>
+      <c r="K562" s="2" t="inlineStr"/>
+      <c r="L562" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="M562" s="2" t="inlineStr"/>
+      <c r="N562" s="2" t="inlineStr">
+        <is>
+          <t>office@komfos.sk</t>
+        </is>
+      </c>
+      <c r="O562" s="2" t="inlineStr"/>
+      <c r="P562" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q562" s="2" t="inlineStr">
+        <is>
+          <t>36454184</t>
+        </is>
+      </c>
+      <c r="R562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cba-komfos/</t>
+        </is>
+      </c>
+      <c r="S562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CBAKomfos</t>
+        </is>
+      </c>
+      <c r="T562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cbakomfos/</t>
+        </is>
+      </c>
+      <c r="U562" s="2" t="inlineStr"/>
+      <c r="V562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@komfospresovs.r.o.-velkoob8582/</t>
+        </is>
+      </c>
+      <c r="W562" s="2" t="inlineStr">
+        <is>
+          <t>Slavko Koncar</t>
+        </is>
+      </c>
+      <c r="X562" s="2" t="inlineStr">
+        <is>
+          <t>Area Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y562" s="2" t="inlineStr"/>
+      <c r="Z562" s="2" t="inlineStr"/>
+      <c r="AA562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/slavko-koncar-2817a726/</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>Alko90</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>Alko90</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>29347</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>Most pri Bratislave</t>
+        </is>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Senec</t>
+        </is>
+      </c>
+      <c r="G563" s="2" t="inlineStr">
+        <is>
+          <t>775, Bratislavská</t>
+        </is>
+      </c>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>900 46</t>
+        </is>
+      </c>
+      <c r="I563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alko90.sk</t>
+        </is>
+      </c>
+      <c r="J563" s="2" t="inlineStr"/>
+      <c r="K563" s="2" t="inlineStr"/>
+      <c r="L563" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M563" s="2" t="inlineStr"/>
+      <c r="N563" s="2" t="inlineStr">
+        <is>
+          <t>info@alko90.sk</t>
+        </is>
+      </c>
+      <c r="O563" s="2" t="inlineStr"/>
+      <c r="P563" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q563" s="2" t="inlineStr">
+        <is>
+          <t>50484800</t>
+        </is>
+      </c>
+      <c r="R563" s="2" t="inlineStr"/>
+      <c r="S563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/alko90sk/</t>
+        </is>
+      </c>
+      <c r="T563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alko90sk/</t>
+        </is>
+      </c>
+      <c r="U563" s="2" t="inlineStr"/>
+      <c r="V563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@alko90sk/</t>
+        </is>
+      </c>
+      <c r="W563" s="2" t="inlineStr">
+        <is>
+          <t>Andrej Slavik</t>
+        </is>
+      </c>
+      <c r="X563" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y563" s="2" t="inlineStr"/>
+      <c r="Z563" s="2" t="inlineStr"/>
+      <c r="AA563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrej-sl%C3%A1vik-91808758/</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>27285</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>18 Jakuba Hašku</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="J564" s="2" t="inlineStr"/>
+      <c r="K564" s="2" t="inlineStr"/>
+      <c r="L564" s="2" t="inlineStr"/>
+      <c r="M564" s="2" t="inlineStr"/>
+      <c r="N564" s="2" t="inlineStr">
+        <is>
+          <t>hornisova.maria@vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="O564" s="2" t="inlineStr"/>
+      <c r="P564" s="2" t="inlineStr"/>
+      <c r="Q564" s="2" t="inlineStr"/>
+      <c r="R564" s="2" t="inlineStr"/>
+      <c r="S564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekahornis/</t>
+        </is>
+      </c>
+      <c r="T564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_hornis/</t>
+        </is>
+      </c>
+      <c r="U564" s="2" t="inlineStr"/>
+      <c r="V564" s="2" t="inlineStr"/>
+      <c r="W564" s="2" t="inlineStr">
+        <is>
+          <t>Viliam Horniš</t>
+        </is>
+      </c>
+      <c r="X564" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y564" s="2" t="inlineStr"/>
+      <c r="Z564" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA564" s="2" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Horniš</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>27285</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>18 Jakuba Hašku</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="J565" s="2" t="inlineStr"/>
+      <c r="K565" s="2" t="inlineStr"/>
+      <c r="L565" s="2" t="inlineStr"/>
+      <c r="M565" s="2" t="inlineStr"/>
+      <c r="N565" s="2" t="inlineStr">
+        <is>
+          <t>hornisova.maria@vinotekahornis.sk</t>
+        </is>
+      </c>
+      <c r="O565" s="2" t="inlineStr"/>
+      <c r="P565" s="2" t="inlineStr"/>
+      <c r="Q565" s="2" t="inlineStr"/>
+      <c r="R565" s="2" t="inlineStr"/>
+      <c r="S565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekahornis/</t>
+        </is>
+      </c>
+      <c r="T565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_hornis/</t>
+        </is>
+      </c>
+      <c r="U565" s="2" t="inlineStr"/>
+      <c r="V565" s="2" t="inlineStr"/>
+      <c r="W565" s="2" t="inlineStr">
+        <is>
+          <t>Mária Hornišová</t>
+        </is>
+      </c>
+      <c r="X565" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y565" s="2" t="inlineStr"/>
+      <c r="Z565" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA565" s="2" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>Radničná Vinotéka Pezinok</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>Radničná Vinotéka Pezinok</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>41106</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>Pezinok</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>1, 1 M. R. Štefánika</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="inlineStr">
+        <is>
+          <t>902 01</t>
+        </is>
+      </c>
+      <c r="I566" s="2" t="inlineStr">
+        <is>
+          <t>http://vinoradnica.sk, https://ratuzky.sk</t>
+        </is>
+      </c>
+      <c r="J566" s="2" t="inlineStr"/>
+      <c r="K566" s="2" t="inlineStr"/>
+      <c r="L566" s="2" t="inlineStr"/>
+      <c r="M566" s="2" t="inlineStr"/>
+      <c r="N566" s="2" t="inlineStr">
+        <is>
+          <t>info@vinoradnica.sk</t>
+        </is>
+      </c>
+      <c r="O566" s="2" t="inlineStr"/>
+      <c r="P566" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q566" s="2" t="inlineStr">
+        <is>
+          <t>34675493</t>
+        </is>
+      </c>
+      <c r="R566" s="2" t="inlineStr"/>
+      <c r="S566" s="2" t="inlineStr"/>
+      <c r="T566" s="2" t="inlineStr"/>
+      <c r="U566" s="2" t="inlineStr"/>
+      <c r="V566" s="2" t="inlineStr"/>
+      <c r="W566" s="2" t="inlineStr"/>
+      <c r="X566" s="2" t="inlineStr"/>
+      <c r="Y566" s="2" t="inlineStr"/>
+      <c r="Z566" s="2" t="inlineStr"/>
+      <c r="AA566" s="2" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka One More</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka One More</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>21140</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>10301, 108 Vajnorská</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I567" s="2" t="inlineStr">
+        <is>
+          <t>https://onemore.sk</t>
+        </is>
+      </c>
+      <c r="J567" s="2" t="inlineStr"/>
+      <c r="K567" s="2" t="inlineStr"/>
+      <c r="L567" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M567" s="2" t="inlineStr"/>
+      <c r="N567" s="2" t="inlineStr">
+        <is>
+          <t>info@onemore.sk</t>
+        </is>
+      </c>
+      <c r="O567" s="2" t="inlineStr"/>
+      <c r="P567" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q567" s="2" t="inlineStr">
+        <is>
+          <t>46896961</t>
+        </is>
+      </c>
+      <c r="R567" s="2" t="inlineStr"/>
+      <c r="S567" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/onemore.wine/</t>
+        </is>
+      </c>
+      <c r="T567" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onemore_wine/</t>
+        </is>
+      </c>
+      <c r="U567" s="2" t="inlineStr"/>
+      <c r="V567" s="2" t="inlineStr"/>
+      <c r="W567" s="2" t="inlineStr"/>
+      <c r="X567" s="2" t="inlineStr"/>
+      <c r="Y567" s="2" t="inlineStr"/>
+      <c r="Z567" s="2" t="inlineStr"/>
+      <c r="AA567" s="2" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>40555</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>Laurinská 210/8</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>811 05</t>
+        </is>
+      </c>
+      <c r="I568" s="2" t="inlineStr">
+        <is>
+          <t>https://bwd.sk</t>
+        </is>
+      </c>
+      <c r="J568" s="2" t="inlineStr"/>
+      <c r="K568" s="2" t="inlineStr"/>
+      <c r="L568" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M568" s="2" t="inlineStr"/>
+      <c r="N568" s="2" t="inlineStr">
+        <is>
+          <t>info@bwd.sk</t>
+        </is>
+      </c>
+      <c r="O568" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/207 824 67</t>
+        </is>
+      </c>
+      <c r="P568" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q568" s="2" t="inlineStr">
+        <is>
+          <t>50444271</t>
+        </is>
+      </c>
+      <c r="R568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/best-wines-distribution/</t>
+        </is>
+      </c>
+      <c r="S568" s="2" t="inlineStr"/>
+      <c r="T568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bwd.sk/</t>
+        </is>
+      </c>
+      <c r="U568" s="2" t="inlineStr"/>
+      <c r="V568" s="2" t="inlineStr"/>
+      <c r="W568" s="2" t="inlineStr">
+        <is>
+          <t>Marco Masutti</t>
+        </is>
+      </c>
+      <c r="X568" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y568" s="2" t="inlineStr"/>
+      <c r="Z568" s="2" t="inlineStr"/>
+      <c r="AA568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marco-masutti-056b12203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>B.w.d. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>40555</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>Laurinská 210/8</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>811 05</t>
+        </is>
+      </c>
+      <c r="I569" s="2" t="inlineStr">
+        <is>
+          <t>https://bwd.sk</t>
+        </is>
+      </c>
+      <c r="J569" s="2" t="inlineStr"/>
+      <c r="K569" s="2" t="inlineStr"/>
+      <c r="L569" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M569" s="2" t="inlineStr"/>
+      <c r="N569" s="2" t="inlineStr">
+        <is>
+          <t>info@bwd.sk</t>
+        </is>
+      </c>
+      <c r="O569" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/207 824 67</t>
+        </is>
+      </c>
+      <c r="P569" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q569" s="2" t="inlineStr">
+        <is>
+          <t>50444271</t>
+        </is>
+      </c>
+      <c r="R569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/best-wines-distribution/</t>
+        </is>
+      </c>
+      <c r="S569" s="2" t="inlineStr"/>
+      <c r="T569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bwd.sk/</t>
+        </is>
+      </c>
+      <c r="U569" s="2" t="inlineStr"/>
+      <c r="V569" s="2" t="inlineStr"/>
+      <c r="W569" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Kollar</t>
+        </is>
+      </c>
+      <c r="X569" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier/ Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y569" s="2" t="inlineStr"/>
+      <c r="Z569" s="2" t="inlineStr"/>
+      <c r="AA569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gabriel-kollar-5996183a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka André, Sro</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka André, Sro</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>41101</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>1 Obchodné centrum Turiec</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="inlineStr">
+        <is>
+          <t>036 01</t>
+        </is>
+      </c>
+      <c r="I570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoteka-andre.sk</t>
+        </is>
+      </c>
+      <c r="J570" s="2" t="inlineStr"/>
+      <c r="K570" s="2" t="inlineStr"/>
+      <c r="L570" s="2" t="inlineStr"/>
+      <c r="M570" s="2" t="inlineStr"/>
+      <c r="N570" s="2" t="inlineStr">
+        <is>
+          <t>info@vinoteka-andre.sk</t>
+        </is>
+      </c>
+      <c r="O570" s="2" t="inlineStr"/>
+      <c r="P570" s="2" t="inlineStr"/>
+      <c r="Q570" s="2" t="inlineStr"/>
+      <c r="R570" s="2" t="inlineStr"/>
+      <c r="S570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinotekaAndre/</t>
+        </is>
+      </c>
+      <c r="T570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotekaandre/</t>
+        </is>
+      </c>
+      <c r="U570" s="2" t="inlineStr"/>
+      <c r="V570" s="2" t="inlineStr"/>
+      <c r="W570" s="2" t="inlineStr"/>
+      <c r="X570" s="2" t="inlineStr"/>
+      <c r="Y570" s="2" t="inlineStr"/>
+      <c r="Z570" s="2" t="inlineStr"/>
+      <c r="AA570" s="2" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>108846</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="inlineStr">
+        <is>
+          <t>Svit</t>
+        </is>
+      </c>
+      <c r="F571" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj, Poprad</t>
+        </is>
+      </c>
+      <c r="G571" s="2" t="inlineStr">
+        <is>
+          <t>208, 156 Mierová</t>
+        </is>
+      </c>
+      <c r="H571" s="2" t="inlineStr">
+        <is>
+          <t>059 21</t>
+        </is>
+      </c>
+      <c r="I571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="J571" s="2" t="inlineStr"/>
+      <c r="K571" s="2" t="inlineStr"/>
+      <c r="L571" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M571" s="2" t="inlineStr"/>
+      <c r="N571" s="2" t="inlineStr">
+        <is>
+          <t>info@jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="O571" s="2" t="inlineStr">
+        <is>
+          <t>+421 52 123 45 67</t>
+        </is>
+      </c>
+      <c r="P571" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q571" s="2" t="inlineStr">
+        <is>
+          <t>46814973</t>
+        </is>
+      </c>
+      <c r="R571" s="2" t="inlineStr"/>
+      <c r="S571" s="2" t="inlineStr"/>
+      <c r="T571" s="2" t="inlineStr"/>
+      <c r="U571" s="2" t="inlineStr"/>
+      <c r="V571" s="2" t="inlineStr"/>
+      <c r="W571" s="2" t="inlineStr">
+        <is>
+          <t>Jan Filipsky</t>
+        </is>
+      </c>
+      <c r="X571" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y571" s="2" t="inlineStr"/>
+      <c r="Z571" s="2" t="inlineStr"/>
+      <c r="AA571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jan-filipsky-a96a5345/</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>Jf Drinks S.r.o.</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>108846</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>Svit</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj, Poprad</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>208, 156 Mierová</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="inlineStr">
+        <is>
+          <t>059 21</t>
+        </is>
+      </c>
+      <c r="I572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="J572" s="2" t="inlineStr"/>
+      <c r="K572" s="2" t="inlineStr"/>
+      <c r="L572" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M572" s="2" t="inlineStr"/>
+      <c r="N572" s="2" t="inlineStr">
+        <is>
+          <t>info@jfdrinks.sk</t>
+        </is>
+      </c>
+      <c r="O572" s="2" t="inlineStr">
+        <is>
+          <t>+421 52 123 45 67</t>
+        </is>
+      </c>
+      <c r="P572" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q572" s="2" t="inlineStr">
+        <is>
+          <t>46814973</t>
+        </is>
+      </c>
+      <c r="R572" s="2" t="inlineStr"/>
+      <c r="S572" s="2" t="inlineStr"/>
+      <c r="T572" s="2" t="inlineStr"/>
+      <c r="U572" s="2" t="inlineStr"/>
+      <c r="V572" s="2" t="inlineStr"/>
+      <c r="W572" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Filipský</t>
+        </is>
+      </c>
+      <c r="X572" s="2" t="inlineStr">
+        <is>
+          <t>Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y572" s="2" t="inlineStr"/>
+      <c r="Z572" s="2" t="inlineStr"/>
+      <c r="AA572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-filipsk%C3%BD-73477383/</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>Reming, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>Reming, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>47015</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="inlineStr">
+        <is>
+          <t>Liptovsky Mikulas</t>
+        </is>
+      </c>
+      <c r="F573" s="2" t="inlineStr"/>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>Moyzesova No. 4358/9</t>
+        </is>
+      </c>
+      <c r="H573" s="2" t="inlineStr">
+        <is>
+          <t>031 01</t>
+        </is>
+      </c>
+      <c r="I573" s="2" t="inlineStr">
+        <is>
+          <t>https://reming-sk.com</t>
+        </is>
+      </c>
+      <c r="J573" s="2" t="inlineStr"/>
+      <c r="K573" s="2" t="inlineStr"/>
+      <c r="L573" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M573" s="2" t="inlineStr"/>
+      <c r="N573" s="2" t="inlineStr">
+        <is>
+          <t>office@reming-sk.com</t>
+        </is>
+      </c>
+      <c r="O573" s="2" t="inlineStr"/>
+      <c r="P573" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q573" s="2" t="inlineStr">
+        <is>
+          <t>45605220</t>
+        </is>
+      </c>
+      <c r="R573" s="2" t="inlineStr"/>
+      <c r="S573" s="2" t="inlineStr"/>
+      <c r="T573" s="2" t="inlineStr"/>
+      <c r="U573" s="2" t="inlineStr"/>
+      <c r="V573" s="2" t="inlineStr"/>
+      <c r="W573" s="2" t="inlineStr"/>
+      <c r="X573" s="2" t="inlineStr"/>
+      <c r="Y573" s="2" t="inlineStr"/>
+      <c r="Z573" s="2" t="inlineStr"/>
+      <c r="AA573" s="2" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>Starosel Slovensko S.r.o.</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>Starosel Slovensko S.r.o.</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>20088</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>Michalovce</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>Kosický</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>Štefaniková 76</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="inlineStr">
+        <is>
+          <t>07101</t>
+        </is>
+      </c>
+      <c r="I574" s="2" t="inlineStr">
+        <is>
+          <t>http://starosel.sk, https://www.staroselshop.sk</t>
+        </is>
+      </c>
+      <c r="J574" s="2" t="inlineStr"/>
+      <c r="K574" s="2" t="inlineStr"/>
+      <c r="L574" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M574" s="2" t="inlineStr"/>
+      <c r="N574" s="2" t="inlineStr">
+        <is>
+          <t>starosel@starosel.sk</t>
+        </is>
+      </c>
+      <c r="O574" s="2" t="inlineStr"/>
+      <c r="P574" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q574" s="2" t="inlineStr">
+        <is>
+          <t>47689901</t>
+        </is>
+      </c>
+      <c r="R574" s="2" t="inlineStr"/>
+      <c r="S574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/starosel.sk/</t>
+        </is>
+      </c>
+      <c r="T574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/staroselslovensko/</t>
+        </is>
+      </c>
+      <c r="U574" s="2" t="inlineStr"/>
+      <c r="V574" s="2" t="inlineStr"/>
+      <c r="W574" s="2" t="inlineStr"/>
+      <c r="X574" s="2" t="inlineStr"/>
+      <c r="Y574" s="2" t="inlineStr"/>
+      <c r="Z574" s="2" t="inlineStr"/>
+      <c r="AA574" s="2" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>Extraprodukty, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>Extraprodukty, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>20087</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="inlineStr">
+        <is>
+          <t>Šamorín</t>
+        </is>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj, Dunajská Streda</t>
+        </is>
+      </c>
+      <c r="G575" s="2" t="inlineStr">
+        <is>
+          <t>Vodárenská 2589/2A</t>
+        </is>
+      </c>
+      <c r="H575" s="2" t="inlineStr">
+        <is>
+          <t>931 01</t>
+        </is>
+      </c>
+      <c r="I575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.extraprodukty.sk</t>
+        </is>
+      </c>
+      <c r="J575" s="2" t="inlineStr"/>
+      <c r="K575" s="2" t="inlineStr"/>
+      <c r="L575" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M575" s="2" t="inlineStr"/>
+      <c r="N575" s="2" t="inlineStr">
+        <is>
+          <t>obchod@extraprodukty.sk</t>
+        </is>
+      </c>
+      <c r="O575" s="2" t="inlineStr"/>
+      <c r="P575" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q575" s="2" t="inlineStr">
+        <is>
+          <t>46158880</t>
+        </is>
+      </c>
+      <c r="R575" s="2" t="inlineStr"/>
+      <c r="S575" s="2" t="inlineStr"/>
+      <c r="T575" s="2" t="inlineStr"/>
+      <c r="U575" s="2" t="inlineStr"/>
+      <c r="V575" s="2" t="inlineStr"/>
+      <c r="W575" s="2" t="inlineStr"/>
+      <c r="X575" s="2" t="inlineStr"/>
+      <c r="Y575" s="2" t="inlineStr"/>
+      <c r="Z575" s="2" t="inlineStr"/>
+      <c r="AA575" s="2" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>Mge Plus S.r.o.</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>Mge Plus S.r.o.</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>28275</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>Trenčianska Teplá</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj, Trenčín</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>Andreja Hlinku 34</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="inlineStr">
+        <is>
+          <t>914 01</t>
+        </is>
+      </c>
+      <c r="I576" s="2" t="inlineStr">
+        <is>
+          <t>https://lacnevino.sk</t>
+        </is>
+      </c>
+      <c r="J576" s="2" t="inlineStr"/>
+      <c r="K576" s="2" t="inlineStr"/>
+      <c r="L576" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M576" s="2" t="inlineStr"/>
+      <c r="N576" s="2" t="inlineStr">
+        <is>
+          <t>mgeplus@centrum.sk</t>
+        </is>
+      </c>
+      <c r="O576" s="2" t="inlineStr"/>
+      <c r="P576" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q576" s="2" t="inlineStr">
+        <is>
+          <t>46198687</t>
+        </is>
+      </c>
+      <c r="R576" s="2" t="inlineStr"/>
+      <c r="S576" s="2" t="inlineStr"/>
+      <c r="T576" s="2" t="inlineStr"/>
+      <c r="U576" s="2" t="inlineStr"/>
+      <c r="V576" s="2" t="inlineStr"/>
+      <c r="W576" s="2" t="inlineStr">
+        <is>
+          <t>Monika Jančová</t>
+        </is>
+      </c>
+      <c r="X576" s="2" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="Y576" s="2" t="inlineStr"/>
+      <c r="Z576" s="2" t="inlineStr"/>
+      <c r="AA576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/monika-jan%C4%8Dov%C3%A1-7ab50a220/</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Pri Modrom Kostolíku</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Pri Modrom Kostolíku</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>49625</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F577" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj I</t>
+        </is>
+      </c>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>2541/2 Sienkiewiczova</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="inlineStr">
+        <is>
+          <t>811 09</t>
+        </is>
+      </c>
+      <c r="I577" s="2" t="inlineStr">
+        <is>
+          <t>https://vinotekamodrykostolik.sk</t>
+        </is>
+      </c>
+      <c r="J577" s="2" t="inlineStr"/>
+      <c r="K577" s="2" t="inlineStr"/>
+      <c r="L577" s="2" t="inlineStr"/>
+      <c r="M577" s="2" t="inlineStr"/>
+      <c r="N577" s="2" t="inlineStr">
+        <is>
+          <t>vinoteka@modrykostolik.sk</t>
+        </is>
+      </c>
+      <c r="O577" s="2" t="inlineStr"/>
+      <c r="P577" s="2" t="inlineStr"/>
+      <c r="Q577" s="2" t="inlineStr"/>
+      <c r="R577" s="2" t="inlineStr"/>
+      <c r="S577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekaprimodromkostoliku/</t>
+        </is>
+      </c>
+      <c r="T577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_modry_kostolik/</t>
+        </is>
+      </c>
+      <c r="U577" s="2" t="inlineStr"/>
+      <c r="V577" s="2" t="inlineStr"/>
+      <c r="W577" s="2" t="inlineStr"/>
+      <c r="X577" s="2" t="inlineStr"/>
+      <c r="Y577" s="2" t="inlineStr"/>
+      <c r="Z577" s="2" t="inlineStr"/>
+      <c r="AA577" s="2" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>Lumarkt, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>Lumarkt, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>11890</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>Staré Mesto</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj, Košice I</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>1 Hutnícka</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="inlineStr">
+        <is>
+          <t>040 01</t>
+        </is>
+      </c>
+      <c r="I578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lumarkt.sk</t>
+        </is>
+      </c>
+      <c r="J578" s="2" t="inlineStr"/>
+      <c r="K578" s="2" t="inlineStr"/>
+      <c r="L578" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M578" s="2" t="inlineStr"/>
+      <c r="N578" s="2" t="inlineStr">
+        <is>
+          <t>info@lumarkt.sk</t>
+        </is>
+      </c>
+      <c r="O578" s="2" t="inlineStr">
+        <is>
+          <t>+421 55 798 85 71</t>
+        </is>
+      </c>
+      <c r="P578" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q578" s="2" t="inlineStr">
+        <is>
+          <t>36216631</t>
+        </is>
+      </c>
+      <c r="R578" s="2" t="inlineStr"/>
+      <c r="S578" s="2" t="inlineStr"/>
+      <c r="T578" s="2" t="inlineStr"/>
+      <c r="U578" s="2" t="inlineStr"/>
+      <c r="V578" s="2" t="inlineStr"/>
+      <c r="W578" s="2" t="inlineStr">
+        <is>
+          <t>Janka Mrugova</t>
+        </is>
+      </c>
+      <c r="X578" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y578" s="2" t="inlineStr"/>
+      <c r="Z578" s="2" t="inlineStr"/>
+      <c r="AA578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/janka-mrugova-b5364047/</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>Karmen - Velkoobchod Potravín S.r.o.</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>Karmen - Velkoobchod Potravín S.r.o.</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>54186</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>Prešov</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>Prešovský kraj</t>
+        </is>
+      </c>
+      <c r="G579" s="2" t="inlineStr">
+        <is>
+          <t>15 Strojnícka</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="inlineStr">
+        <is>
+          <t>080 06</t>
+        </is>
+      </c>
+      <c r="I579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karmen.sk</t>
+        </is>
+      </c>
+      <c r="J579" s="2" t="inlineStr"/>
+      <c r="K579" s="2" t="inlineStr"/>
+      <c r="L579" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="M579" s="2" t="inlineStr"/>
+      <c r="N579" s="2" t="inlineStr">
+        <is>
+          <t>karmen@karmen.sk</t>
+        </is>
+      </c>
+      <c r="O579" s="2" t="inlineStr">
+        <is>
+          <t>+421 51/771 17 14</t>
+        </is>
+      </c>
+      <c r="P579" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q579" s="2" t="inlineStr">
+        <is>
+          <t>36447269</t>
+        </is>
+      </c>
+      <c r="R579" s="2" t="inlineStr"/>
+      <c r="S579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100063498972682</t>
+        </is>
+      </c>
+      <c r="T579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cba_karmen/</t>
+        </is>
+      </c>
+      <c r="U579" s="2" t="inlineStr"/>
+      <c r="V579" s="2" t="inlineStr"/>
+      <c r="W579" s="2" t="inlineStr"/>
+      <c r="X579" s="2" t="inlineStr"/>
+      <c r="Y579" s="2" t="inlineStr"/>
+      <c r="Z579" s="2" t="inlineStr"/>
+      <c r="AA579" s="2" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>Great Wines Cellar</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>Great Wines Cellar</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>24602</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>Ružinov</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava II</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>937 Koceľova</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>821 08</t>
+        </is>
+      </c>
+      <c r="I580" s="2" t="inlineStr">
+        <is>
+          <t>https://greatwinescellar.com</t>
+        </is>
+      </c>
+      <c r="J580" s="2" t="inlineStr"/>
+      <c r="K580" s="2" t="inlineStr"/>
+      <c r="L580" s="2" t="inlineStr"/>
+      <c r="M580" s="2" t="inlineStr"/>
+      <c r="N580" s="2" t="inlineStr">
+        <is>
+          <t>info@greatwinescellar.com</t>
+        </is>
+      </c>
+      <c r="O580" s="2" t="inlineStr">
+        <is>
+          <t>+43 1 9437915</t>
+        </is>
+      </c>
+      <c r="P580" s="2" t="inlineStr"/>
+      <c r="Q580" s="2" t="inlineStr"/>
+      <c r="R580" s="2" t="inlineStr"/>
+      <c r="S580" s="2" t="inlineStr"/>
+      <c r="T580" s="2" t="inlineStr"/>
+      <c r="U580" s="2" t="inlineStr"/>
+      <c r="V580" s="2" t="inlineStr"/>
+      <c r="W580" s="2" t="inlineStr">
+        <is>
+          <t>Denis Danilenko</t>
+        </is>
+      </c>
+      <c r="X580" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y580" s="2" t="inlineStr"/>
+      <c r="Z580" s="2" t="inlineStr"/>
+      <c r="AA580" s="2" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>Vineria S.r.o.</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>Vineria S.r.o.</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>108851</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>Topoľčany</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>Nitriansky kraj</t>
+        </is>
+      </c>
+      <c r="G581" s="2" t="inlineStr">
+        <is>
+          <t>958, 20 Československej armády</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>955 01</t>
+        </is>
+      </c>
+      <c r="I581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vineria.sk</t>
+        </is>
+      </c>
+      <c r="J581" s="2" t="inlineStr"/>
+      <c r="K581" s="2" t="inlineStr"/>
+      <c r="L581" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M581" s="2" t="inlineStr"/>
+      <c r="N581" s="2" t="inlineStr">
+        <is>
+          <t>obchod@vineria.sk</t>
+        </is>
+      </c>
+      <c r="O581" s="2" t="inlineStr"/>
+      <c r="P581" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q581" s="2" t="inlineStr">
+        <is>
+          <t>46409165</t>
+        </is>
+      </c>
+      <c r="R581" s="2" t="inlineStr"/>
+      <c r="S581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Vineria-Topo%C4%BE%C4%8Dany-100027232792145/</t>
+        </is>
+      </c>
+      <c r="T581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_vineria_/</t>
+        </is>
+      </c>
+      <c r="U581" s="2" t="inlineStr"/>
+      <c r="V581" s="2" t="inlineStr"/>
+      <c r="W581" s="2" t="inlineStr"/>
+      <c r="X581" s="2" t="inlineStr"/>
+      <c r="Y581" s="2" t="inlineStr"/>
+      <c r="Z581" s="2" t="inlineStr"/>
+      <c r="AA581" s="2" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>Novino, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>Novino, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>108848</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava I</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>4087, 26 Krížna</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>811 07</t>
+        </is>
+      </c>
+      <c r="I582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novino.sk</t>
+        </is>
+      </c>
+      <c r="J582" s="2" t="inlineStr"/>
+      <c r="K582" s="2" t="inlineStr"/>
+      <c r="L582" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M582" s="2" t="inlineStr"/>
+      <c r="N582" s="2" t="inlineStr">
+        <is>
+          <t>predaj@novino.sk</t>
+        </is>
+      </c>
+      <c r="O582" s="2" t="inlineStr"/>
+      <c r="P582" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q582" s="2" t="inlineStr">
+        <is>
+          <t>53348800</t>
+        </is>
+      </c>
+      <c r="R582" s="2" t="inlineStr"/>
+      <c r="S582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Novino.sk/</t>
+        </is>
+      </c>
+      <c r="T582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/novino_sk/</t>
+        </is>
+      </c>
+      <c r="U582" s="2" t="inlineStr"/>
+      <c r="V582" s="2" t="inlineStr"/>
+      <c r="W582" s="2" t="inlineStr">
+        <is>
+          <t>Marek Paulen</t>
+        </is>
+      </c>
+      <c r="X582" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y582" s="2" t="inlineStr"/>
+      <c r="Z582" s="2" t="inlineStr"/>
+      <c r="AA582" s="2" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>ENERGY TRANS, spol. s r.o.</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>Dom Vína žilina</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>11919</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr">
+        <is>
+          <t>Rosina</t>
+        </is>
+      </c>
+      <c r="F583" s="2" t="inlineStr"/>
+      <c r="G583" s="2" t="inlineStr">
+        <is>
+          <t>Rosina 1057</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="inlineStr">
+        <is>
+          <t>013 22</t>
+        </is>
+      </c>
+      <c r="I583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kupvino.sk</t>
+        </is>
+      </c>
+      <c r="J583" s="2" t="inlineStr"/>
+      <c r="K583" s="2" t="inlineStr"/>
+      <c r="L583" s="2" t="inlineStr"/>
+      <c r="M583" s="2" t="inlineStr"/>
+      <c r="N583" s="2" t="inlineStr">
+        <is>
+          <t>kupvino@kupvino.sk</t>
+        </is>
+      </c>
+      <c r="O583" s="2" t="inlineStr"/>
+      <c r="P583" s="2" t="inlineStr"/>
+      <c r="Q583" s="2" t="inlineStr"/>
+      <c r="R583" s="2" t="inlineStr"/>
+      <c r="S583" s="2" t="inlineStr"/>
+      <c r="T583" s="2" t="inlineStr"/>
+      <c r="U583" s="2" t="inlineStr"/>
+      <c r="V583" s="2" t="inlineStr"/>
+      <c r="W583" s="2" t="inlineStr"/>
+      <c r="X583" s="2" t="inlineStr"/>
+      <c r="Y583" s="2" t="inlineStr"/>
+      <c r="Z583" s="2" t="inlineStr"/>
+      <c r="AA583" s="2" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>Vinalma, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>Vinalma, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>11903</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>76 Opatovská</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="inlineStr">
+        <is>
+          <t>911 01</t>
+        </is>
+      </c>
+      <c r="I584" s="2" t="inlineStr">
+        <is>
+          <t>http://www.vinalma.sk</t>
+        </is>
+      </c>
+      <c r="J584" s="2" t="inlineStr"/>
+      <c r="K584" s="2" t="inlineStr"/>
+      <c r="L584" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M584" s="2" t="inlineStr"/>
+      <c r="N584" s="2" t="inlineStr">
+        <is>
+          <t>office@vinalma.sk</t>
+        </is>
+      </c>
+      <c r="O584" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/744 58 12</t>
+        </is>
+      </c>
+      <c r="P584" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q584" s="2" t="inlineStr">
+        <is>
+          <t>35697768</t>
+        </is>
+      </c>
+      <c r="R584" s="2" t="inlineStr"/>
+      <c r="S584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinalmaSro/</t>
+        </is>
+      </c>
+      <c r="T584" s="2" t="inlineStr"/>
+      <c r="U584" s="2" t="inlineStr"/>
+      <c r="V584" s="2" t="inlineStr"/>
+      <c r="W584" s="2" t="inlineStr">
+        <is>
+          <t>Edita Durcova</t>
+        </is>
+      </c>
+      <c r="X584" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y584" s="2" t="inlineStr"/>
+      <c r="Z584" s="2" t="inlineStr"/>
+      <c r="AA584" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/edita-durcova-4856203a</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>Pálinkás-Szicsek sro</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>Szicsek Slovakia</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>20089</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr">
+        <is>
+          <t>Dunajská Streda</t>
+        </is>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj</t>
+        </is>
+      </c>
+      <c r="G585" s="2" t="inlineStr">
+        <is>
+          <t>39, 29 Hlavná</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="inlineStr">
+        <is>
+          <t>929 01</t>
+        </is>
+      </c>
+      <c r="I585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.palinkas.sk</t>
+        </is>
+      </c>
+      <c r="J585" s="2" t="inlineStr"/>
+      <c r="K585" s="2" t="inlineStr"/>
+      <c r="L585" s="2" t="inlineStr"/>
+      <c r="M585" s="2" t="inlineStr"/>
+      <c r="N585" s="2" t="inlineStr">
+        <is>
+          <t>palinka-wine@palinkas.sk</t>
+        </is>
+      </c>
+      <c r="O585" s="2" t="inlineStr"/>
+      <c r="P585" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q585" s="2" t="inlineStr">
+        <is>
+          <t>33934363</t>
+        </is>
+      </c>
+      <c r="R585" s="2" t="inlineStr"/>
+      <c r="S585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SzicsekSlovensko</t>
+        </is>
+      </c>
+      <c r="T585" s="2" t="inlineStr"/>
+      <c r="U585" s="2" t="inlineStr"/>
+      <c r="V585" s="2" t="inlineStr"/>
+      <c r="W585" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Pálinkás</t>
+        </is>
+      </c>
+      <c r="X585" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y585" s="2" t="inlineStr"/>
+      <c r="Z585" s="2" t="inlineStr"/>
+      <c r="AA585" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/gabriel-pálinkás-440998a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>Sklié, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>La Vie en Rose</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>31686</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava I</t>
+        </is>
+      </c>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>4 Radlinského</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="inlineStr">
+        <is>
+          <t>811 07</t>
+        </is>
+      </c>
+      <c r="I586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lavieenrose.sk</t>
+        </is>
+      </c>
+      <c r="J586" s="2" t="inlineStr"/>
+      <c r="K586" s="2" t="inlineStr"/>
+      <c r="L586" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M586" s="2" t="inlineStr"/>
+      <c r="N586" s="2" t="inlineStr">
+        <is>
+          <t>info@lavieenrose.sk</t>
+        </is>
+      </c>
+      <c r="O586" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/524 927 42</t>
+        </is>
+      </c>
+      <c r="P586" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q586" s="2" t="inlineStr">
+        <is>
+          <t>35950978</t>
+        </is>
+      </c>
+      <c r="R586" s="2" t="inlineStr"/>
+      <c r="S586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinotekaLaVieenRose/</t>
+        </is>
+      </c>
+      <c r="T586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotekalavieenrose/</t>
+        </is>
+      </c>
+      <c r="U586" s="2" t="inlineStr"/>
+      <c r="V586" s="2" t="inlineStr"/>
+      <c r="W586" s="2" t="inlineStr"/>
+      <c r="X586" s="2" t="inlineStr"/>
+      <c r="Y586" s="2" t="inlineStr"/>
+      <c r="Z586" s="2" t="inlineStr"/>
+      <c r="AA586" s="2" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>Belvet, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>Belvet, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>11913</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr">
+        <is>
+          <t>Križovany nad Dudváhom</t>
+        </is>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>Trnavský kraj, Trnava</t>
+        </is>
+      </c>
+      <c r="G587" s="2" t="inlineStr">
+        <is>
+          <t>Križovany Nad Dudváhom 511</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="inlineStr">
+        <is>
+          <t>919 24</t>
+        </is>
+      </c>
+      <c r="I587" s="2" t="inlineStr">
+        <is>
+          <t>https://belvet.sk</t>
+        </is>
+      </c>
+      <c r="J587" s="2" t="inlineStr"/>
+      <c r="K587" s="2" t="inlineStr"/>
+      <c r="L587" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M587" s="2" t="inlineStr"/>
+      <c r="N587" s="2" t="inlineStr">
+        <is>
+          <t>belvet@belvet.sk</t>
+        </is>
+      </c>
+      <c r="O587" s="2" t="inlineStr"/>
+      <c r="P587" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q587" s="2" t="inlineStr">
+        <is>
+          <t>46284699</t>
+        </is>
+      </c>
+      <c r="R587" s="2" t="inlineStr"/>
+      <c r="S587" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/belvet.eshop</t>
+        </is>
+      </c>
+      <c r="T587" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/belvet.sk.lubos/</t>
+        </is>
+      </c>
+      <c r="U587" s="2" t="inlineStr"/>
+      <c r="V587" s="2" t="inlineStr"/>
+      <c r="W587" s="2" t="inlineStr"/>
+      <c r="X587" s="2" t="inlineStr"/>
+      <c r="Y587" s="2" t="inlineStr"/>
+      <c r="Z587" s="2" t="inlineStr"/>
+      <c r="AA587" s="2" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>Vinocentrum S. R. O.</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>Vinocentrum S. R. O.</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>58758</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr">
+        <is>
+          <t>Banska Stiavnica</t>
+        </is>
+      </c>
+      <c r="F588" s="2" t="inlineStr"/>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>Kammerhofská 178/2</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="inlineStr">
+        <is>
+          <t>96901</t>
+        </is>
+      </c>
+      <c r="I588" s="2" t="inlineStr">
+        <is>
+          <t>https://vinocentrum.sk</t>
+        </is>
+      </c>
+      <c r="J588" s="2" t="inlineStr"/>
+      <c r="K588" s="2" t="inlineStr"/>
+      <c r="L588" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M588" s="2" t="inlineStr"/>
+      <c r="N588" s="2" t="inlineStr">
+        <is>
+          <t>vinocentrum@gmail.com</t>
+        </is>
+      </c>
+      <c r="O588" s="2" t="inlineStr"/>
+      <c r="P588" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q588" s="2" t="inlineStr">
+        <is>
+          <t>53125967</t>
+        </is>
+      </c>
+      <c r="R588" s="2" t="inlineStr"/>
+      <c r="S588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinocentrum/</t>
+        </is>
+      </c>
+      <c r="T588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinocentrum/</t>
+        </is>
+      </c>
+      <c r="U588" s="2" t="inlineStr"/>
+      <c r="V588" s="2" t="inlineStr"/>
+      <c r="W588" s="2" t="inlineStr">
+        <is>
+          <t>Brano Bahna</t>
+        </is>
+      </c>
+      <c r="X588" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y588" s="2" t="inlineStr"/>
+      <c r="Z588" s="2" t="inlineStr"/>
+      <c r="AA588" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/brano-bahna-a394978b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>58756</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov</t>
+        </is>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
+        <is>
+          <t>Trnava Region, Trnava District</t>
+        </is>
+      </c>
+      <c r="G589" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov 464</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="inlineStr">
+        <is>
+          <t>919 22</t>
+        </is>
+      </c>
+      <c r="I589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoteka-cassalle.sk</t>
+        </is>
+      </c>
+      <c r="J589" s="2" t="inlineStr"/>
+      <c r="K589" s="2" t="inlineStr"/>
+      <c r="L589" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M589" s="2" t="inlineStr"/>
+      <c r="N589" s="2" t="inlineStr">
+        <is>
+          <t>cassalle.vinoteka@gmail.com</t>
+        </is>
+      </c>
+      <c r="O589" s="2" t="inlineStr"/>
+      <c r="P589" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q589" s="2" t="inlineStr">
+        <is>
+          <t>46829679</t>
+        </is>
+      </c>
+      <c r="R589" s="2" t="inlineStr"/>
+      <c r="S589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekacassalletrnava/</t>
+        </is>
+      </c>
+      <c r="T589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cassallevinoteka</t>
+        </is>
+      </c>
+      <c r="U589" s="2" t="inlineStr"/>
+      <c r="V589" s="2" t="inlineStr"/>
+      <c r="W589" s="2" t="inlineStr">
+        <is>
+          <t>Marcel Kuracina</t>
+        </is>
+      </c>
+      <c r="X589" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y589" s="2" t="inlineStr"/>
+      <c r="Z589" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA589" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/marcel-kuracina-0464b9a5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>Amk Group S.r.o.</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>58756</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov</t>
+        </is>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
+        <is>
+          <t>Trnava Region, Trnava District</t>
+        </is>
+      </c>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>Majcichov 464</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="inlineStr">
+        <is>
+          <t>919 22</t>
+        </is>
+      </c>
+      <c r="I590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoteka-cassalle.sk</t>
+        </is>
+      </c>
+      <c r="J590" s="2" t="inlineStr"/>
+      <c r="K590" s="2" t="inlineStr"/>
+      <c r="L590" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M590" s="2" t="inlineStr"/>
+      <c r="N590" s="2" t="inlineStr">
+        <is>
+          <t>cassalle.vinoteka@gmail.com</t>
+        </is>
+      </c>
+      <c r="O590" s="2" t="inlineStr"/>
+      <c r="P590" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q590" s="2" t="inlineStr">
+        <is>
+          <t>46829679</t>
+        </is>
+      </c>
+      <c r="R590" s="2" t="inlineStr"/>
+      <c r="S590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekacassalletrnava/</t>
+        </is>
+      </c>
+      <c r="T590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cassallevinoteka</t>
+        </is>
+      </c>
+      <c r="U590" s="2" t="inlineStr"/>
+      <c r="V590" s="2" t="inlineStr"/>
+      <c r="W590" s="2" t="inlineStr">
+        <is>
+          <t>Andrej Kleštinec</t>
+        </is>
+      </c>
+      <c r="X590" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y590" s="2" t="inlineStr"/>
+      <c r="Z590" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA590" s="2" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>Michal Heinz - Obchod S Vínom</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>Michal Heinz - Obchod S Vínom</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>20097</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="inlineStr">
+        <is>
+          <t>Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="F591" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj</t>
+        </is>
+      </c>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>97, 41 Horná</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="inlineStr">
+        <is>
+          <t>974 01</t>
+        </is>
+      </c>
+      <c r="I591" s="2" t="inlineStr">
+        <is>
+          <t>http://www.somelier.sk</t>
+        </is>
+      </c>
+      <c r="J591" s="2" t="inlineStr"/>
+      <c r="K591" s="2" t="inlineStr"/>
+      <c r="L591" s="2" t="inlineStr"/>
+      <c r="M591" s="2" t="inlineStr"/>
+      <c r="N591" s="2" t="inlineStr">
+        <is>
+          <t>somelier@somelier.sk</t>
+        </is>
+      </c>
+      <c r="O591" s="2" t="inlineStr"/>
+      <c r="P591" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q591" s="2" t="inlineStr">
+        <is>
+          <t>40888789</t>
+        </is>
+      </c>
+      <c r="R591" s="2" t="inlineStr"/>
+      <c r="S591" s="2" t="inlineStr"/>
+      <c r="T591" s="2" t="inlineStr"/>
+      <c r="U591" s="2" t="inlineStr"/>
+      <c r="V591" s="2" t="inlineStr"/>
+      <c r="W591" s="2" t="inlineStr"/>
+      <c r="X591" s="2" t="inlineStr"/>
+      <c r="Y591" s="2" t="inlineStr"/>
+      <c r="Z591" s="2" t="inlineStr"/>
+      <c r="AA591" s="2" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>54060</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F592" s="2" t="inlineStr"/>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavská 923 (INDUSTRIAL PARK)</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I592" s="2" t="inlineStr">
+        <is>
+          <t>https://pima.sk</t>
+        </is>
+      </c>
+      <c r="J592" s="2" t="inlineStr"/>
+      <c r="K592" s="2" t="inlineStr"/>
+      <c r="L592" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M592" s="2" t="inlineStr"/>
+      <c r="N592" s="2" t="inlineStr">
+        <is>
+          <t>obchod@pima.sk</t>
+        </is>
+      </c>
+      <c r="O592" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/743 09 11</t>
+        </is>
+      </c>
+      <c r="P592" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q592" s="2" t="inlineStr">
+        <is>
+          <t>36350036</t>
+        </is>
+      </c>
+      <c r="R592" s="2" t="inlineStr"/>
+      <c r="S592" s="2" t="inlineStr"/>
+      <c r="T592" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pima.sk</t>
+        </is>
+      </c>
+      <c r="U592" s="2" t="inlineStr"/>
+      <c r="V592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC4phGWgVZeTSxNP3V23gzgQ</t>
+        </is>
+      </c>
+      <c r="W592" s="2" t="inlineStr">
+        <is>
+          <t>Rudolf Ďatko</t>
+        </is>
+      </c>
+      <c r="X592" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Managing Director </t>
+        </is>
+      </c>
+      <c r="Y592" s="2" t="inlineStr"/>
+      <c r="Z592" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA592" s="2" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>Pima, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>54060</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F593" s="2" t="inlineStr"/>
+      <c r="G593" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavská 923 (INDUSTRIAL PARK)</t>
+        </is>
+      </c>
+      <c r="H593" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I593" s="2" t="inlineStr">
+        <is>
+          <t>https://pima.sk</t>
+        </is>
+      </c>
+      <c r="J593" s="2" t="inlineStr"/>
+      <c r="K593" s="2" t="inlineStr"/>
+      <c r="L593" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M593" s="2" t="inlineStr"/>
+      <c r="N593" s="2" t="inlineStr">
+        <is>
+          <t>obchod@pima.sk</t>
+        </is>
+      </c>
+      <c r="O593" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/743 09 11</t>
+        </is>
+      </c>
+      <c r="P593" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q593" s="2" t="inlineStr">
+        <is>
+          <t>36350036</t>
+        </is>
+      </c>
+      <c r="R593" s="2" t="inlineStr"/>
+      <c r="S593" s="2" t="inlineStr"/>
+      <c r="T593" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pima.sk</t>
+        </is>
+      </c>
+      <c r="U593" s="2" t="inlineStr"/>
+      <c r="V593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC4phGWgVZeTSxNP3V23gzgQ</t>
+        </is>
+      </c>
+      <c r="W593" s="2" t="inlineStr">
+        <is>
+          <t>Martin Kotrha</t>
+        </is>
+      </c>
+      <c r="X593" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales Director </t>
+        </is>
+      </c>
+      <c r="Y593" s="2" t="inlineStr"/>
+      <c r="Z593" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA593" s="2" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>11882</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>49 Vlárska</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I594" s="2" t="inlineStr">
+        <is>
+          <t>https://akevino.sk</t>
+        </is>
+      </c>
+      <c r="J594" s="2" t="inlineStr"/>
+      <c r="K594" s="2" t="inlineStr"/>
+      <c r="L594" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M594" s="2" t="inlineStr"/>
+      <c r="N594" s="2" t="inlineStr">
+        <is>
+          <t>obchod@akevino.sk</t>
+        </is>
+      </c>
+      <c r="O594" s="2" t="inlineStr"/>
+      <c r="P594" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q594" s="2" t="inlineStr">
+        <is>
+          <t>45704163</t>
+        </is>
+      </c>
+      <c r="R594" s="2" t="inlineStr"/>
+      <c r="S594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/akevino.sk/</t>
+        </is>
+      </c>
+      <c r="T594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/akevinosk</t>
+        </is>
+      </c>
+      <c r="U594" s="2" t="inlineStr"/>
+      <c r="V594" s="2" t="inlineStr"/>
+      <c r="W594" s="2" t="inlineStr">
+        <is>
+          <t>Matej Poláčik</t>
+        </is>
+      </c>
+      <c r="X594" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y594" s="2" t="inlineStr"/>
+      <c r="Z594" s="2" t="inlineStr"/>
+      <c r="AA594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/matej-pol%C3%A1%C4%8Dik-8b519519b</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>Grandvino S.r.o.</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>11882</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G595" s="2" t="inlineStr">
+        <is>
+          <t>49 Vlárska</t>
+        </is>
+      </c>
+      <c r="H595" s="2" t="inlineStr">
+        <is>
+          <t>911 05</t>
+        </is>
+      </c>
+      <c r="I595" s="2" t="inlineStr">
+        <is>
+          <t>https://akevino.sk</t>
+        </is>
+      </c>
+      <c r="J595" s="2" t="inlineStr"/>
+      <c r="K595" s="2" t="inlineStr"/>
+      <c r="L595" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M595" s="2" t="inlineStr"/>
+      <c r="N595" s="2" t="inlineStr">
+        <is>
+          <t>obchod@akevino.sk</t>
+        </is>
+      </c>
+      <c r="O595" s="2" t="inlineStr"/>
+      <c r="P595" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q595" s="2" t="inlineStr">
+        <is>
+          <t>45704163</t>
+        </is>
+      </c>
+      <c r="R595" s="2" t="inlineStr"/>
+      <c r="S595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/akevino.sk/</t>
+        </is>
+      </c>
+      <c r="T595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/akevinosk</t>
+        </is>
+      </c>
+      <c r="U595" s="2" t="inlineStr"/>
+      <c r="V595" s="2" t="inlineStr"/>
+      <c r="W595" s="2" t="inlineStr">
+        <is>
+          <t>Juraj Drozd</t>
+        </is>
+      </c>
+      <c r="X595" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y595" s="2" t="inlineStr"/>
+      <c r="Z595" s="2" t="inlineStr"/>
+      <c r="AA595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/juraj-drozd-8ab51a19a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>Ing. Anton Minčík - Amicomp</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>Ing. Anton Minčík - Amicomp</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>53942</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr">
+        <is>
+          <t>Košice</t>
+        </is>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj, Košice IV</t>
+        </is>
+      </c>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>7 Omská</t>
+        </is>
+      </c>
+      <c r="H596" s="2" t="inlineStr">
+        <is>
+          <t>040 01</t>
+        </is>
+      </c>
+      <c r="I596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amicomp1.sk</t>
+        </is>
+      </c>
+      <c r="J596" s="2" t="inlineStr"/>
+      <c r="K596" s="2" t="inlineStr"/>
+      <c r="L596" s="2" t="inlineStr"/>
+      <c r="M596" s="2" t="inlineStr"/>
+      <c r="N596" s="2" t="inlineStr">
+        <is>
+          <t>amicomp1@amicomp1.sk</t>
+        </is>
+      </c>
+      <c r="O596" s="2" t="inlineStr"/>
+      <c r="P596" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q596" s="2" t="inlineStr">
+        <is>
+          <t>30673275</t>
+        </is>
+      </c>
+      <c r="R596" s="2" t="inlineStr"/>
+      <c r="S596" s="2" t="inlineStr"/>
+      <c r="T596" s="2" t="inlineStr"/>
+      <c r="U596" s="2" t="inlineStr"/>
+      <c r="V596" s="2" t="inlineStr"/>
+      <c r="W596" s="2" t="inlineStr">
+        <is>
+          <t>Anton Minčík</t>
+        </is>
+      </c>
+      <c r="X596" s="2" t="inlineStr">
+        <is>
+          <t>Owner - Manager</t>
+        </is>
+      </c>
+      <c r="Y596" s="2" t="inlineStr"/>
+      <c r="Z596" s="2" t="inlineStr"/>
+      <c r="AA596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anton-mincik-43b691101/</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>Vk Suma Sro</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>Vk Suma Sro</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>53809</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="inlineStr">
+        <is>
+          <t>Veľký Krtíš</t>
+        </is>
+      </c>
+      <c r="F597" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj</t>
+        </is>
+      </c>
+      <c r="G597" s="2" t="inlineStr">
+        <is>
+          <t>27 Osloboditeľov</t>
+        </is>
+      </c>
+      <c r="H597" s="2" t="inlineStr">
+        <is>
+          <t>990 01</t>
+        </is>
+      </c>
+      <c r="I597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vksuma.sk</t>
+        </is>
+      </c>
+      <c r="J597" s="2" t="inlineStr"/>
+      <c r="K597" s="2" t="inlineStr"/>
+      <c r="L597" s="2" t="inlineStr"/>
+      <c r="M597" s="2" t="inlineStr"/>
+      <c r="N597" s="2" t="inlineStr">
+        <is>
+          <t>karolszuma@gmail.com</t>
+        </is>
+      </c>
+      <c r="O597" s="2" t="inlineStr">
+        <is>
+          <t>+421 47 483 11 00</t>
+        </is>
+      </c>
+      <c r="P597" s="2" t="inlineStr"/>
+      <c r="Q597" s="2" t="inlineStr"/>
+      <c r="R597" s="2" t="inlineStr"/>
+      <c r="S597" s="2" t="inlineStr"/>
+      <c r="T597" s="2" t="inlineStr"/>
+      <c r="U597" s="2" t="inlineStr"/>
+      <c r="V597" s="2" t="inlineStr"/>
+      <c r="W597" s="2" t="inlineStr"/>
+      <c r="X597" s="2" t="inlineStr"/>
+      <c r="Y597" s="2" t="inlineStr"/>
+      <c r="Z597" s="2" t="inlineStr"/>
+      <c r="AA597" s="2" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F598" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj IV</t>
+        </is>
+      </c>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>28a Jána Stanislava</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="inlineStr">
+        <is>
+          <t>841 05</t>
+        </is>
+      </c>
+      <c r="I598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koft.sk</t>
+        </is>
+      </c>
+      <c r="J598" s="2" t="inlineStr"/>
+      <c r="K598" s="2" t="inlineStr"/>
+      <c r="L598" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M598" s="2" t="inlineStr"/>
+      <c r="N598" s="2" t="inlineStr">
+        <is>
+          <t>infokoft@koft.sk</t>
+        </is>
+      </c>
+      <c r="O598" s="2" t="inlineStr">
+        <is>
+          <t>+421 2 502 052 00</t>
+        </is>
+      </c>
+      <c r="P598" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q598" s="2" t="inlineStr">
+        <is>
+          <t>17335248</t>
+        </is>
+      </c>
+      <c r="R598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/koft-s-r-o/</t>
+        </is>
+      </c>
+      <c r="S598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/otazkavoflasi</t>
+        </is>
+      </c>
+      <c r="T598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/koft.sk</t>
+        </is>
+      </c>
+      <c r="U598" s="2" t="inlineStr"/>
+      <c r="V598" s="2" t="inlineStr"/>
+      <c r="W598" s="2" t="inlineStr">
+        <is>
+          <t>Branislav Machovič</t>
+        </is>
+      </c>
+      <c r="X598" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y598" s="2" t="inlineStr"/>
+      <c r="Z598" s="2" t="inlineStr"/>
+      <c r="AA598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/branislav-machovič-53a57085</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>Koft, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F599" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj IV</t>
+        </is>
+      </c>
+      <c r="G599" s="2" t="inlineStr">
+        <is>
+          <t>28a Jána Stanislava</t>
+        </is>
+      </c>
+      <c r="H599" s="2" t="inlineStr">
+        <is>
+          <t>841 05</t>
+        </is>
+      </c>
+      <c r="I599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koft.sk</t>
+        </is>
+      </c>
+      <c r="J599" s="2" t="inlineStr"/>
+      <c r="K599" s="2" t="inlineStr"/>
+      <c r="L599" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M599" s="2" t="inlineStr"/>
+      <c r="N599" s="2" t="inlineStr">
+        <is>
+          <t>infokoft@koft.sk</t>
+        </is>
+      </c>
+      <c r="O599" s="2" t="inlineStr">
+        <is>
+          <t>+421 2 502 052 00</t>
+        </is>
+      </c>
+      <c r="P599" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q599" s="2" t="inlineStr">
+        <is>
+          <t>17335248</t>
+        </is>
+      </c>
+      <c r="R599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/koft-s-r-o/</t>
+        </is>
+      </c>
+      <c r="S599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/otazkavoflasi</t>
+        </is>
+      </c>
+      <c r="T599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/koft.sk</t>
+        </is>
+      </c>
+      <c r="U599" s="2" t="inlineStr"/>
+      <c r="V599" s="2" t="inlineStr"/>
+      <c r="W599" s="2" t="inlineStr">
+        <is>
+          <t>Martin Lešo</t>
+        </is>
+      </c>
+      <c r="X599" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y599" s="2" t="inlineStr"/>
+      <c r="Z599" s="2" t="inlineStr"/>
+      <c r="AA599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martin-le%C5%A1o-8536aa34/?originalSubdomain=sk</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>Valsesia, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>Valsesia, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>11929</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>Budča</t>
+        </is>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj, Zvolen</t>
+        </is>
+      </c>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>10 Stromová</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="inlineStr">
+        <is>
+          <t>962 33</t>
+        </is>
+      </c>
+      <c r="I600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vino-obchod.sk</t>
+        </is>
+      </c>
+      <c r="J600" s="2" t="inlineStr"/>
+      <c r="K600" s="2" t="inlineStr"/>
+      <c r="L600" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M600" s="2" t="inlineStr"/>
+      <c r="N600" s="2" t="inlineStr">
+        <is>
+          <t>info@vino-obchod.sk</t>
+        </is>
+      </c>
+      <c r="O600" s="2" t="inlineStr"/>
+      <c r="P600" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q600" s="2" t="inlineStr">
+        <is>
+          <t>36626031</t>
+        </is>
+      </c>
+      <c r="R600" s="2" t="inlineStr"/>
+      <c r="S600" s="2" t="inlineStr"/>
+      <c r="T600" s="2" t="inlineStr"/>
+      <c r="U600" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Valsesiasro</t>
+        </is>
+      </c>
+      <c r="V600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCAnww4K_EunrRxjdBi6EfvQ</t>
+        </is>
+      </c>
+      <c r="W600" s="2" t="inlineStr">
+        <is>
+          <t>Róbert Mráz</t>
+        </is>
+      </c>
+      <c r="X600" s="2" t="inlineStr">
+        <is>
+          <t>Executive Manager</t>
+        </is>
+      </c>
+      <c r="Y600" s="2" t="inlineStr"/>
+      <c r="Z600" s="2" t="inlineStr"/>
+      <c r="AA600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/r%C3%B3bert-mr%C3%A1z-718436153/</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>Diskonto S.r.o.</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>Diskonto S.r.o.</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>54205</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr">
+        <is>
+          <t>Spišská Nová Ves</t>
+        </is>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
+        <is>
+          <t>Košický kraj</t>
+        </is>
+      </c>
+      <c r="G601" s="2" t="inlineStr">
+        <is>
+          <t>17 Radlinského</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="inlineStr">
+        <is>
+          <t>052 01</t>
+        </is>
+      </c>
+      <c r="I601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.diskonto.sk</t>
+        </is>
+      </c>
+      <c r="J601" s="2" t="inlineStr"/>
+      <c r="K601" s="2" t="inlineStr"/>
+      <c r="L601" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M601" s="2" t="inlineStr"/>
+      <c r="N601" s="2" t="inlineStr">
+        <is>
+          <t>diskonto@diskonto.sk</t>
+        </is>
+      </c>
+      <c r="O601" s="2" t="inlineStr"/>
+      <c r="P601" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q601" s="2" t="inlineStr">
+        <is>
+          <t>44541473</t>
+        </is>
+      </c>
+      <c r="R601" s="2" t="inlineStr"/>
+      <c r="S601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/diskontoSK/</t>
+        </is>
+      </c>
+      <c r="T601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diskonto_sk/</t>
+        </is>
+      </c>
+      <c r="U601" s="2" t="inlineStr"/>
+      <c r="V601" s="2" t="inlineStr"/>
+      <c r="W601" s="2" t="inlineStr"/>
+      <c r="X601" s="2" t="inlineStr"/>
+      <c r="Y601" s="2" t="inlineStr"/>
+      <c r="Z601" s="2" t="inlineStr"/>
+      <c r="AA601" s="2" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>Vino Sardo S. R. O.</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>Vino Sardo S. R. O.</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>20247</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>Myjava</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>524/19 Nám. M. R. Štefánika</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="inlineStr">
+        <is>
+          <t>907 01</t>
+        </is>
+      </c>
+      <c r="I602" s="2" t="inlineStr">
+        <is>
+          <t>https://vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="J602" s="2" t="inlineStr"/>
+      <c r="K602" s="2" t="inlineStr"/>
+      <c r="L602" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M602" s="2" t="inlineStr"/>
+      <c r="N602" s="2" t="inlineStr">
+        <is>
+          <t>info@vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="O602" s="2" t="inlineStr">
+        <is>
+          <t>+421 34/653 81 85</t>
+        </is>
+      </c>
+      <c r="P602" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q602" s="2" t="inlineStr">
+        <is>
+          <t>46833625</t>
+        </is>
+      </c>
+      <c r="R602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vino-sardo</t>
+        </is>
+      </c>
+      <c r="S602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinosardo.sk</t>
+        </is>
+      </c>
+      <c r="T602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinosardo</t>
+        </is>
+      </c>
+      <c r="U602" s="2" t="inlineStr"/>
+      <c r="V602" s="2" t="inlineStr"/>
+      <c r="W602" s="2" t="inlineStr">
+        <is>
+          <t>Veronika Lhotska</t>
+        </is>
+      </c>
+      <c r="X602" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y602" s="2" t="inlineStr"/>
+      <c r="Z602" s="2" t="inlineStr"/>
+      <c r="AA602" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/veronika-lhotska-00808511a</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>Fine Wines S.r.o.</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>Fine Wines S.r.o.</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>11880</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G603" s="2" t="inlineStr">
+        <is>
+          <t>Staré Grunty 7A</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="inlineStr">
+        <is>
+          <t>841 04</t>
+        </is>
+      </c>
+      <c r="I603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.finewines.sk</t>
+        </is>
+      </c>
+      <c r="J603" s="2" t="inlineStr"/>
+      <c r="K603" s="2" t="inlineStr"/>
+      <c r="L603" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M603" s="2" t="inlineStr"/>
+      <c r="N603" s="2" t="inlineStr">
+        <is>
+          <t>office@finewines.sk</t>
+        </is>
+      </c>
+      <c r="O603" s="2" t="inlineStr"/>
+      <c r="P603" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q603" s="2" t="inlineStr">
+        <is>
+          <t>35752173</t>
+        </is>
+      </c>
+      <c r="R603" s="2" t="inlineStr"/>
+      <c r="S603" s="2" t="inlineStr"/>
+      <c r="T603" s="2" t="inlineStr"/>
+      <c r="U603" s="2" t="inlineStr"/>
+      <c r="V603" s="2" t="inlineStr"/>
+      <c r="W603" s="2" t="inlineStr"/>
+      <c r="X603" s="2" t="inlineStr"/>
+      <c r="Y603" s="2" t="inlineStr"/>
+      <c r="Z603" s="2" t="inlineStr"/>
+      <c r="AA603" s="2" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>Cromatop, S.r.o</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>Cromatop, S.r.o</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>54109</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>Hôrka nad Váhom</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj, Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>Hôrka Nad Váhom 1</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="inlineStr">
+        <is>
+          <t>916 32</t>
+        </is>
+      </c>
+      <c r="I604" s="2" t="inlineStr">
+        <is>
+          <t>https://croma.sk, https://www.flaskomat.sk</t>
+        </is>
+      </c>
+      <c r="J604" s="2" t="inlineStr"/>
+      <c r="K604" s="2" t="inlineStr"/>
+      <c r="L604" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M604" s="2" t="inlineStr"/>
+      <c r="N604" s="2" t="inlineStr">
+        <is>
+          <t>croma@croma.sk</t>
+        </is>
+      </c>
+      <c r="O604" s="2" t="inlineStr"/>
+      <c r="P604" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q604" s="2" t="inlineStr">
+        <is>
+          <t>36338893</t>
+        </is>
+      </c>
+      <c r="R604" s="2" t="inlineStr"/>
+      <c r="S604" s="2" t="inlineStr"/>
+      <c r="T604" s="2" t="inlineStr"/>
+      <c r="U604" s="2" t="inlineStr"/>
+      <c r="V604" s="2" t="inlineStr"/>
+      <c r="W604" s="2" t="inlineStr">
+        <is>
+          <t>Miloslav Králik</t>
+        </is>
+      </c>
+      <c r="X604" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y604" s="2" t="inlineStr"/>
+      <c r="Z604" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA604" s="2" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>Gourmand Sk S. R. O.</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>Gourmand Sk S. R. O.</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>11918</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F605" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>12573, 50E Tomášikova</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I605" s="2" t="inlineStr">
+        <is>
+          <t>https://vinopolis.sk</t>
+        </is>
+      </c>
+      <c r="J605" s="2" t="inlineStr"/>
+      <c r="K605" s="2" t="inlineStr"/>
+      <c r="L605" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M605" s="2" t="inlineStr"/>
+      <c r="N605" s="2" t="inlineStr">
+        <is>
+          <t>info@vinopolis.sk</t>
+        </is>
+      </c>
+      <c r="O605" s="2" t="inlineStr"/>
+      <c r="P605" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q605" s="2" t="inlineStr">
+        <is>
+          <t>46005188</t>
+        </is>
+      </c>
+      <c r="R605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinopolis-sk/</t>
+        </is>
+      </c>
+      <c r="S605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinopolis.sk/</t>
+        </is>
+      </c>
+      <c r="T605" s="2" t="inlineStr"/>
+      <c r="U605" s="2" t="inlineStr"/>
+      <c r="V605" s="2" t="inlineStr"/>
+      <c r="W605" s="2" t="inlineStr">
+        <is>
+          <t>Tibor Körmendi</t>
+        </is>
+      </c>
+      <c r="X605" s="2" t="inlineStr">
+        <is>
+          <t>Responsible</t>
+        </is>
+      </c>
+      <c r="Y605" s="2" t="inlineStr"/>
+      <c r="Z605" s="2" t="inlineStr"/>
+      <c r="AA605" s="2" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>Ll Wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>Ll Wine S.r.o.</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>42564</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj V</t>
+        </is>
+      </c>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>7 Bosákova</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="inlineStr">
+        <is>
+          <t>851 04</t>
+        </is>
+      </c>
+      <c r="I606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.llwine.sk</t>
+        </is>
+      </c>
+      <c r="J606" s="2" t="inlineStr"/>
+      <c r="K606" s="2" t="inlineStr"/>
+      <c r="L606" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M606" s="2" t="inlineStr"/>
+      <c r="N606" s="2" t="inlineStr">
+        <is>
+          <t>lipka@llwine.sk</t>
+        </is>
+      </c>
+      <c r="O606" s="2" t="inlineStr"/>
+      <c r="P606" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q606" s="2" t="inlineStr">
+        <is>
+          <t>45895813</t>
+        </is>
+      </c>
+      <c r="R606" s="2" t="inlineStr"/>
+      <c r="S606" s="2" t="inlineStr"/>
+      <c r="T606" s="2" t="inlineStr"/>
+      <c r="U606" s="2" t="inlineStr"/>
+      <c r="V606" s="2" t="inlineStr"/>
+      <c r="W606" s="2" t="inlineStr"/>
+      <c r="X606" s="2" t="inlineStr"/>
+      <c r="Y606" s="2" t="inlineStr"/>
+      <c r="Z606" s="2" t="inlineStr"/>
+      <c r="AA606" s="2" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>Barbara Mincíková - Vinopolitan</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>Vinotéka Vinopolitan</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>32100</t>
+        </is>
+      </c>
+      <c r="D607" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F607" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj I</t>
+        </is>
+      </c>
+      <c r="G607" s="2" t="inlineStr">
+        <is>
+          <t>6 Námestie SNP</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="inlineStr">
+        <is>
+          <t>811 06</t>
+        </is>
+      </c>
+      <c r="I607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinopolitan.sk</t>
+        </is>
+      </c>
+      <c r="J607" s="2" t="inlineStr"/>
+      <c r="K607" s="2" t="inlineStr"/>
+      <c r="L607" s="2" t="inlineStr"/>
+      <c r="M607" s="2" t="inlineStr"/>
+      <c r="N607" s="2" t="inlineStr">
+        <is>
+          <t>info@vinopolitan.sk</t>
+        </is>
+      </c>
+      <c r="O607" s="2" t="inlineStr"/>
+      <c r="P607" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q607" s="2" t="inlineStr">
+        <is>
+          <t>47657235</t>
+        </is>
+      </c>
+      <c r="R607" s="2" t="inlineStr"/>
+      <c r="S607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinopolitanbratislava/</t>
+        </is>
+      </c>
+      <c r="T607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinopolitan_wineshop/</t>
+        </is>
+      </c>
+      <c r="U607" s="2" t="inlineStr"/>
+      <c r="V607" s="2" t="inlineStr"/>
+      <c r="W607" s="2" t="inlineStr"/>
+      <c r="X607" s="2" t="inlineStr"/>
+      <c r="Y607" s="2" t="inlineStr"/>
+      <c r="Z607" s="2" t="inlineStr"/>
+      <c r="AA607" s="2" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G608" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I608" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J608" s="2" t="inlineStr"/>
+      <c r="K608" s="2" t="inlineStr"/>
+      <c r="L608" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M608" s="2" t="inlineStr"/>
+      <c r="N608" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O608" s="2" t="inlineStr"/>
+      <c r="P608" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q608" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R608" s="2" t="inlineStr"/>
+      <c r="S608" s="2" t="inlineStr"/>
+      <c r="T608" s="2" t="inlineStr"/>
+      <c r="U608" s="2" t="inlineStr"/>
+      <c r="V608" s="2" t="inlineStr"/>
+      <c r="W608" s="2" t="inlineStr">
+        <is>
+          <t>Pavol Pavlus</t>
+        </is>
+      </c>
+      <c r="X608" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y608" s="2" t="inlineStr"/>
+      <c r="Z608" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA608" s="2" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D609" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F609" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G609" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H609" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I609" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J609" s="2" t="inlineStr"/>
+      <c r="K609" s="2" t="inlineStr"/>
+      <c r="L609" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M609" s="2" t="inlineStr"/>
+      <c r="N609" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O609" s="2" t="inlineStr"/>
+      <c r="P609" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q609" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R609" s="2" t="inlineStr"/>
+      <c r="S609" s="2" t="inlineStr"/>
+      <c r="T609" s="2" t="inlineStr"/>
+      <c r="U609" s="2" t="inlineStr"/>
+      <c r="V609" s="2" t="inlineStr"/>
+      <c r="W609" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Vrska</t>
+        </is>
+      </c>
+      <c r="X609" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y609" s="2" t="inlineStr"/>
+      <c r="Z609" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA609" s="2" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G610" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H610" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I610" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J610" s="2" t="inlineStr"/>
+      <c r="K610" s="2" t="inlineStr"/>
+      <c r="L610" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M610" s="2" t="inlineStr"/>
+      <c r="N610" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O610" s="2" t="inlineStr"/>
+      <c r="P610" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q610" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R610" s="2" t="inlineStr"/>
+      <c r="S610" s="2" t="inlineStr"/>
+      <c r="T610" s="2" t="inlineStr"/>
+      <c r="U610" s="2" t="inlineStr"/>
+      <c r="V610" s="2" t="inlineStr"/>
+      <c r="W610" s="2" t="inlineStr">
+        <is>
+          <t>Štefan Ondrúš</t>
+        </is>
+      </c>
+      <c r="X610" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y610" s="2" t="inlineStr"/>
+      <c r="Z610" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA610" s="2" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F611" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G611" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I611" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J611" s="2" t="inlineStr"/>
+      <c r="K611" s="2" t="inlineStr"/>
+      <c r="L611" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M611" s="2" t="inlineStr"/>
+      <c r="N611" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O611" s="2" t="inlineStr"/>
+      <c r="P611" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q611" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R611" s="2" t="inlineStr"/>
+      <c r="S611" s="2" t="inlineStr"/>
+      <c r="T611" s="2" t="inlineStr"/>
+      <c r="U611" s="2" t="inlineStr"/>
+      <c r="V611" s="2" t="inlineStr"/>
+      <c r="W611" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Bošanský</t>
+        </is>
+      </c>
+      <c r="X611" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y611" s="2" t="inlineStr"/>
+      <c r="Z611" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA611" s="2" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Trade S.r.o.</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj II</t>
+        </is>
+      </c>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>4818/28 Staré záhrady</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>821 05</t>
+        </is>
+      </c>
+      <c r="I612" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="J612" s="2" t="inlineStr"/>
+      <c r="K612" s="2" t="inlineStr"/>
+      <c r="L612" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M612" s="2" t="inlineStr"/>
+      <c r="N612" s="2" t="inlineStr">
+        <is>
+          <t>victoriatrade@victoriatrade.sk</t>
+        </is>
+      </c>
+      <c r="O612" s="2" t="inlineStr"/>
+      <c r="P612" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q612" s="2" t="inlineStr">
+        <is>
+          <t>36278793</t>
+        </is>
+      </c>
+      <c r="R612" s="2" t="inlineStr"/>
+      <c r="S612" s="2" t="inlineStr"/>
+      <c r="T612" s="2" t="inlineStr"/>
+      <c r="U612" s="2" t="inlineStr"/>
+      <c r="V612" s="2" t="inlineStr"/>
+      <c r="W612" s="2" t="inlineStr">
+        <is>
+          <t>Martin Cehula</t>
+        </is>
+      </c>
+      <c r="X612" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y612" s="2" t="inlineStr"/>
+      <c r="Z612" s="2" t="inlineStr"/>
+      <c r="AA612" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
